--- a/spec-tech/ig/all-profiles.xlsx
+++ b/spec-tech/ig/all-profiles.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-09T18:19:16+00:00</t>
+    <t>2026-07-15T06:27:44+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/spec-tech/ig/all-profiles.xlsx
+++ b/spec-tech/ig/all-profiles.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-15T06:27:44+00:00</t>
+    <t>2026-07-15T13:41:49+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/spec-tech/ig/all-profiles.xlsx
+++ b/spec-tech/ig/all-profiles.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13608" uniqueCount="1001">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13704" uniqueCount="1004">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-15T13:41:49+00:00</t>
+    <t>2026-07-15T16:11:54+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -2663,7 +2663,17 @@
     <t>PDLGC Metadata</t>
   </si>
   <si>
-    <t>Le fichier METADATA.XML porte les métadonnées des documents cliniques d'un patient</t>
+    <t>Modèle logique décrivant la structure d'un fichier METADATA associé à un SUBSET IHE XDM.
+Regroupe un SubmissionSet, ses DocumentEntries et les Associations entre objets.</t>
+  </si>
+  <si>
+    <t>pdlgc-metadata.submissionSet</t>
+  </si>
+  <si>
+    <t>pdlgc-metadata.documentEntry</t>
+  </si>
+  <si>
+    <t>pdlgc-metadata.association</t>
   </si>
   <si>
     <t>pdlgc-readme</t>
@@ -8651,7 +8661,7 @@
         <v>2</v>
       </c>
       <c r="B695" t="s" s="2">
-        <v>839</v>
+        <v>842</v>
       </c>
     </row>
     <row r="696">
@@ -8659,7 +8669,7 @@
         <v>4</v>
       </c>
       <c r="B696" t="s" s="2">
-        <v>840</v>
+        <v>843</v>
       </c>
     </row>
     <row r="697">
@@ -8675,7 +8685,7 @@
         <v>8</v>
       </c>
       <c r="B698" t="s" s="2">
-        <v>841</v>
+        <v>844</v>
       </c>
     </row>
     <row r="699">
@@ -8683,7 +8693,7 @@
         <v>9</v>
       </c>
       <c r="B699" t="s" s="2">
-        <v>842</v>
+        <v>845</v>
       </c>
     </row>
     <row r="700">
@@ -8737,7 +8747,7 @@
         <v>22</v>
       </c>
       <c r="B706" t="s" s="2">
-        <v>843</v>
+        <v>846</v>
       </c>
     </row>
     <row r="707">
@@ -8773,7 +8783,7 @@
         <v>30</v>
       </c>
       <c r="B711" t="s" s="2">
-        <v>840</v>
+        <v>843</v>
       </c>
     </row>
     <row r="712">
@@ -8813,7 +8823,7 @@
         <v>2</v>
       </c>
       <c r="B716" t="s" s="2">
-        <v>850</v>
+        <v>853</v>
       </c>
     </row>
     <row r="717">
@@ -8821,7 +8831,7 @@
         <v>4</v>
       </c>
       <c r="B717" t="s" s="2">
-        <v>851</v>
+        <v>854</v>
       </c>
     </row>
     <row r="718">
@@ -8837,7 +8847,7 @@
         <v>8</v>
       </c>
       <c r="B719" t="s" s="2">
-        <v>852</v>
+        <v>855</v>
       </c>
     </row>
     <row r="720">
@@ -8845,7 +8855,7 @@
         <v>9</v>
       </c>
       <c r="B720" t="s" s="2">
-        <v>853</v>
+        <v>856</v>
       </c>
     </row>
     <row r="721">
@@ -8935,7 +8945,7 @@
         <v>30</v>
       </c>
       <c r="B732" t="s" s="2">
-        <v>851</v>
+        <v>854</v>
       </c>
     </row>
     <row r="733">
@@ -8975,7 +8985,7 @@
         <v>2</v>
       </c>
       <c r="B737" t="s" s="2">
-        <v>990</v>
+        <v>993</v>
       </c>
     </row>
     <row r="738">
@@ -8983,7 +8993,7 @@
         <v>4</v>
       </c>
       <c r="B738" t="s" s="2">
-        <v>991</v>
+        <v>994</v>
       </c>
     </row>
     <row r="739">
@@ -8999,7 +9009,7 @@
         <v>8</v>
       </c>
       <c r="B740" t="s" s="2">
-        <v>992</v>
+        <v>995</v>
       </c>
     </row>
     <row r="741">
@@ -9007,7 +9017,7 @@
         <v>9</v>
       </c>
       <c r="B741" t="s" s="2">
-        <v>993</v>
+        <v>996</v>
       </c>
     </row>
     <row r="742">
@@ -9061,7 +9071,7 @@
         <v>22</v>
       </c>
       <c r="B748" t="s" s="2">
-        <v>994</v>
+        <v>997</v>
       </c>
     </row>
     <row r="749">
@@ -9097,7 +9107,7 @@
         <v>30</v>
       </c>
       <c r="B753" t="s" s="2">
-        <v>991</v>
+        <v>994</v>
       </c>
     </row>
     <row r="754">
@@ -9131,7 +9141,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AK379"/>
+  <dimension ref="A1:AK382"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="20.78125" customWidth="true" bestFit="true"/>
@@ -37402,7 +37412,7 @@
         <v>73</v>
       </c>
       <c r="L275" t="s" s="2">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="M275" t="s" s="2">
         <v>837</v>
@@ -37476,7 +37486,7 @@
     </row>
     <row r="276">
       <c r="A276" t="s" s="2">
-        <v>839</v>
+        <v>834</v>
       </c>
       <c r="B276" t="s" s="2">
         <v>839</v>
@@ -37490,10 +37500,10 @@
       </c>
       <c r="F276" s="2"/>
       <c r="G276" t="s" s="2">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="H276" t="s" s="2">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="I276" t="s" s="2">
         <v>73</v>
@@ -37505,13 +37515,13 @@
         <v>73</v>
       </c>
       <c r="L276" t="s" s="2">
-        <v>76</v>
+        <v>488</v>
       </c>
       <c r="M276" t="s" s="2">
-        <v>842</v>
+        <v>489</v>
       </c>
       <c r="N276" t="s" s="2">
-        <v>843</v>
+        <v>489</v>
       </c>
       <c r="O276" s="2"/>
       <c r="P276" s="2"/>
@@ -37562,13 +37572,13 @@
         <v>73</v>
       </c>
       <c r="AG276" t="s" s="2">
-        <v>77</v>
+        <v>839</v>
       </c>
       <c r="AH276" t="s" s="2">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="AI276" t="s" s="2">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="AJ276" t="s" s="2">
         <v>73</v>
@@ -37579,13 +37589,13 @@
     </row>
     <row r="277">
       <c r="A277" t="s" s="2">
-        <v>839</v>
+        <v>834</v>
       </c>
       <c r="B277" t="s" s="2">
-        <v>844</v>
+        <v>840</v>
       </c>
       <c r="C277" t="s" s="2">
-        <v>844</v>
+        <v>840</v>
       </c>
       <c r="D277" s="2"/>
       <c r="E277" t="s" s="2">
@@ -37596,7 +37606,7 @@
         <v>79</v>
       </c>
       <c r="H277" t="s" s="2">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="I277" t="s" s="2">
         <v>73</v>
@@ -37608,13 +37618,13 @@
         <v>73</v>
       </c>
       <c r="L277" t="s" s="2">
-        <v>813</v>
+        <v>491</v>
       </c>
       <c r="M277" t="s" s="2">
-        <v>845</v>
+        <v>492</v>
       </c>
       <c r="N277" t="s" s="2">
-        <v>845</v>
+        <v>492</v>
       </c>
       <c r="O277" s="2"/>
       <c r="P277" s="2"/>
@@ -37665,13 +37675,13 @@
         <v>73</v>
       </c>
       <c r="AG277" t="s" s="2">
-        <v>844</v>
+        <v>840</v>
       </c>
       <c r="AH277" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AI277" t="s" s="2">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="AJ277" t="s" s="2">
         <v>73</v>
@@ -37682,13 +37692,13 @@
     </row>
     <row r="278">
       <c r="A278" t="s" s="2">
-        <v>839</v>
+        <v>834</v>
       </c>
       <c r="B278" t="s" s="2">
-        <v>846</v>
+        <v>841</v>
       </c>
       <c r="C278" t="s" s="2">
-        <v>846</v>
+        <v>841</v>
       </c>
       <c r="D278" s="2"/>
       <c r="E278" t="s" s="2">
@@ -37699,7 +37709,7 @@
         <v>79</v>
       </c>
       <c r="H278" t="s" s="2">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="I278" t="s" s="2">
         <v>73</v>
@@ -37711,13 +37721,13 @@
         <v>73</v>
       </c>
       <c r="L278" t="s" s="2">
-        <v>89</v>
+        <v>494</v>
       </c>
       <c r="M278" t="s" s="2">
-        <v>847</v>
+        <v>495</v>
       </c>
       <c r="N278" t="s" s="2">
-        <v>847</v>
+        <v>495</v>
       </c>
       <c r="O278" s="2"/>
       <c r="P278" s="2"/>
@@ -37768,13 +37778,13 @@
         <v>73</v>
       </c>
       <c r="AG278" t="s" s="2">
-        <v>846</v>
+        <v>841</v>
       </c>
       <c r="AH278" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AI278" t="s" s="2">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="AJ278" t="s" s="2">
         <v>73</v>
@@ -37785,13 +37795,13 @@
     </row>
     <row r="279">
       <c r="A279" t="s" s="2">
-        <v>839</v>
+        <v>842</v>
       </c>
       <c r="B279" t="s" s="2">
-        <v>848</v>
+        <v>842</v>
       </c>
       <c r="C279" t="s" s="2">
-        <v>848</v>
+        <v>842</v>
       </c>
       <c r="D279" s="2"/>
       <c r="E279" t="s" s="2">
@@ -37799,10 +37809,10 @@
       </c>
       <c r="F279" s="2"/>
       <c r="G279" t="s" s="2">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="H279" t="s" s="2">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="I279" t="s" s="2">
         <v>73</v>
@@ -37814,13 +37824,13 @@
         <v>73</v>
       </c>
       <c r="L279" t="s" s="2">
-        <v>89</v>
+        <v>76</v>
       </c>
       <c r="M279" t="s" s="2">
-        <v>849</v>
+        <v>845</v>
       </c>
       <c r="N279" t="s" s="2">
-        <v>849</v>
+        <v>846</v>
       </c>
       <c r="O279" s="2"/>
       <c r="P279" s="2"/>
@@ -37871,13 +37881,13 @@
         <v>73</v>
       </c>
       <c r="AG279" t="s" s="2">
-        <v>848</v>
+        <v>77</v>
       </c>
       <c r="AH279" t="s" s="2">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="AI279" t="s" s="2">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="AJ279" t="s" s="2">
         <v>73</v>
@@ -37888,13 +37898,13 @@
     </row>
     <row r="280">
       <c r="A280" t="s" s="2">
-        <v>850</v>
+        <v>842</v>
       </c>
       <c r="B280" t="s" s="2">
-        <v>850</v>
+        <v>847</v>
       </c>
       <c r="C280" t="s" s="2">
-        <v>850</v>
+        <v>847</v>
       </c>
       <c r="D280" s="2"/>
       <c r="E280" t="s" s="2">
@@ -37902,10 +37912,10 @@
       </c>
       <c r="F280" s="2"/>
       <c r="G280" t="s" s="2">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="H280" t="s" s="2">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="I280" t="s" s="2">
         <v>73</v>
@@ -37917,13 +37927,13 @@
         <v>73</v>
       </c>
       <c r="L280" t="s" s="2">
-        <v>76</v>
+        <v>813</v>
       </c>
       <c r="M280" t="s" s="2">
-        <v>853</v>
+        <v>848</v>
       </c>
       <c r="N280" t="s" s="2">
-        <v>562</v>
+        <v>848</v>
       </c>
       <c r="O280" s="2"/>
       <c r="P280" s="2"/>
@@ -37974,13 +37984,13 @@
         <v>73</v>
       </c>
       <c r="AG280" t="s" s="2">
-        <v>77</v>
+        <v>847</v>
       </c>
       <c r="AH280" t="s" s="2">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="AI280" t="s" s="2">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="AJ280" t="s" s="2">
         <v>73</v>
@@ -37991,13 +38001,13 @@
     </row>
     <row r="281">
       <c r="A281" t="s" s="2">
-        <v>850</v>
+        <v>842</v>
       </c>
       <c r="B281" t="s" s="2">
-        <v>854</v>
+        <v>849</v>
       </c>
       <c r="C281" t="s" s="2">
-        <v>854</v>
+        <v>849</v>
       </c>
       <c r="D281" s="2"/>
       <c r="E281" t="s" s="2">
@@ -38020,13 +38030,13 @@
         <v>73</v>
       </c>
       <c r="L281" t="s" s="2">
-        <v>522</v>
+        <v>89</v>
       </c>
       <c r="M281" t="s" s="2">
-        <v>855</v>
+        <v>850</v>
       </c>
       <c r="N281" t="s" s="2">
-        <v>855</v>
+        <v>850</v>
       </c>
       <c r="O281" s="2"/>
       <c r="P281" s="2"/>
@@ -38077,7 +38087,7 @@
         <v>73</v>
       </c>
       <c r="AG281" t="s" s="2">
-        <v>854</v>
+        <v>849</v>
       </c>
       <c r="AH281" t="s" s="2">
         <v>79</v>
@@ -38089,18 +38099,18 @@
         <v>73</v>
       </c>
       <c r="AK281" t="s" s="2">
-        <v>367</v>
+        <v>73</v>
       </c>
     </row>
     <row r="282">
       <c r="A282" t="s" s="2">
-        <v>850</v>
+        <v>842</v>
       </c>
       <c r="B282" t="s" s="2">
-        <v>856</v>
+        <v>851</v>
       </c>
       <c r="C282" t="s" s="2">
-        <v>856</v>
+        <v>851</v>
       </c>
       <c r="D282" s="2"/>
       <c r="E282" t="s" s="2">
@@ -38108,7 +38118,7 @@
       </c>
       <c r="F282" s="2"/>
       <c r="G282" t="s" s="2">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="H282" t="s" s="2">
         <v>79</v>
@@ -38126,10 +38136,10 @@
         <v>89</v>
       </c>
       <c r="M282" t="s" s="2">
-        <v>525</v>
+        <v>852</v>
       </c>
       <c r="N282" t="s" s="2">
-        <v>526</v>
+        <v>852</v>
       </c>
       <c r="O282" s="2"/>
       <c r="P282" s="2"/>
@@ -38180,10 +38190,10 @@
         <v>73</v>
       </c>
       <c r="AG282" t="s" s="2">
-        <v>371</v>
+        <v>851</v>
       </c>
       <c r="AH282" t="s" s="2">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="AI282" t="s" s="2">
         <v>79</v>
@@ -38197,17 +38207,17 @@
     </row>
     <row r="283">
       <c r="A283" t="s" s="2">
-        <v>850</v>
+        <v>853</v>
       </c>
       <c r="B283" t="s" s="2">
-        <v>857</v>
+        <v>853</v>
       </c>
       <c r="C283" t="s" s="2">
-        <v>857</v>
+        <v>853</v>
       </c>
       <c r="D283" s="2"/>
       <c r="E283" t="s" s="2">
-        <v>373</v>
+        <v>73</v>
       </c>
       <c r="F283" s="2"/>
       <c r="G283" t="s" s="2">
@@ -38226,17 +38236,15 @@
         <v>73</v>
       </c>
       <c r="L283" t="s" s="2">
-        <v>374</v>
+        <v>76</v>
       </c>
       <c r="M283" t="s" s="2">
-        <v>375</v>
+        <v>856</v>
       </c>
       <c r="N283" t="s" s="2">
-        <v>528</v>
-      </c>
-      <c r="O283" t="s" s="2">
-        <v>377</v>
-      </c>
+        <v>562</v>
+      </c>
+      <c r="O283" s="2"/>
       <c r="P283" s="2"/>
       <c r="Q283" t="s" s="2">
         <v>73</v>
@@ -38273,19 +38281,19 @@
         <v>73</v>
       </c>
       <c r="AC283" t="s" s="2">
-        <v>529</v>
+        <v>73</v>
       </c>
       <c r="AD283" t="s" s="2">
-        <v>530</v>
+        <v>73</v>
       </c>
       <c r="AE283" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AF283" t="s" s="2">
-        <v>531</v>
+        <v>73</v>
       </c>
       <c r="AG283" t="s" s="2">
-        <v>378</v>
+        <v>77</v>
       </c>
       <c r="AH283" t="s" s="2">
         <v>74</v>
@@ -38297,54 +38305,50 @@
         <v>73</v>
       </c>
       <c r="AK283" t="s" s="2">
-        <v>379</v>
+        <v>73</v>
       </c>
     </row>
     <row r="284">
       <c r="A284" t="s" s="2">
-        <v>850</v>
+        <v>853</v>
       </c>
       <c r="B284" t="s" s="2">
-        <v>858</v>
+        <v>857</v>
       </c>
       <c r="C284" t="s" s="2">
-        <v>858</v>
+        <v>857</v>
       </c>
       <c r="D284" s="2"/>
       <c r="E284" t="s" s="2">
-        <v>533</v>
+        <v>73</v>
       </c>
       <c r="F284" s="2"/>
       <c r="G284" t="s" s="2">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="H284" t="s" s="2">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="I284" t="s" s="2">
         <v>73</v>
       </c>
       <c r="J284" t="s" s="2">
-        <v>534</v>
+        <v>73</v>
       </c>
       <c r="K284" t="s" s="2">
-        <v>534</v>
+        <v>73</v>
       </c>
       <c r="L284" t="s" s="2">
-        <v>374</v>
+        <v>522</v>
       </c>
       <c r="M284" t="s" s="2">
-        <v>535</v>
+        <v>858</v>
       </c>
       <c r="N284" t="s" s="2">
-        <v>536</v>
-      </c>
-      <c r="O284" t="s" s="2">
-        <v>377</v>
-      </c>
-      <c r="P284" t="s" s="2">
-        <v>537</v>
-      </c>
+        <v>858</v>
+      </c>
+      <c r="O284" s="2"/>
+      <c r="P284" s="2"/>
       <c r="Q284" t="s" s="2">
         <v>73</v>
       </c>
@@ -38392,24 +38396,24 @@
         <v>73</v>
       </c>
       <c r="AG284" t="s" s="2">
-        <v>538</v>
+        <v>857</v>
       </c>
       <c r="AH284" t="s" s="2">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="AI284" t="s" s="2">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="AJ284" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AK284" t="s" s="2">
-        <v>379</v>
+        <v>367</v>
       </c>
     </row>
     <row r="285">
       <c r="A285" t="s" s="2">
-        <v>850</v>
+        <v>853</v>
       </c>
       <c r="B285" t="s" s="2">
         <v>859</v>
@@ -38423,7 +38427,7 @@
       </c>
       <c r="F285" s="2"/>
       <c r="G285" t="s" s="2">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="H285" t="s" s="2">
         <v>79</v>
@@ -38441,10 +38445,10 @@
         <v>89</v>
       </c>
       <c r="M285" t="s" s="2">
-        <v>860</v>
+        <v>525</v>
       </c>
       <c r="N285" t="s" s="2">
-        <v>860</v>
+        <v>526</v>
       </c>
       <c r="O285" s="2"/>
       <c r="P285" s="2"/>
@@ -38495,10 +38499,10 @@
         <v>73</v>
       </c>
       <c r="AG285" t="s" s="2">
-        <v>859</v>
+        <v>371</v>
       </c>
       <c r="AH285" t="s" s="2">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="AI285" t="s" s="2">
         <v>79</v>
@@ -38512,24 +38516,24 @@
     </row>
     <row r="286">
       <c r="A286" t="s" s="2">
-        <v>850</v>
+        <v>853</v>
       </c>
       <c r="B286" t="s" s="2">
-        <v>861</v>
+        <v>860</v>
       </c>
       <c r="C286" t="s" s="2">
-        <v>861</v>
+        <v>860</v>
       </c>
       <c r="D286" s="2"/>
       <c r="E286" t="s" s="2">
-        <v>73</v>
+        <v>373</v>
       </c>
       <c r="F286" s="2"/>
       <c r="G286" t="s" s="2">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="H286" t="s" s="2">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="I286" t="s" s="2">
         <v>73</v>
@@ -38541,15 +38545,17 @@
         <v>73</v>
       </c>
       <c r="L286" t="s" s="2">
-        <v>89</v>
+        <v>374</v>
       </c>
       <c r="M286" t="s" s="2">
-        <v>862</v>
+        <v>375</v>
       </c>
       <c r="N286" t="s" s="2">
-        <v>862</v>
-      </c>
-      <c r="O286" s="2"/>
+        <v>528</v>
+      </c>
+      <c r="O286" t="s" s="2">
+        <v>377</v>
+      </c>
       <c r="P286" s="2"/>
       <c r="Q286" t="s" s="2">
         <v>73</v>
@@ -38586,74 +38592,78 @@
         <v>73</v>
       </c>
       <c r="AC286" t="s" s="2">
-        <v>73</v>
+        <v>529</v>
       </c>
       <c r="AD286" t="s" s="2">
-        <v>73</v>
+        <v>530</v>
       </c>
       <c r="AE286" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AF286" t="s" s="2">
-        <v>73</v>
+        <v>531</v>
       </c>
       <c r="AG286" t="s" s="2">
-        <v>861</v>
+        <v>378</v>
       </c>
       <c r="AH286" t="s" s="2">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="AI286" t="s" s="2">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="AJ286" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AK286" t="s" s="2">
-        <v>73</v>
+        <v>379</v>
       </c>
     </row>
     <row r="287">
       <c r="A287" t="s" s="2">
-        <v>850</v>
+        <v>853</v>
       </c>
       <c r="B287" t="s" s="2">
-        <v>863</v>
+        <v>861</v>
       </c>
       <c r="C287" t="s" s="2">
-        <v>863</v>
+        <v>861</v>
       </c>
       <c r="D287" s="2"/>
       <c r="E287" t="s" s="2">
-        <v>73</v>
+        <v>533</v>
       </c>
       <c r="F287" s="2"/>
       <c r="G287" t="s" s="2">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="H287" t="s" s="2">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="I287" t="s" s="2">
         <v>73</v>
       </c>
       <c r="J287" t="s" s="2">
-        <v>73</v>
+        <v>534</v>
       </c>
       <c r="K287" t="s" s="2">
-        <v>73</v>
+        <v>534</v>
       </c>
       <c r="L287" t="s" s="2">
-        <v>522</v>
+        <v>374</v>
       </c>
       <c r="M287" t="s" s="2">
-        <v>864</v>
+        <v>535</v>
       </c>
       <c r="N287" t="s" s="2">
-        <v>864</v>
-      </c>
-      <c r="O287" s="2"/>
-      <c r="P287" s="2"/>
+        <v>536</v>
+      </c>
+      <c r="O287" t="s" s="2">
+        <v>377</v>
+      </c>
+      <c r="P287" t="s" s="2">
+        <v>537</v>
+      </c>
       <c r="Q287" t="s" s="2">
         <v>73</v>
       </c>
@@ -38701,30 +38711,30 @@
         <v>73</v>
       </c>
       <c r="AG287" t="s" s="2">
-        <v>863</v>
+        <v>538</v>
       </c>
       <c r="AH287" t="s" s="2">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="AI287" t="s" s="2">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="AJ287" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AK287" t="s" s="2">
-        <v>367</v>
+        <v>379</v>
       </c>
     </row>
     <row r="288">
       <c r="A288" t="s" s="2">
-        <v>850</v>
+        <v>853</v>
       </c>
       <c r="B288" t="s" s="2">
-        <v>865</v>
+        <v>862</v>
       </c>
       <c r="C288" t="s" s="2">
-        <v>865</v>
+        <v>862</v>
       </c>
       <c r="D288" s="2"/>
       <c r="E288" t="s" s="2">
@@ -38732,7 +38742,7 @@
       </c>
       <c r="F288" s="2"/>
       <c r="G288" t="s" s="2">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="H288" t="s" s="2">
         <v>79</v>
@@ -38750,10 +38760,10 @@
         <v>89</v>
       </c>
       <c r="M288" t="s" s="2">
-        <v>525</v>
+        <v>863</v>
       </c>
       <c r="N288" t="s" s="2">
-        <v>526</v>
+        <v>863</v>
       </c>
       <c r="O288" s="2"/>
       <c r="P288" s="2"/>
@@ -38804,10 +38814,10 @@
         <v>73</v>
       </c>
       <c r="AG288" t="s" s="2">
-        <v>371</v>
+        <v>862</v>
       </c>
       <c r="AH288" t="s" s="2">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="AI288" t="s" s="2">
         <v>79</v>
@@ -38821,24 +38831,24 @@
     </row>
     <row r="289">
       <c r="A289" t="s" s="2">
-        <v>850</v>
+        <v>853</v>
       </c>
       <c r="B289" t="s" s="2">
-        <v>866</v>
+        <v>864</v>
       </c>
       <c r="C289" t="s" s="2">
-        <v>866</v>
+        <v>864</v>
       </c>
       <c r="D289" s="2"/>
       <c r="E289" t="s" s="2">
-        <v>373</v>
+        <v>73</v>
       </c>
       <c r="F289" s="2"/>
       <c r="G289" t="s" s="2">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="H289" t="s" s="2">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="I289" t="s" s="2">
         <v>73</v>
@@ -38850,17 +38860,15 @@
         <v>73</v>
       </c>
       <c r="L289" t="s" s="2">
-        <v>374</v>
+        <v>89</v>
       </c>
       <c r="M289" t="s" s="2">
-        <v>375</v>
+        <v>865</v>
       </c>
       <c r="N289" t="s" s="2">
-        <v>528</v>
-      </c>
-      <c r="O289" t="s" s="2">
-        <v>377</v>
-      </c>
+        <v>865</v>
+      </c>
+      <c r="O289" s="2"/>
       <c r="P289" s="2"/>
       <c r="Q289" t="s" s="2">
         <v>73</v>
@@ -38897,78 +38905,74 @@
         <v>73</v>
       </c>
       <c r="AC289" t="s" s="2">
-        <v>529</v>
+        <v>73</v>
       </c>
       <c r="AD289" t="s" s="2">
-        <v>530</v>
+        <v>73</v>
       </c>
       <c r="AE289" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AF289" t="s" s="2">
-        <v>531</v>
+        <v>73</v>
       </c>
       <c r="AG289" t="s" s="2">
-        <v>378</v>
+        <v>864</v>
       </c>
       <c r="AH289" t="s" s="2">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="AI289" t="s" s="2">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="AJ289" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AK289" t="s" s="2">
-        <v>379</v>
+        <v>73</v>
       </c>
     </row>
     <row r="290">
       <c r="A290" t="s" s="2">
-        <v>850</v>
+        <v>853</v>
       </c>
       <c r="B290" t="s" s="2">
-        <v>867</v>
+        <v>866</v>
       </c>
       <c r="C290" t="s" s="2">
-        <v>867</v>
+        <v>866</v>
       </c>
       <c r="D290" s="2"/>
       <c r="E290" t="s" s="2">
-        <v>533</v>
+        <v>73</v>
       </c>
       <c r="F290" s="2"/>
       <c r="G290" t="s" s="2">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="H290" t="s" s="2">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="I290" t="s" s="2">
         <v>73</v>
       </c>
       <c r="J290" t="s" s="2">
-        <v>534</v>
+        <v>73</v>
       </c>
       <c r="K290" t="s" s="2">
-        <v>534</v>
+        <v>73</v>
       </c>
       <c r="L290" t="s" s="2">
-        <v>374</v>
+        <v>522</v>
       </c>
       <c r="M290" t="s" s="2">
-        <v>535</v>
+        <v>867</v>
       </c>
       <c r="N290" t="s" s="2">
-        <v>536</v>
-      </c>
-      <c r="O290" t="s" s="2">
-        <v>377</v>
-      </c>
-      <c r="P290" t="s" s="2">
-        <v>537</v>
-      </c>
+        <v>867</v>
+      </c>
+      <c r="O290" s="2"/>
+      <c r="P290" s="2"/>
       <c r="Q290" t="s" s="2">
         <v>73</v>
       </c>
@@ -39016,24 +39020,24 @@
         <v>73</v>
       </c>
       <c r="AG290" t="s" s="2">
-        <v>538</v>
+        <v>866</v>
       </c>
       <c r="AH290" t="s" s="2">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="AI290" t="s" s="2">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="AJ290" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AK290" t="s" s="2">
-        <v>379</v>
+        <v>367</v>
       </c>
     </row>
     <row r="291">
       <c r="A291" t="s" s="2">
-        <v>850</v>
+        <v>853</v>
       </c>
       <c r="B291" t="s" s="2">
         <v>868</v>
@@ -39047,7 +39051,7 @@
       </c>
       <c r="F291" s="2"/>
       <c r="G291" t="s" s="2">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="H291" t="s" s="2">
         <v>79</v>
@@ -39065,10 +39069,10 @@
         <v>89</v>
       </c>
       <c r="M291" t="s" s="2">
-        <v>869</v>
+        <v>525</v>
       </c>
       <c r="N291" t="s" s="2">
-        <v>869</v>
+        <v>526</v>
       </c>
       <c r="O291" s="2"/>
       <c r="P291" s="2"/>
@@ -39119,10 +39123,10 @@
         <v>73</v>
       </c>
       <c r="AG291" t="s" s="2">
-        <v>868</v>
+        <v>371</v>
       </c>
       <c r="AH291" t="s" s="2">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="AI291" t="s" s="2">
         <v>79</v>
@@ -39136,24 +39140,24 @@
     </row>
     <row r="292">
       <c r="A292" t="s" s="2">
-        <v>850</v>
+        <v>853</v>
       </c>
       <c r="B292" t="s" s="2">
-        <v>870</v>
+        <v>869</v>
       </c>
       <c r="C292" t="s" s="2">
-        <v>870</v>
+        <v>869</v>
       </c>
       <c r="D292" s="2"/>
       <c r="E292" t="s" s="2">
-        <v>73</v>
+        <v>373</v>
       </c>
       <c r="F292" s="2"/>
       <c r="G292" t="s" s="2">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="H292" t="s" s="2">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="I292" t="s" s="2">
         <v>73</v>
@@ -39165,15 +39169,17 @@
         <v>73</v>
       </c>
       <c r="L292" t="s" s="2">
-        <v>89</v>
+        <v>374</v>
       </c>
       <c r="M292" t="s" s="2">
-        <v>871</v>
+        <v>375</v>
       </c>
       <c r="N292" t="s" s="2">
-        <v>871</v>
-      </c>
-      <c r="O292" s="2"/>
+        <v>528</v>
+      </c>
+      <c r="O292" t="s" s="2">
+        <v>377</v>
+      </c>
       <c r="P292" s="2"/>
       <c r="Q292" t="s" s="2">
         <v>73</v>
@@ -39210,74 +39216,78 @@
         <v>73</v>
       </c>
       <c r="AC292" t="s" s="2">
-        <v>73</v>
+        <v>529</v>
       </c>
       <c r="AD292" t="s" s="2">
-        <v>73</v>
+        <v>530</v>
       </c>
       <c r="AE292" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AF292" t="s" s="2">
-        <v>73</v>
+        <v>531</v>
       </c>
       <c r="AG292" t="s" s="2">
-        <v>870</v>
+        <v>378</v>
       </c>
       <c r="AH292" t="s" s="2">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="AI292" t="s" s="2">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="AJ292" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AK292" t="s" s="2">
-        <v>73</v>
+        <v>379</v>
       </c>
     </row>
     <row r="293">
       <c r="A293" t="s" s="2">
-        <v>850</v>
+        <v>853</v>
       </c>
       <c r="B293" t="s" s="2">
-        <v>872</v>
+        <v>870</v>
       </c>
       <c r="C293" t="s" s="2">
-        <v>872</v>
+        <v>870</v>
       </c>
       <c r="D293" s="2"/>
       <c r="E293" t="s" s="2">
-        <v>73</v>
+        <v>533</v>
       </c>
       <c r="F293" s="2"/>
       <c r="G293" t="s" s="2">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="H293" t="s" s="2">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="I293" t="s" s="2">
         <v>73</v>
       </c>
       <c r="J293" t="s" s="2">
-        <v>73</v>
+        <v>534</v>
       </c>
       <c r="K293" t="s" s="2">
-        <v>73</v>
+        <v>534</v>
       </c>
       <c r="L293" t="s" s="2">
-        <v>89</v>
+        <v>374</v>
       </c>
       <c r="M293" t="s" s="2">
-        <v>873</v>
+        <v>535</v>
       </c>
       <c r="N293" t="s" s="2">
-        <v>873</v>
-      </c>
-      <c r="O293" s="2"/>
-      <c r="P293" s="2"/>
+        <v>536</v>
+      </c>
+      <c r="O293" t="s" s="2">
+        <v>377</v>
+      </c>
+      <c r="P293" t="s" s="2">
+        <v>537</v>
+      </c>
       <c r="Q293" t="s" s="2">
         <v>73</v>
       </c>
@@ -39325,30 +39335,30 @@
         <v>73</v>
       </c>
       <c r="AG293" t="s" s="2">
-        <v>872</v>
+        <v>538</v>
       </c>
       <c r="AH293" t="s" s="2">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="AI293" t="s" s="2">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="AJ293" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AK293" t="s" s="2">
-        <v>73</v>
+        <v>379</v>
       </c>
     </row>
     <row r="294">
       <c r="A294" t="s" s="2">
-        <v>850</v>
+        <v>853</v>
       </c>
       <c r="B294" t="s" s="2">
-        <v>874</v>
+        <v>871</v>
       </c>
       <c r="C294" t="s" s="2">
-        <v>874</v>
+        <v>871</v>
       </c>
       <c r="D294" s="2"/>
       <c r="E294" t="s" s="2">
@@ -39374,10 +39384,10 @@
         <v>89</v>
       </c>
       <c r="M294" t="s" s="2">
-        <v>875</v>
+        <v>872</v>
       </c>
       <c r="N294" t="s" s="2">
-        <v>875</v>
+        <v>872</v>
       </c>
       <c r="O294" s="2"/>
       <c r="P294" s="2"/>
@@ -39428,7 +39438,7 @@
         <v>73</v>
       </c>
       <c r="AG294" t="s" s="2">
-        <v>874</v>
+        <v>871</v>
       </c>
       <c r="AH294" t="s" s="2">
         <v>79</v>
@@ -39445,13 +39455,13 @@
     </row>
     <row r="295">
       <c r="A295" t="s" s="2">
-        <v>850</v>
+        <v>853</v>
       </c>
       <c r="B295" t="s" s="2">
-        <v>876</v>
+        <v>873</v>
       </c>
       <c r="C295" t="s" s="2">
-        <v>876</v>
+        <v>873</v>
       </c>
       <c r="D295" s="2"/>
       <c r="E295" t="s" s="2">
@@ -39474,13 +39484,13 @@
         <v>73</v>
       </c>
       <c r="L295" t="s" s="2">
-        <v>522</v>
+        <v>89</v>
       </c>
       <c r="M295" t="s" s="2">
-        <v>877</v>
+        <v>874</v>
       </c>
       <c r="N295" t="s" s="2">
-        <v>877</v>
+        <v>874</v>
       </c>
       <c r="O295" s="2"/>
       <c r="P295" s="2"/>
@@ -39531,7 +39541,7 @@
         <v>73</v>
       </c>
       <c r="AG295" t="s" s="2">
-        <v>876</v>
+        <v>873</v>
       </c>
       <c r="AH295" t="s" s="2">
         <v>79</v>
@@ -39543,18 +39553,18 @@
         <v>73</v>
       </c>
       <c r="AK295" t="s" s="2">
-        <v>367</v>
+        <v>73</v>
       </c>
     </row>
     <row r="296">
       <c r="A296" t="s" s="2">
-        <v>850</v>
+        <v>853</v>
       </c>
       <c r="B296" t="s" s="2">
-        <v>878</v>
+        <v>875</v>
       </c>
       <c r="C296" t="s" s="2">
-        <v>878</v>
+        <v>875</v>
       </c>
       <c r="D296" s="2"/>
       <c r="E296" t="s" s="2">
@@ -39562,7 +39572,7 @@
       </c>
       <c r="F296" s="2"/>
       <c r="G296" t="s" s="2">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="H296" t="s" s="2">
         <v>79</v>
@@ -39580,10 +39590,10 @@
         <v>89</v>
       </c>
       <c r="M296" t="s" s="2">
-        <v>525</v>
+        <v>876</v>
       </c>
       <c r="N296" t="s" s="2">
-        <v>526</v>
+        <v>876</v>
       </c>
       <c r="O296" s="2"/>
       <c r="P296" s="2"/>
@@ -39634,10 +39644,10 @@
         <v>73</v>
       </c>
       <c r="AG296" t="s" s="2">
-        <v>371</v>
+        <v>875</v>
       </c>
       <c r="AH296" t="s" s="2">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="AI296" t="s" s="2">
         <v>79</v>
@@ -39651,24 +39661,24 @@
     </row>
     <row r="297">
       <c r="A297" t="s" s="2">
-        <v>850</v>
+        <v>853</v>
       </c>
       <c r="B297" t="s" s="2">
-        <v>879</v>
+        <v>877</v>
       </c>
       <c r="C297" t="s" s="2">
-        <v>879</v>
+        <v>877</v>
       </c>
       <c r="D297" s="2"/>
       <c r="E297" t="s" s="2">
-        <v>373</v>
+        <v>73</v>
       </c>
       <c r="F297" s="2"/>
       <c r="G297" t="s" s="2">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="H297" t="s" s="2">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="I297" t="s" s="2">
         <v>73</v>
@@ -39680,17 +39690,15 @@
         <v>73</v>
       </c>
       <c r="L297" t="s" s="2">
-        <v>374</v>
+        <v>89</v>
       </c>
       <c r="M297" t="s" s="2">
-        <v>375</v>
+        <v>878</v>
       </c>
       <c r="N297" t="s" s="2">
-        <v>528</v>
-      </c>
-      <c r="O297" t="s" s="2">
-        <v>377</v>
-      </c>
+        <v>878</v>
+      </c>
+      <c r="O297" s="2"/>
       <c r="P297" s="2"/>
       <c r="Q297" t="s" s="2">
         <v>73</v>
@@ -39727,78 +39735,74 @@
         <v>73</v>
       </c>
       <c r="AC297" t="s" s="2">
-        <v>529</v>
+        <v>73</v>
       </c>
       <c r="AD297" t="s" s="2">
-        <v>530</v>
+        <v>73</v>
       </c>
       <c r="AE297" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AF297" t="s" s="2">
-        <v>531</v>
+        <v>73</v>
       </c>
       <c r="AG297" t="s" s="2">
-        <v>378</v>
+        <v>877</v>
       </c>
       <c r="AH297" t="s" s="2">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="AI297" t="s" s="2">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="AJ297" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AK297" t="s" s="2">
-        <v>379</v>
+        <v>73</v>
       </c>
     </row>
     <row r="298">
       <c r="A298" t="s" s="2">
-        <v>850</v>
+        <v>853</v>
       </c>
       <c r="B298" t="s" s="2">
-        <v>880</v>
+        <v>879</v>
       </c>
       <c r="C298" t="s" s="2">
-        <v>880</v>
+        <v>879</v>
       </c>
       <c r="D298" s="2"/>
       <c r="E298" t="s" s="2">
-        <v>533</v>
+        <v>73</v>
       </c>
       <c r="F298" s="2"/>
       <c r="G298" t="s" s="2">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="H298" t="s" s="2">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="I298" t="s" s="2">
         <v>73</v>
       </c>
       <c r="J298" t="s" s="2">
-        <v>534</v>
+        <v>73</v>
       </c>
       <c r="K298" t="s" s="2">
-        <v>534</v>
+        <v>73</v>
       </c>
       <c r="L298" t="s" s="2">
-        <v>374</v>
+        <v>522</v>
       </c>
       <c r="M298" t="s" s="2">
-        <v>535</v>
+        <v>880</v>
       </c>
       <c r="N298" t="s" s="2">
-        <v>536</v>
-      </c>
-      <c r="O298" t="s" s="2">
-        <v>377</v>
-      </c>
-      <c r="P298" t="s" s="2">
-        <v>537</v>
-      </c>
+        <v>880</v>
+      </c>
+      <c r="O298" s="2"/>
+      <c r="P298" s="2"/>
       <c r="Q298" t="s" s="2">
         <v>73</v>
       </c>
@@ -39846,24 +39850,24 @@
         <v>73</v>
       </c>
       <c r="AG298" t="s" s="2">
-        <v>538</v>
+        <v>879</v>
       </c>
       <c r="AH298" t="s" s="2">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="AI298" t="s" s="2">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="AJ298" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AK298" t="s" s="2">
-        <v>379</v>
+        <v>367</v>
       </c>
     </row>
     <row r="299">
       <c r="A299" t="s" s="2">
-        <v>850</v>
+        <v>853</v>
       </c>
       <c r="B299" t="s" s="2">
         <v>881</v>
@@ -39877,7 +39881,7 @@
       </c>
       <c r="F299" s="2"/>
       <c r="G299" t="s" s="2">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="H299" t="s" s="2">
         <v>79</v>
@@ -39892,13 +39896,13 @@
         <v>73</v>
       </c>
       <c r="L299" t="s" s="2">
-        <v>522</v>
+        <v>89</v>
       </c>
       <c r="M299" t="s" s="2">
-        <v>882</v>
+        <v>525</v>
       </c>
       <c r="N299" t="s" s="2">
-        <v>882</v>
+        <v>526</v>
       </c>
       <c r="O299" s="2"/>
       <c r="P299" s="2"/>
@@ -39949,10 +39953,10 @@
         <v>73</v>
       </c>
       <c r="AG299" t="s" s="2">
-        <v>881</v>
+        <v>371</v>
       </c>
       <c r="AH299" t="s" s="2">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="AI299" t="s" s="2">
         <v>79</v>
@@ -39961,29 +39965,29 @@
         <v>73</v>
       </c>
       <c r="AK299" t="s" s="2">
-        <v>367</v>
+        <v>73</v>
       </c>
     </row>
     <row r="300">
       <c r="A300" t="s" s="2">
-        <v>850</v>
+        <v>853</v>
       </c>
       <c r="B300" t="s" s="2">
-        <v>883</v>
+        <v>882</v>
       </c>
       <c r="C300" t="s" s="2">
-        <v>883</v>
+        <v>882</v>
       </c>
       <c r="D300" s="2"/>
       <c r="E300" t="s" s="2">
-        <v>73</v>
+        <v>373</v>
       </c>
       <c r="F300" s="2"/>
       <c r="G300" t="s" s="2">
         <v>74</v>
       </c>
       <c r="H300" t="s" s="2">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="I300" t="s" s="2">
         <v>73</v>
@@ -39995,15 +39999,17 @@
         <v>73</v>
       </c>
       <c r="L300" t="s" s="2">
-        <v>89</v>
+        <v>374</v>
       </c>
       <c r="M300" t="s" s="2">
-        <v>525</v>
+        <v>375</v>
       </c>
       <c r="N300" t="s" s="2">
-        <v>526</v>
-      </c>
-      <c r="O300" s="2"/>
+        <v>528</v>
+      </c>
+      <c r="O300" t="s" s="2">
+        <v>377</v>
+      </c>
       <c r="P300" s="2"/>
       <c r="Q300" t="s" s="2">
         <v>73</v>
@@ -40040,46 +40046,46 @@
         <v>73</v>
       </c>
       <c r="AC300" t="s" s="2">
-        <v>73</v>
+        <v>529</v>
       </c>
       <c r="AD300" t="s" s="2">
-        <v>73</v>
+        <v>530</v>
       </c>
       <c r="AE300" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AF300" t="s" s="2">
-        <v>73</v>
+        <v>531</v>
       </c>
       <c r="AG300" t="s" s="2">
-        <v>371</v>
+        <v>378</v>
       </c>
       <c r="AH300" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AI300" t="s" s="2">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="AJ300" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AK300" t="s" s="2">
-        <v>73</v>
+        <v>379</v>
       </c>
     </row>
     <row r="301">
       <c r="A301" t="s" s="2">
-        <v>850</v>
+        <v>853</v>
       </c>
       <c r="B301" t="s" s="2">
-        <v>884</v>
+        <v>883</v>
       </c>
       <c r="C301" t="s" s="2">
-        <v>884</v>
+        <v>883</v>
       </c>
       <c r="D301" s="2"/>
       <c r="E301" t="s" s="2">
-        <v>373</v>
+        <v>533</v>
       </c>
       <c r="F301" s="2"/>
       <c r="G301" t="s" s="2">
@@ -40092,24 +40098,26 @@
         <v>73</v>
       </c>
       <c r="J301" t="s" s="2">
-        <v>73</v>
+        <v>534</v>
       </c>
       <c r="K301" t="s" s="2">
-        <v>73</v>
+        <v>534</v>
       </c>
       <c r="L301" t="s" s="2">
         <v>374</v>
       </c>
       <c r="M301" t="s" s="2">
-        <v>375</v>
+        <v>535</v>
       </c>
       <c r="N301" t="s" s="2">
-        <v>528</v>
+        <v>536</v>
       </c>
       <c r="O301" t="s" s="2">
         <v>377</v>
       </c>
-      <c r="P301" s="2"/>
+      <c r="P301" t="s" s="2">
+        <v>537</v>
+      </c>
       <c r="Q301" t="s" s="2">
         <v>73</v>
       </c>
@@ -40145,19 +40153,19 @@
         <v>73</v>
       </c>
       <c r="AC301" t="s" s="2">
-        <v>529</v>
+        <v>73</v>
       </c>
       <c r="AD301" t="s" s="2">
-        <v>530</v>
+        <v>73</v>
       </c>
       <c r="AE301" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AF301" t="s" s="2">
-        <v>531</v>
+        <v>73</v>
       </c>
       <c r="AG301" t="s" s="2">
-        <v>378</v>
+        <v>538</v>
       </c>
       <c r="AH301" t="s" s="2">
         <v>74</v>
@@ -40174,49 +40182,45 @@
     </row>
     <row r="302">
       <c r="A302" t="s" s="2">
-        <v>850</v>
+        <v>853</v>
       </c>
       <c r="B302" t="s" s="2">
-        <v>885</v>
+        <v>884</v>
       </c>
       <c r="C302" t="s" s="2">
-        <v>885</v>
+        <v>884</v>
       </c>
       <c r="D302" s="2"/>
       <c r="E302" t="s" s="2">
-        <v>533</v>
+        <v>73</v>
       </c>
       <c r="F302" s="2"/>
       <c r="G302" t="s" s="2">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="H302" t="s" s="2">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="I302" t="s" s="2">
         <v>73</v>
       </c>
       <c r="J302" t="s" s="2">
-        <v>534</v>
+        <v>73</v>
       </c>
       <c r="K302" t="s" s="2">
-        <v>534</v>
+        <v>73</v>
       </c>
       <c r="L302" t="s" s="2">
-        <v>374</v>
+        <v>522</v>
       </c>
       <c r="M302" t="s" s="2">
-        <v>535</v>
+        <v>885</v>
       </c>
       <c r="N302" t="s" s="2">
-        <v>536</v>
-      </c>
-      <c r="O302" t="s" s="2">
-        <v>377</v>
-      </c>
-      <c r="P302" t="s" s="2">
-        <v>537</v>
-      </c>
+        <v>885</v>
+      </c>
+      <c r="O302" s="2"/>
+      <c r="P302" s="2"/>
       <c r="Q302" t="s" s="2">
         <v>73</v>
       </c>
@@ -40264,24 +40268,24 @@
         <v>73</v>
       </c>
       <c r="AG302" t="s" s="2">
-        <v>538</v>
+        <v>884</v>
       </c>
       <c r="AH302" t="s" s="2">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="AI302" t="s" s="2">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="AJ302" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AK302" t="s" s="2">
-        <v>379</v>
+        <v>367</v>
       </c>
     </row>
     <row r="303">
       <c r="A303" t="s" s="2">
-        <v>850</v>
+        <v>853</v>
       </c>
       <c r="B303" t="s" s="2">
         <v>886</v>
@@ -40295,7 +40299,7 @@
       </c>
       <c r="F303" s="2"/>
       <c r="G303" t="s" s="2">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="H303" t="s" s="2">
         <v>79</v>
@@ -40313,10 +40317,10 @@
         <v>89</v>
       </c>
       <c r="M303" t="s" s="2">
-        <v>887</v>
+        <v>525</v>
       </c>
       <c r="N303" t="s" s="2">
-        <v>887</v>
+        <v>526</v>
       </c>
       <c r="O303" s="2"/>
       <c r="P303" s="2"/>
@@ -40367,10 +40371,10 @@
         <v>73</v>
       </c>
       <c r="AG303" t="s" s="2">
-        <v>886</v>
+        <v>371</v>
       </c>
       <c r="AH303" t="s" s="2">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="AI303" t="s" s="2">
         <v>79</v>
@@ -40384,24 +40388,24 @@
     </row>
     <row r="304">
       <c r="A304" t="s" s="2">
-        <v>850</v>
+        <v>853</v>
       </c>
       <c r="B304" t="s" s="2">
-        <v>888</v>
+        <v>887</v>
       </c>
       <c r="C304" t="s" s="2">
-        <v>888</v>
+        <v>887</v>
       </c>
       <c r="D304" s="2"/>
       <c r="E304" t="s" s="2">
-        <v>73</v>
+        <v>373</v>
       </c>
       <c r="F304" s="2"/>
       <c r="G304" t="s" s="2">
         <v>74</v>
       </c>
       <c r="H304" t="s" s="2">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="I304" t="s" s="2">
         <v>73</v>
@@ -40413,15 +40417,17 @@
         <v>73</v>
       </c>
       <c r="L304" t="s" s="2">
-        <v>522</v>
+        <v>374</v>
       </c>
       <c r="M304" t="s" s="2">
-        <v>889</v>
+        <v>375</v>
       </c>
       <c r="N304" t="s" s="2">
-        <v>889</v>
-      </c>
-      <c r="O304" s="2"/>
+        <v>528</v>
+      </c>
+      <c r="O304" t="s" s="2">
+        <v>377</v>
+      </c>
       <c r="P304" s="2"/>
       <c r="Q304" t="s" s="2">
         <v>73</v>
@@ -40458,74 +40464,78 @@
         <v>73</v>
       </c>
       <c r="AC304" t="s" s="2">
-        <v>73</v>
+        <v>529</v>
       </c>
       <c r="AD304" t="s" s="2">
-        <v>73</v>
+        <v>530</v>
       </c>
       <c r="AE304" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AF304" t="s" s="2">
-        <v>73</v>
+        <v>531</v>
       </c>
       <c r="AG304" t="s" s="2">
-        <v>888</v>
+        <v>378</v>
       </c>
       <c r="AH304" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AI304" t="s" s="2">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="AJ304" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AK304" t="s" s="2">
-        <v>367</v>
+        <v>379</v>
       </c>
     </row>
     <row r="305">
       <c r="A305" t="s" s="2">
-        <v>850</v>
+        <v>853</v>
       </c>
       <c r="B305" t="s" s="2">
-        <v>890</v>
+        <v>888</v>
       </c>
       <c r="C305" t="s" s="2">
-        <v>890</v>
+        <v>888</v>
       </c>
       <c r="D305" s="2"/>
       <c r="E305" t="s" s="2">
-        <v>73</v>
+        <v>533</v>
       </c>
       <c r="F305" s="2"/>
       <c r="G305" t="s" s="2">
         <v>74</v>
       </c>
       <c r="H305" t="s" s="2">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="I305" t="s" s="2">
         <v>73</v>
       </c>
       <c r="J305" t="s" s="2">
-        <v>73</v>
+        <v>534</v>
       </c>
       <c r="K305" t="s" s="2">
-        <v>73</v>
+        <v>534</v>
       </c>
       <c r="L305" t="s" s="2">
-        <v>89</v>
+        <v>374</v>
       </c>
       <c r="M305" t="s" s="2">
-        <v>525</v>
+        <v>535</v>
       </c>
       <c r="N305" t="s" s="2">
-        <v>526</v>
-      </c>
-      <c r="O305" s="2"/>
-      <c r="P305" s="2"/>
+        <v>536</v>
+      </c>
+      <c r="O305" t="s" s="2">
+        <v>377</v>
+      </c>
+      <c r="P305" t="s" s="2">
+        <v>537</v>
+      </c>
       <c r="Q305" t="s" s="2">
         <v>73</v>
       </c>
@@ -40573,41 +40583,41 @@
         <v>73</v>
       </c>
       <c r="AG305" t="s" s="2">
-        <v>371</v>
+        <v>538</v>
       </c>
       <c r="AH305" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AI305" t="s" s="2">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="AJ305" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AK305" t="s" s="2">
-        <v>73</v>
+        <v>379</v>
       </c>
     </row>
     <row r="306">
       <c r="A306" t="s" s="2">
-        <v>850</v>
+        <v>853</v>
       </c>
       <c r="B306" t="s" s="2">
-        <v>891</v>
+        <v>889</v>
       </c>
       <c r="C306" t="s" s="2">
-        <v>891</v>
+        <v>889</v>
       </c>
       <c r="D306" s="2"/>
       <c r="E306" t="s" s="2">
-        <v>373</v>
+        <v>73</v>
       </c>
       <c r="F306" s="2"/>
       <c r="G306" t="s" s="2">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="H306" t="s" s="2">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="I306" t="s" s="2">
         <v>73</v>
@@ -40619,17 +40629,15 @@
         <v>73</v>
       </c>
       <c r="L306" t="s" s="2">
-        <v>374</v>
+        <v>89</v>
       </c>
       <c r="M306" t="s" s="2">
-        <v>375</v>
+        <v>890</v>
       </c>
       <c r="N306" t="s" s="2">
-        <v>528</v>
-      </c>
-      <c r="O306" t="s" s="2">
-        <v>377</v>
-      </c>
+        <v>890</v>
+      </c>
+      <c r="O306" s="2"/>
       <c r="P306" s="2"/>
       <c r="Q306" t="s" s="2">
         <v>73</v>
@@ -40666,78 +40674,74 @@
         <v>73</v>
       </c>
       <c r="AC306" t="s" s="2">
-        <v>529</v>
+        <v>73</v>
       </c>
       <c r="AD306" t="s" s="2">
-        <v>530</v>
+        <v>73</v>
       </c>
       <c r="AE306" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AF306" t="s" s="2">
-        <v>531</v>
+        <v>73</v>
       </c>
       <c r="AG306" t="s" s="2">
-        <v>378</v>
+        <v>889</v>
       </c>
       <c r="AH306" t="s" s="2">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="AI306" t="s" s="2">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="AJ306" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AK306" t="s" s="2">
-        <v>379</v>
+        <v>73</v>
       </c>
     </row>
     <row r="307">
       <c r="A307" t="s" s="2">
-        <v>850</v>
+        <v>853</v>
       </c>
       <c r="B307" t="s" s="2">
-        <v>892</v>
+        <v>891</v>
       </c>
       <c r="C307" t="s" s="2">
-        <v>892</v>
+        <v>891</v>
       </c>
       <c r="D307" s="2"/>
       <c r="E307" t="s" s="2">
-        <v>533</v>
+        <v>73</v>
       </c>
       <c r="F307" s="2"/>
       <c r="G307" t="s" s="2">
         <v>74</v>
       </c>
       <c r="H307" t="s" s="2">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="I307" t="s" s="2">
         <v>73</v>
       </c>
       <c r="J307" t="s" s="2">
-        <v>534</v>
+        <v>73</v>
       </c>
       <c r="K307" t="s" s="2">
-        <v>534</v>
+        <v>73</v>
       </c>
       <c r="L307" t="s" s="2">
-        <v>374</v>
+        <v>522</v>
       </c>
       <c r="M307" t="s" s="2">
-        <v>535</v>
+        <v>892</v>
       </c>
       <c r="N307" t="s" s="2">
-        <v>536</v>
-      </c>
-      <c r="O307" t="s" s="2">
-        <v>377</v>
-      </c>
-      <c r="P307" t="s" s="2">
-        <v>537</v>
-      </c>
+        <v>892</v>
+      </c>
+      <c r="O307" s="2"/>
+      <c r="P307" s="2"/>
       <c r="Q307" t="s" s="2">
         <v>73</v>
       </c>
@@ -40785,24 +40789,24 @@
         <v>73</v>
       </c>
       <c r="AG307" t="s" s="2">
-        <v>538</v>
+        <v>891</v>
       </c>
       <c r="AH307" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AI307" t="s" s="2">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="AJ307" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AK307" t="s" s="2">
-        <v>379</v>
+        <v>367</v>
       </c>
     </row>
     <row r="308">
       <c r="A308" t="s" s="2">
-        <v>850</v>
+        <v>853</v>
       </c>
       <c r="B308" t="s" s="2">
         <v>893</v>
@@ -40816,7 +40820,7 @@
       </c>
       <c r="F308" s="2"/>
       <c r="G308" t="s" s="2">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="H308" t="s" s="2">
         <v>79</v>
@@ -40834,10 +40838,10 @@
         <v>89</v>
       </c>
       <c r="M308" t="s" s="2">
-        <v>894</v>
+        <v>525</v>
       </c>
       <c r="N308" t="s" s="2">
-        <v>894</v>
+        <v>526</v>
       </c>
       <c r="O308" s="2"/>
       <c r="P308" s="2"/>
@@ -40888,10 +40892,10 @@
         <v>73</v>
       </c>
       <c r="AG308" t="s" s="2">
-        <v>893</v>
+        <v>371</v>
       </c>
       <c r="AH308" t="s" s="2">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="AI308" t="s" s="2">
         <v>79</v>
@@ -40905,24 +40909,24 @@
     </row>
     <row r="309">
       <c r="A309" t="s" s="2">
-        <v>850</v>
+        <v>853</v>
       </c>
       <c r="B309" t="s" s="2">
-        <v>895</v>
+        <v>894</v>
       </c>
       <c r="C309" t="s" s="2">
-        <v>895</v>
+        <v>894</v>
       </c>
       <c r="D309" s="2"/>
       <c r="E309" t="s" s="2">
-        <v>73</v>
+        <v>373</v>
       </c>
       <c r="F309" s="2"/>
       <c r="G309" t="s" s="2">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="H309" t="s" s="2">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="I309" t="s" s="2">
         <v>73</v>
@@ -40934,15 +40938,17 @@
         <v>73</v>
       </c>
       <c r="L309" t="s" s="2">
-        <v>89</v>
+        <v>374</v>
       </c>
       <c r="M309" t="s" s="2">
-        <v>896</v>
+        <v>375</v>
       </c>
       <c r="N309" t="s" s="2">
-        <v>896</v>
-      </c>
-      <c r="O309" s="2"/>
+        <v>528</v>
+      </c>
+      <c r="O309" t="s" s="2">
+        <v>377</v>
+      </c>
       <c r="P309" s="2"/>
       <c r="Q309" t="s" s="2">
         <v>73</v>
@@ -40979,74 +40985,78 @@
         <v>73</v>
       </c>
       <c r="AC309" t="s" s="2">
-        <v>73</v>
+        <v>529</v>
       </c>
       <c r="AD309" t="s" s="2">
-        <v>73</v>
+        <v>530</v>
       </c>
       <c r="AE309" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AF309" t="s" s="2">
-        <v>73</v>
+        <v>531</v>
       </c>
       <c r="AG309" t="s" s="2">
-        <v>895</v>
+        <v>378</v>
       </c>
       <c r="AH309" t="s" s="2">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="AI309" t="s" s="2">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="AJ309" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AK309" t="s" s="2">
-        <v>73</v>
+        <v>379</v>
       </c>
     </row>
     <row r="310">
       <c r="A310" t="s" s="2">
-        <v>850</v>
+        <v>853</v>
       </c>
       <c r="B310" t="s" s="2">
-        <v>897</v>
+        <v>895</v>
       </c>
       <c r="C310" t="s" s="2">
-        <v>897</v>
+        <v>895</v>
       </c>
       <c r="D310" s="2"/>
       <c r="E310" t="s" s="2">
-        <v>73</v>
+        <v>533</v>
       </c>
       <c r="F310" s="2"/>
       <c r="G310" t="s" s="2">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="H310" t="s" s="2">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="I310" t="s" s="2">
         <v>73</v>
       </c>
       <c r="J310" t="s" s="2">
-        <v>73</v>
+        <v>534</v>
       </c>
       <c r="K310" t="s" s="2">
-        <v>73</v>
+        <v>534</v>
       </c>
       <c r="L310" t="s" s="2">
-        <v>522</v>
+        <v>374</v>
       </c>
       <c r="M310" t="s" s="2">
-        <v>898</v>
+        <v>535</v>
       </c>
       <c r="N310" t="s" s="2">
-        <v>898</v>
-      </c>
-      <c r="O310" s="2"/>
-      <c r="P310" s="2"/>
+        <v>536</v>
+      </c>
+      <c r="O310" t="s" s="2">
+        <v>377</v>
+      </c>
+      <c r="P310" t="s" s="2">
+        <v>537</v>
+      </c>
       <c r="Q310" t="s" s="2">
         <v>73</v>
       </c>
@@ -41094,30 +41104,30 @@
         <v>73</v>
       </c>
       <c r="AG310" t="s" s="2">
-        <v>897</v>
+        <v>538</v>
       </c>
       <c r="AH310" t="s" s="2">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="AI310" t="s" s="2">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="AJ310" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AK310" t="s" s="2">
-        <v>367</v>
+        <v>379</v>
       </c>
     </row>
     <row r="311">
       <c r="A311" t="s" s="2">
-        <v>850</v>
+        <v>853</v>
       </c>
       <c r="B311" t="s" s="2">
-        <v>899</v>
+        <v>896</v>
       </c>
       <c r="C311" t="s" s="2">
-        <v>899</v>
+        <v>896</v>
       </c>
       <c r="D311" s="2"/>
       <c r="E311" t="s" s="2">
@@ -41125,7 +41135,7 @@
       </c>
       <c r="F311" s="2"/>
       <c r="G311" t="s" s="2">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="H311" t="s" s="2">
         <v>79</v>
@@ -41143,10 +41153,10 @@
         <v>89</v>
       </c>
       <c r="M311" t="s" s="2">
-        <v>525</v>
+        <v>897</v>
       </c>
       <c r="N311" t="s" s="2">
-        <v>526</v>
+        <v>897</v>
       </c>
       <c r="O311" s="2"/>
       <c r="P311" s="2"/>
@@ -41197,10 +41207,10 @@
         <v>73</v>
       </c>
       <c r="AG311" t="s" s="2">
-        <v>371</v>
+        <v>896</v>
       </c>
       <c r="AH311" t="s" s="2">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="AI311" t="s" s="2">
         <v>79</v>
@@ -41214,24 +41224,24 @@
     </row>
     <row r="312">
       <c r="A312" t="s" s="2">
-        <v>850</v>
+        <v>853</v>
       </c>
       <c r="B312" t="s" s="2">
-        <v>900</v>
+        <v>898</v>
       </c>
       <c r="C312" t="s" s="2">
-        <v>900</v>
+        <v>898</v>
       </c>
       <c r="D312" s="2"/>
       <c r="E312" t="s" s="2">
-        <v>373</v>
+        <v>73</v>
       </c>
       <c r="F312" s="2"/>
       <c r="G312" t="s" s="2">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="H312" t="s" s="2">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="I312" t="s" s="2">
         <v>73</v>
@@ -41243,17 +41253,15 @@
         <v>73</v>
       </c>
       <c r="L312" t="s" s="2">
-        <v>374</v>
+        <v>89</v>
       </c>
       <c r="M312" t="s" s="2">
-        <v>375</v>
+        <v>899</v>
       </c>
       <c r="N312" t="s" s="2">
-        <v>528</v>
-      </c>
-      <c r="O312" t="s" s="2">
-        <v>377</v>
-      </c>
+        <v>899</v>
+      </c>
+      <c r="O312" s="2"/>
       <c r="P312" s="2"/>
       <c r="Q312" t="s" s="2">
         <v>73</v>
@@ -41290,78 +41298,74 @@
         <v>73</v>
       </c>
       <c r="AC312" t="s" s="2">
-        <v>529</v>
+        <v>73</v>
       </c>
       <c r="AD312" t="s" s="2">
-        <v>530</v>
+        <v>73</v>
       </c>
       <c r="AE312" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AF312" t="s" s="2">
-        <v>531</v>
+        <v>73</v>
       </c>
       <c r="AG312" t="s" s="2">
-        <v>378</v>
+        <v>898</v>
       </c>
       <c r="AH312" t="s" s="2">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="AI312" t="s" s="2">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="AJ312" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AK312" t="s" s="2">
-        <v>379</v>
+        <v>73</v>
       </c>
     </row>
     <row r="313">
       <c r="A313" t="s" s="2">
-        <v>850</v>
+        <v>853</v>
       </c>
       <c r="B313" t="s" s="2">
-        <v>901</v>
+        <v>900</v>
       </c>
       <c r="C313" t="s" s="2">
-        <v>901</v>
+        <v>900</v>
       </c>
       <c r="D313" s="2"/>
       <c r="E313" t="s" s="2">
-        <v>533</v>
+        <v>73</v>
       </c>
       <c r="F313" s="2"/>
       <c r="G313" t="s" s="2">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="H313" t="s" s="2">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="I313" t="s" s="2">
         <v>73</v>
       </c>
       <c r="J313" t="s" s="2">
-        <v>534</v>
+        <v>73</v>
       </c>
       <c r="K313" t="s" s="2">
-        <v>534</v>
+        <v>73</v>
       </c>
       <c r="L313" t="s" s="2">
-        <v>374</v>
+        <v>522</v>
       </c>
       <c r="M313" t="s" s="2">
-        <v>535</v>
+        <v>901</v>
       </c>
       <c r="N313" t="s" s="2">
-        <v>536</v>
-      </c>
-      <c r="O313" t="s" s="2">
-        <v>377</v>
-      </c>
-      <c r="P313" t="s" s="2">
-        <v>537</v>
-      </c>
+        <v>901</v>
+      </c>
+      <c r="O313" s="2"/>
+      <c r="P313" s="2"/>
       <c r="Q313" t="s" s="2">
         <v>73</v>
       </c>
@@ -41409,24 +41413,24 @@
         <v>73</v>
       </c>
       <c r="AG313" t="s" s="2">
-        <v>538</v>
+        <v>900</v>
       </c>
       <c r="AH313" t="s" s="2">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="AI313" t="s" s="2">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="AJ313" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AK313" t="s" s="2">
-        <v>379</v>
+        <v>367</v>
       </c>
     </row>
     <row r="314">
       <c r="A314" t="s" s="2">
-        <v>850</v>
+        <v>853</v>
       </c>
       <c r="B314" t="s" s="2">
         <v>902</v>
@@ -41440,7 +41444,7 @@
       </c>
       <c r="F314" s="2"/>
       <c r="G314" t="s" s="2">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="H314" t="s" s="2">
         <v>79</v>
@@ -41455,13 +41459,13 @@
         <v>73</v>
       </c>
       <c r="L314" t="s" s="2">
-        <v>522</v>
+        <v>89</v>
       </c>
       <c r="M314" t="s" s="2">
-        <v>903</v>
+        <v>525</v>
       </c>
       <c r="N314" t="s" s="2">
-        <v>903</v>
+        <v>526</v>
       </c>
       <c r="O314" s="2"/>
       <c r="P314" s="2"/>
@@ -41512,10 +41516,10 @@
         <v>73</v>
       </c>
       <c r="AG314" t="s" s="2">
-        <v>902</v>
+        <v>371</v>
       </c>
       <c r="AH314" t="s" s="2">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="AI314" t="s" s="2">
         <v>79</v>
@@ -41524,29 +41528,29 @@
         <v>73</v>
       </c>
       <c r="AK314" t="s" s="2">
-        <v>367</v>
+        <v>73</v>
       </c>
     </row>
     <row r="315">
       <c r="A315" t="s" s="2">
-        <v>850</v>
+        <v>853</v>
       </c>
       <c r="B315" t="s" s="2">
-        <v>904</v>
+        <v>903</v>
       </c>
       <c r="C315" t="s" s="2">
-        <v>904</v>
+        <v>903</v>
       </c>
       <c r="D315" s="2"/>
       <c r="E315" t="s" s="2">
-        <v>73</v>
+        <v>373</v>
       </c>
       <c r="F315" s="2"/>
       <c r="G315" t="s" s="2">
         <v>74</v>
       </c>
       <c r="H315" t="s" s="2">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="I315" t="s" s="2">
         <v>73</v>
@@ -41558,15 +41562,17 @@
         <v>73</v>
       </c>
       <c r="L315" t="s" s="2">
-        <v>89</v>
+        <v>374</v>
       </c>
       <c r="M315" t="s" s="2">
-        <v>525</v>
+        <v>375</v>
       </c>
       <c r="N315" t="s" s="2">
-        <v>526</v>
-      </c>
-      <c r="O315" s="2"/>
+        <v>528</v>
+      </c>
+      <c r="O315" t="s" s="2">
+        <v>377</v>
+      </c>
       <c r="P315" s="2"/>
       <c r="Q315" t="s" s="2">
         <v>73</v>
@@ -41603,46 +41609,46 @@
         <v>73</v>
       </c>
       <c r="AC315" t="s" s="2">
-        <v>73</v>
+        <v>529</v>
       </c>
       <c r="AD315" t="s" s="2">
-        <v>73</v>
+        <v>530</v>
       </c>
       <c r="AE315" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AF315" t="s" s="2">
-        <v>73</v>
+        <v>531</v>
       </c>
       <c r="AG315" t="s" s="2">
-        <v>371</v>
+        <v>378</v>
       </c>
       <c r="AH315" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AI315" t="s" s="2">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="AJ315" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AK315" t="s" s="2">
-        <v>73</v>
+        <v>379</v>
       </c>
     </row>
     <row r="316">
       <c r="A316" t="s" s="2">
-        <v>850</v>
+        <v>853</v>
       </c>
       <c r="B316" t="s" s="2">
-        <v>905</v>
+        <v>904</v>
       </c>
       <c r="C316" t="s" s="2">
-        <v>905</v>
+        <v>904</v>
       </c>
       <c r="D316" s="2"/>
       <c r="E316" t="s" s="2">
-        <v>373</v>
+        <v>533</v>
       </c>
       <c r="F316" s="2"/>
       <c r="G316" t="s" s="2">
@@ -41655,24 +41661,26 @@
         <v>73</v>
       </c>
       <c r="J316" t="s" s="2">
-        <v>73</v>
+        <v>534</v>
       </c>
       <c r="K316" t="s" s="2">
-        <v>73</v>
+        <v>534</v>
       </c>
       <c r="L316" t="s" s="2">
         <v>374</v>
       </c>
       <c r="M316" t="s" s="2">
-        <v>375</v>
+        <v>535</v>
       </c>
       <c r="N316" t="s" s="2">
-        <v>528</v>
+        <v>536</v>
       </c>
       <c r="O316" t="s" s="2">
         <v>377</v>
       </c>
-      <c r="P316" s="2"/>
+      <c r="P316" t="s" s="2">
+        <v>537</v>
+      </c>
       <c r="Q316" t="s" s="2">
         <v>73</v>
       </c>
@@ -41708,19 +41716,19 @@
         <v>73</v>
       </c>
       <c r="AC316" t="s" s="2">
-        <v>529</v>
+        <v>73</v>
       </c>
       <c r="AD316" t="s" s="2">
-        <v>530</v>
+        <v>73</v>
       </c>
       <c r="AE316" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AF316" t="s" s="2">
-        <v>531</v>
+        <v>73</v>
       </c>
       <c r="AG316" t="s" s="2">
-        <v>378</v>
+        <v>538</v>
       </c>
       <c r="AH316" t="s" s="2">
         <v>74</v>
@@ -41737,49 +41745,45 @@
     </row>
     <row r="317">
       <c r="A317" t="s" s="2">
-        <v>850</v>
+        <v>853</v>
       </c>
       <c r="B317" t="s" s="2">
-        <v>906</v>
+        <v>905</v>
       </c>
       <c r="C317" t="s" s="2">
-        <v>906</v>
+        <v>905</v>
       </c>
       <c r="D317" s="2"/>
       <c r="E317" t="s" s="2">
-        <v>533</v>
+        <v>73</v>
       </c>
       <c r="F317" s="2"/>
       <c r="G317" t="s" s="2">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="H317" t="s" s="2">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="I317" t="s" s="2">
         <v>73</v>
       </c>
       <c r="J317" t="s" s="2">
-        <v>534</v>
+        <v>73</v>
       </c>
       <c r="K317" t="s" s="2">
-        <v>534</v>
+        <v>73</v>
       </c>
       <c r="L317" t="s" s="2">
-        <v>374</v>
+        <v>522</v>
       </c>
       <c r="M317" t="s" s="2">
-        <v>535</v>
+        <v>906</v>
       </c>
       <c r="N317" t="s" s="2">
-        <v>536</v>
-      </c>
-      <c r="O317" t="s" s="2">
-        <v>377</v>
-      </c>
-      <c r="P317" t="s" s="2">
-        <v>537</v>
-      </c>
+        <v>906</v>
+      </c>
+      <c r="O317" s="2"/>
+      <c r="P317" s="2"/>
       <c r="Q317" t="s" s="2">
         <v>73</v>
       </c>
@@ -41827,24 +41831,24 @@
         <v>73</v>
       </c>
       <c r="AG317" t="s" s="2">
-        <v>538</v>
+        <v>905</v>
       </c>
       <c r="AH317" t="s" s="2">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="AI317" t="s" s="2">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="AJ317" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AK317" t="s" s="2">
-        <v>379</v>
+        <v>367</v>
       </c>
     </row>
     <row r="318">
       <c r="A318" t="s" s="2">
-        <v>850</v>
+        <v>853</v>
       </c>
       <c r="B318" t="s" s="2">
         <v>907</v>
@@ -41858,7 +41862,7 @@
       </c>
       <c r="F318" s="2"/>
       <c r="G318" t="s" s="2">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="H318" t="s" s="2">
         <v>79</v>
@@ -41873,13 +41877,13 @@
         <v>73</v>
       </c>
       <c r="L318" t="s" s="2">
-        <v>279</v>
+        <v>89</v>
       </c>
       <c r="M318" t="s" s="2">
-        <v>908</v>
+        <v>525</v>
       </c>
       <c r="N318" t="s" s="2">
-        <v>909</v>
+        <v>526</v>
       </c>
       <c r="O318" s="2"/>
       <c r="P318" s="2"/>
@@ -41930,10 +41934,10 @@
         <v>73</v>
       </c>
       <c r="AG318" t="s" s="2">
-        <v>907</v>
+        <v>371</v>
       </c>
       <c r="AH318" t="s" s="2">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="AI318" t="s" s="2">
         <v>79</v>
@@ -41947,24 +41951,24 @@
     </row>
     <row r="319">
       <c r="A319" t="s" s="2">
-        <v>850</v>
+        <v>853</v>
       </c>
       <c r="B319" t="s" s="2">
-        <v>910</v>
+        <v>908</v>
       </c>
       <c r="C319" t="s" s="2">
-        <v>910</v>
+        <v>908</v>
       </c>
       <c r="D319" s="2"/>
       <c r="E319" t="s" s="2">
-        <v>73</v>
+        <v>373</v>
       </c>
       <c r="F319" s="2"/>
       <c r="G319" t="s" s="2">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="H319" t="s" s="2">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="I319" t="s" s="2">
         <v>73</v>
@@ -41976,15 +41980,17 @@
         <v>73</v>
       </c>
       <c r="L319" t="s" s="2">
-        <v>522</v>
+        <v>374</v>
       </c>
       <c r="M319" t="s" s="2">
-        <v>911</v>
+        <v>375</v>
       </c>
       <c r="N319" t="s" s="2">
-        <v>912</v>
-      </c>
-      <c r="O319" s="2"/>
+        <v>528</v>
+      </c>
+      <c r="O319" t="s" s="2">
+        <v>377</v>
+      </c>
       <c r="P319" s="2"/>
       <c r="Q319" t="s" s="2">
         <v>73</v>
@@ -42021,74 +42027,78 @@
         <v>73</v>
       </c>
       <c r="AC319" t="s" s="2">
-        <v>73</v>
+        <v>529</v>
       </c>
       <c r="AD319" t="s" s="2">
-        <v>73</v>
+        <v>530</v>
       </c>
       <c r="AE319" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AF319" t="s" s="2">
-        <v>73</v>
+        <v>531</v>
       </c>
       <c r="AG319" t="s" s="2">
-        <v>910</v>
+        <v>378</v>
       </c>
       <c r="AH319" t="s" s="2">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="AI319" t="s" s="2">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="AJ319" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AK319" t="s" s="2">
-        <v>367</v>
+        <v>379</v>
       </c>
     </row>
     <row r="320">
       <c r="A320" t="s" s="2">
-        <v>850</v>
+        <v>853</v>
       </c>
       <c r="B320" t="s" s="2">
-        <v>913</v>
+        <v>909</v>
       </c>
       <c r="C320" t="s" s="2">
-        <v>913</v>
+        <v>909</v>
       </c>
       <c r="D320" s="2"/>
       <c r="E320" t="s" s="2">
-        <v>73</v>
+        <v>533</v>
       </c>
       <c r="F320" s="2"/>
       <c r="G320" t="s" s="2">
         <v>74</v>
       </c>
       <c r="H320" t="s" s="2">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="I320" t="s" s="2">
         <v>73</v>
       </c>
       <c r="J320" t="s" s="2">
-        <v>73</v>
+        <v>534</v>
       </c>
       <c r="K320" t="s" s="2">
-        <v>73</v>
+        <v>534</v>
       </c>
       <c r="L320" t="s" s="2">
-        <v>89</v>
+        <v>374</v>
       </c>
       <c r="M320" t="s" s="2">
-        <v>525</v>
+        <v>535</v>
       </c>
       <c r="N320" t="s" s="2">
-        <v>526</v>
-      </c>
-      <c r="O320" s="2"/>
-      <c r="P320" s="2"/>
+        <v>536</v>
+      </c>
+      <c r="O320" t="s" s="2">
+        <v>377</v>
+      </c>
+      <c r="P320" t="s" s="2">
+        <v>537</v>
+      </c>
       <c r="Q320" t="s" s="2">
         <v>73</v>
       </c>
@@ -42136,41 +42146,41 @@
         <v>73</v>
       </c>
       <c r="AG320" t="s" s="2">
-        <v>371</v>
+        <v>538</v>
       </c>
       <c r="AH320" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AI320" t="s" s="2">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="AJ320" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AK320" t="s" s="2">
-        <v>73</v>
+        <v>379</v>
       </c>
     </row>
     <row r="321">
       <c r="A321" t="s" s="2">
-        <v>850</v>
+        <v>853</v>
       </c>
       <c r="B321" t="s" s="2">
-        <v>914</v>
+        <v>910</v>
       </c>
       <c r="C321" t="s" s="2">
-        <v>914</v>
+        <v>910</v>
       </c>
       <c r="D321" s="2"/>
       <c r="E321" t="s" s="2">
-        <v>373</v>
+        <v>73</v>
       </c>
       <c r="F321" s="2"/>
       <c r="G321" t="s" s="2">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="H321" t="s" s="2">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="I321" t="s" s="2">
         <v>73</v>
@@ -42182,17 +42192,15 @@
         <v>73</v>
       </c>
       <c r="L321" t="s" s="2">
-        <v>374</v>
+        <v>279</v>
       </c>
       <c r="M321" t="s" s="2">
-        <v>375</v>
+        <v>911</v>
       </c>
       <c r="N321" t="s" s="2">
-        <v>528</v>
-      </c>
-      <c r="O321" t="s" s="2">
-        <v>377</v>
-      </c>
+        <v>912</v>
+      </c>
+      <c r="O321" s="2"/>
       <c r="P321" s="2"/>
       <c r="Q321" t="s" s="2">
         <v>73</v>
@@ -42229,78 +42237,74 @@
         <v>73</v>
       </c>
       <c r="AC321" t="s" s="2">
-        <v>529</v>
+        <v>73</v>
       </c>
       <c r="AD321" t="s" s="2">
-        <v>530</v>
+        <v>73</v>
       </c>
       <c r="AE321" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AF321" t="s" s="2">
-        <v>531</v>
+        <v>73</v>
       </c>
       <c r="AG321" t="s" s="2">
-        <v>378</v>
+        <v>910</v>
       </c>
       <c r="AH321" t="s" s="2">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="AI321" t="s" s="2">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="AJ321" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AK321" t="s" s="2">
-        <v>379</v>
+        <v>73</v>
       </c>
     </row>
     <row r="322">
       <c r="A322" t="s" s="2">
-        <v>850</v>
+        <v>853</v>
       </c>
       <c r="B322" t="s" s="2">
-        <v>915</v>
+        <v>913</v>
       </c>
       <c r="C322" t="s" s="2">
-        <v>915</v>
+        <v>913</v>
       </c>
       <c r="D322" s="2"/>
       <c r="E322" t="s" s="2">
-        <v>533</v>
+        <v>73</v>
       </c>
       <c r="F322" s="2"/>
       <c r="G322" t="s" s="2">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="H322" t="s" s="2">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="I322" t="s" s="2">
         <v>73</v>
       </c>
       <c r="J322" t="s" s="2">
-        <v>534</v>
+        <v>73</v>
       </c>
       <c r="K322" t="s" s="2">
-        <v>534</v>
+        <v>73</v>
       </c>
       <c r="L322" t="s" s="2">
-        <v>374</v>
+        <v>522</v>
       </c>
       <c r="M322" t="s" s="2">
-        <v>535</v>
+        <v>914</v>
       </c>
       <c r="N322" t="s" s="2">
-        <v>536</v>
-      </c>
-      <c r="O322" t="s" s="2">
-        <v>377</v>
-      </c>
-      <c r="P322" t="s" s="2">
-        <v>537</v>
-      </c>
+        <v>915</v>
+      </c>
+      <c r="O322" s="2"/>
+      <c r="P322" s="2"/>
       <c r="Q322" t="s" s="2">
         <v>73</v>
       </c>
@@ -42348,24 +42352,24 @@
         <v>73</v>
       </c>
       <c r="AG322" t="s" s="2">
-        <v>538</v>
+        <v>913</v>
       </c>
       <c r="AH322" t="s" s="2">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="AI322" t="s" s="2">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="AJ322" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AK322" t="s" s="2">
-        <v>379</v>
+        <v>367</v>
       </c>
     </row>
     <row r="323">
       <c r="A323" t="s" s="2">
-        <v>850</v>
+        <v>853</v>
       </c>
       <c r="B323" t="s" s="2">
         <v>916</v>
@@ -42379,7 +42383,7 @@
       </c>
       <c r="F323" s="2"/>
       <c r="G323" t="s" s="2">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="H323" t="s" s="2">
         <v>79</v>
@@ -42394,13 +42398,13 @@
         <v>73</v>
       </c>
       <c r="L323" t="s" s="2">
-        <v>522</v>
+        <v>89</v>
       </c>
       <c r="M323" t="s" s="2">
-        <v>917</v>
+        <v>525</v>
       </c>
       <c r="N323" t="s" s="2">
-        <v>917</v>
+        <v>526</v>
       </c>
       <c r="O323" s="2"/>
       <c r="P323" s="2"/>
@@ -42451,10 +42455,10 @@
         <v>73</v>
       </c>
       <c r="AG323" t="s" s="2">
-        <v>916</v>
+        <v>371</v>
       </c>
       <c r="AH323" t="s" s="2">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="AI323" t="s" s="2">
         <v>79</v>
@@ -42463,29 +42467,29 @@
         <v>73</v>
       </c>
       <c r="AK323" t="s" s="2">
-        <v>367</v>
+        <v>73</v>
       </c>
     </row>
     <row r="324">
       <c r="A324" t="s" s="2">
-        <v>850</v>
+        <v>853</v>
       </c>
       <c r="B324" t="s" s="2">
-        <v>918</v>
+        <v>917</v>
       </c>
       <c r="C324" t="s" s="2">
-        <v>918</v>
+        <v>917</v>
       </c>
       <c r="D324" s="2"/>
       <c r="E324" t="s" s="2">
-        <v>73</v>
+        <v>373</v>
       </c>
       <c r="F324" s="2"/>
       <c r="G324" t="s" s="2">
         <v>74</v>
       </c>
       <c r="H324" t="s" s="2">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="I324" t="s" s="2">
         <v>73</v>
@@ -42497,15 +42501,17 @@
         <v>73</v>
       </c>
       <c r="L324" t="s" s="2">
-        <v>89</v>
+        <v>374</v>
       </c>
       <c r="M324" t="s" s="2">
-        <v>525</v>
+        <v>375</v>
       </c>
       <c r="N324" t="s" s="2">
-        <v>526</v>
-      </c>
-      <c r="O324" s="2"/>
+        <v>528</v>
+      </c>
+      <c r="O324" t="s" s="2">
+        <v>377</v>
+      </c>
       <c r="P324" s="2"/>
       <c r="Q324" t="s" s="2">
         <v>73</v>
@@ -42542,46 +42548,46 @@
         <v>73</v>
       </c>
       <c r="AC324" t="s" s="2">
-        <v>73</v>
+        <v>529</v>
       </c>
       <c r="AD324" t="s" s="2">
-        <v>73</v>
+        <v>530</v>
       </c>
       <c r="AE324" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AF324" t="s" s="2">
-        <v>73</v>
+        <v>531</v>
       </c>
       <c r="AG324" t="s" s="2">
-        <v>371</v>
+        <v>378</v>
       </c>
       <c r="AH324" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AI324" t="s" s="2">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="AJ324" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AK324" t="s" s="2">
-        <v>73</v>
+        <v>379</v>
       </c>
     </row>
     <row r="325">
       <c r="A325" t="s" s="2">
-        <v>850</v>
+        <v>853</v>
       </c>
       <c r="B325" t="s" s="2">
-        <v>919</v>
+        <v>918</v>
       </c>
       <c r="C325" t="s" s="2">
-        <v>919</v>
+        <v>918</v>
       </c>
       <c r="D325" s="2"/>
       <c r="E325" t="s" s="2">
-        <v>373</v>
+        <v>533</v>
       </c>
       <c r="F325" s="2"/>
       <c r="G325" t="s" s="2">
@@ -42594,24 +42600,26 @@
         <v>73</v>
       </c>
       <c r="J325" t="s" s="2">
-        <v>73</v>
+        <v>534</v>
       </c>
       <c r="K325" t="s" s="2">
-        <v>73</v>
+        <v>534</v>
       </c>
       <c r="L325" t="s" s="2">
         <v>374</v>
       </c>
       <c r="M325" t="s" s="2">
-        <v>375</v>
+        <v>535</v>
       </c>
       <c r="N325" t="s" s="2">
-        <v>528</v>
+        <v>536</v>
       </c>
       <c r="O325" t="s" s="2">
         <v>377</v>
       </c>
-      <c r="P325" s="2"/>
+      <c r="P325" t="s" s="2">
+        <v>537</v>
+      </c>
       <c r="Q325" t="s" s="2">
         <v>73</v>
       </c>
@@ -42647,19 +42655,19 @@
         <v>73</v>
       </c>
       <c r="AC325" t="s" s="2">
-        <v>529</v>
+        <v>73</v>
       </c>
       <c r="AD325" t="s" s="2">
-        <v>530</v>
+        <v>73</v>
       </c>
       <c r="AE325" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AF325" t="s" s="2">
-        <v>531</v>
+        <v>73</v>
       </c>
       <c r="AG325" t="s" s="2">
-        <v>378</v>
+        <v>538</v>
       </c>
       <c r="AH325" t="s" s="2">
         <v>74</v>
@@ -42676,49 +42684,45 @@
     </row>
     <row r="326">
       <c r="A326" t="s" s="2">
-        <v>850</v>
+        <v>853</v>
       </c>
       <c r="B326" t="s" s="2">
-        <v>920</v>
+        <v>919</v>
       </c>
       <c r="C326" t="s" s="2">
-        <v>920</v>
+        <v>919</v>
       </c>
       <c r="D326" s="2"/>
       <c r="E326" t="s" s="2">
-        <v>533</v>
+        <v>73</v>
       </c>
       <c r="F326" s="2"/>
       <c r="G326" t="s" s="2">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="H326" t="s" s="2">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="I326" t="s" s="2">
         <v>73</v>
       </c>
       <c r="J326" t="s" s="2">
-        <v>534</v>
+        <v>73</v>
       </c>
       <c r="K326" t="s" s="2">
-        <v>534</v>
+        <v>73</v>
       </c>
       <c r="L326" t="s" s="2">
-        <v>374</v>
+        <v>522</v>
       </c>
       <c r="M326" t="s" s="2">
-        <v>535</v>
+        <v>920</v>
       </c>
       <c r="N326" t="s" s="2">
-        <v>536</v>
-      </c>
-      <c r="O326" t="s" s="2">
-        <v>377</v>
-      </c>
-      <c r="P326" t="s" s="2">
-        <v>537</v>
-      </c>
+        <v>920</v>
+      </c>
+      <c r="O326" s="2"/>
+      <c r="P326" s="2"/>
       <c r="Q326" t="s" s="2">
         <v>73</v>
       </c>
@@ -42766,24 +42770,24 @@
         <v>73</v>
       </c>
       <c r="AG326" t="s" s="2">
-        <v>538</v>
+        <v>919</v>
       </c>
       <c r="AH326" t="s" s="2">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="AI326" t="s" s="2">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="AJ326" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AK326" t="s" s="2">
-        <v>379</v>
+        <v>367</v>
       </c>
     </row>
     <row r="327">
       <c r="A327" t="s" s="2">
-        <v>850</v>
+        <v>853</v>
       </c>
       <c r="B327" t="s" s="2">
         <v>921</v>
@@ -42797,7 +42801,7 @@
       </c>
       <c r="F327" s="2"/>
       <c r="G327" t="s" s="2">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="H327" t="s" s="2">
         <v>79</v>
@@ -42815,10 +42819,10 @@
         <v>89</v>
       </c>
       <c r="M327" t="s" s="2">
-        <v>922</v>
+        <v>525</v>
       </c>
       <c r="N327" t="s" s="2">
-        <v>922</v>
+        <v>526</v>
       </c>
       <c r="O327" s="2"/>
       <c r="P327" s="2"/>
@@ -42869,10 +42873,10 @@
         <v>73</v>
       </c>
       <c r="AG327" t="s" s="2">
-        <v>921</v>
+        <v>371</v>
       </c>
       <c r="AH327" t="s" s="2">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="AI327" t="s" s="2">
         <v>79</v>
@@ -42886,24 +42890,24 @@
     </row>
     <row r="328">
       <c r="A328" t="s" s="2">
-        <v>850</v>
+        <v>853</v>
       </c>
       <c r="B328" t="s" s="2">
-        <v>923</v>
+        <v>922</v>
       </c>
       <c r="C328" t="s" s="2">
-        <v>923</v>
+        <v>922</v>
       </c>
       <c r="D328" s="2"/>
       <c r="E328" t="s" s="2">
-        <v>73</v>
+        <v>373</v>
       </c>
       <c r="F328" s="2"/>
       <c r="G328" t="s" s="2">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="H328" t="s" s="2">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="I328" t="s" s="2">
         <v>73</v>
@@ -42915,15 +42919,17 @@
         <v>73</v>
       </c>
       <c r="L328" t="s" s="2">
-        <v>89</v>
+        <v>374</v>
       </c>
       <c r="M328" t="s" s="2">
-        <v>924</v>
+        <v>375</v>
       </c>
       <c r="N328" t="s" s="2">
-        <v>924</v>
-      </c>
-      <c r="O328" s="2"/>
+        <v>528</v>
+      </c>
+      <c r="O328" t="s" s="2">
+        <v>377</v>
+      </c>
       <c r="P328" s="2"/>
       <c r="Q328" t="s" s="2">
         <v>73</v>
@@ -42960,74 +42966,78 @@
         <v>73</v>
       </c>
       <c r="AC328" t="s" s="2">
-        <v>73</v>
+        <v>529</v>
       </c>
       <c r="AD328" t="s" s="2">
-        <v>73</v>
+        <v>530</v>
       </c>
       <c r="AE328" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AF328" t="s" s="2">
-        <v>73</v>
+        <v>531</v>
       </c>
       <c r="AG328" t="s" s="2">
-        <v>923</v>
+        <v>378</v>
       </c>
       <c r="AH328" t="s" s="2">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="AI328" t="s" s="2">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="AJ328" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AK328" t="s" s="2">
-        <v>73</v>
+        <v>379</v>
       </c>
     </row>
     <row r="329">
       <c r="A329" t="s" s="2">
-        <v>850</v>
+        <v>853</v>
       </c>
       <c r="B329" t="s" s="2">
-        <v>925</v>
+        <v>923</v>
       </c>
       <c r="C329" t="s" s="2">
-        <v>925</v>
+        <v>923</v>
       </c>
       <c r="D329" s="2"/>
       <c r="E329" t="s" s="2">
-        <v>73</v>
+        <v>533</v>
       </c>
       <c r="F329" s="2"/>
       <c r="G329" t="s" s="2">
         <v>74</v>
       </c>
       <c r="H329" t="s" s="2">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="I329" t="s" s="2">
         <v>73</v>
       </c>
       <c r="J329" t="s" s="2">
-        <v>73</v>
+        <v>534</v>
       </c>
       <c r="K329" t="s" s="2">
-        <v>73</v>
+        <v>534</v>
       </c>
       <c r="L329" t="s" s="2">
-        <v>522</v>
+        <v>374</v>
       </c>
       <c r="M329" t="s" s="2">
-        <v>926</v>
+        <v>535</v>
       </c>
       <c r="N329" t="s" s="2">
-        <v>926</v>
-      </c>
-      <c r="O329" s="2"/>
-      <c r="P329" s="2"/>
+        <v>536</v>
+      </c>
+      <c r="O329" t="s" s="2">
+        <v>377</v>
+      </c>
+      <c r="P329" t="s" s="2">
+        <v>537</v>
+      </c>
       <c r="Q329" t="s" s="2">
         <v>73</v>
       </c>
@@ -43075,30 +43085,30 @@
         <v>73</v>
       </c>
       <c r="AG329" t="s" s="2">
-        <v>925</v>
+        <v>538</v>
       </c>
       <c r="AH329" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AI329" t="s" s="2">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="AJ329" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AK329" t="s" s="2">
-        <v>367</v>
+        <v>379</v>
       </c>
     </row>
     <row r="330">
       <c r="A330" t="s" s="2">
-        <v>850</v>
+        <v>853</v>
       </c>
       <c r="B330" t="s" s="2">
-        <v>927</v>
+        <v>924</v>
       </c>
       <c r="C330" t="s" s="2">
-        <v>927</v>
+        <v>924</v>
       </c>
       <c r="D330" s="2"/>
       <c r="E330" t="s" s="2">
@@ -43106,7 +43116,7 @@
       </c>
       <c r="F330" s="2"/>
       <c r="G330" t="s" s="2">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="H330" t="s" s="2">
         <v>79</v>
@@ -43124,10 +43134,10 @@
         <v>89</v>
       </c>
       <c r="M330" t="s" s="2">
-        <v>525</v>
+        <v>925</v>
       </c>
       <c r="N330" t="s" s="2">
-        <v>526</v>
+        <v>925</v>
       </c>
       <c r="O330" s="2"/>
       <c r="P330" s="2"/>
@@ -43178,10 +43188,10 @@
         <v>73</v>
       </c>
       <c r="AG330" t="s" s="2">
-        <v>371</v>
+        <v>924</v>
       </c>
       <c r="AH330" t="s" s="2">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="AI330" t="s" s="2">
         <v>79</v>
@@ -43195,24 +43205,24 @@
     </row>
     <row r="331">
       <c r="A331" t="s" s="2">
-        <v>850</v>
+        <v>853</v>
       </c>
       <c r="B331" t="s" s="2">
-        <v>928</v>
+        <v>926</v>
       </c>
       <c r="C331" t="s" s="2">
-        <v>928</v>
+        <v>926</v>
       </c>
       <c r="D331" s="2"/>
       <c r="E331" t="s" s="2">
-        <v>373</v>
+        <v>73</v>
       </c>
       <c r="F331" s="2"/>
       <c r="G331" t="s" s="2">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="H331" t="s" s="2">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="I331" t="s" s="2">
         <v>73</v>
@@ -43224,17 +43234,15 @@
         <v>73</v>
       </c>
       <c r="L331" t="s" s="2">
-        <v>374</v>
+        <v>89</v>
       </c>
       <c r="M331" t="s" s="2">
-        <v>375</v>
+        <v>927</v>
       </c>
       <c r="N331" t="s" s="2">
-        <v>528</v>
-      </c>
-      <c r="O331" t="s" s="2">
-        <v>377</v>
-      </c>
+        <v>927</v>
+      </c>
+      <c r="O331" s="2"/>
       <c r="P331" s="2"/>
       <c r="Q331" t="s" s="2">
         <v>73</v>
@@ -43271,78 +43279,74 @@
         <v>73</v>
       </c>
       <c r="AC331" t="s" s="2">
-        <v>529</v>
+        <v>73</v>
       </c>
       <c r="AD331" t="s" s="2">
-        <v>530</v>
+        <v>73</v>
       </c>
       <c r="AE331" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AF331" t="s" s="2">
-        <v>531</v>
+        <v>73</v>
       </c>
       <c r="AG331" t="s" s="2">
-        <v>378</v>
+        <v>926</v>
       </c>
       <c r="AH331" t="s" s="2">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="AI331" t="s" s="2">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="AJ331" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AK331" t="s" s="2">
-        <v>379</v>
+        <v>73</v>
       </c>
     </row>
     <row r="332">
       <c r="A332" t="s" s="2">
-        <v>850</v>
+        <v>853</v>
       </c>
       <c r="B332" t="s" s="2">
-        <v>929</v>
+        <v>928</v>
       </c>
       <c r="C332" t="s" s="2">
-        <v>929</v>
+        <v>928</v>
       </c>
       <c r="D332" s="2"/>
       <c r="E332" t="s" s="2">
-        <v>533</v>
+        <v>73</v>
       </c>
       <c r="F332" s="2"/>
       <c r="G332" t="s" s="2">
         <v>74</v>
       </c>
       <c r="H332" t="s" s="2">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="I332" t="s" s="2">
         <v>73</v>
       </c>
       <c r="J332" t="s" s="2">
-        <v>534</v>
+        <v>73</v>
       </c>
       <c r="K332" t="s" s="2">
-        <v>534</v>
+        <v>73</v>
       </c>
       <c r="L332" t="s" s="2">
-        <v>374</v>
+        <v>522</v>
       </c>
       <c r="M332" t="s" s="2">
-        <v>535</v>
+        <v>929</v>
       </c>
       <c r="N332" t="s" s="2">
-        <v>536</v>
-      </c>
-      <c r="O332" t="s" s="2">
-        <v>377</v>
-      </c>
-      <c r="P332" t="s" s="2">
-        <v>537</v>
-      </c>
+        <v>929</v>
+      </c>
+      <c r="O332" s="2"/>
+      <c r="P332" s="2"/>
       <c r="Q332" t="s" s="2">
         <v>73</v>
       </c>
@@ -43390,24 +43394,24 @@
         <v>73</v>
       </c>
       <c r="AG332" t="s" s="2">
-        <v>538</v>
+        <v>928</v>
       </c>
       <c r="AH332" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AI332" t="s" s="2">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="AJ332" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AK332" t="s" s="2">
-        <v>379</v>
+        <v>367</v>
       </c>
     </row>
     <row r="333">
       <c r="A333" t="s" s="2">
-        <v>850</v>
+        <v>853</v>
       </c>
       <c r="B333" t="s" s="2">
         <v>930</v>
@@ -43424,7 +43428,7 @@
         <v>74</v>
       </c>
       <c r="H333" t="s" s="2">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="I333" t="s" s="2">
         <v>73</v>
@@ -43436,13 +43440,13 @@
         <v>73</v>
       </c>
       <c r="L333" t="s" s="2">
-        <v>522</v>
+        <v>89</v>
       </c>
       <c r="M333" t="s" s="2">
-        <v>931</v>
+        <v>525</v>
       </c>
       <c r="N333" t="s" s="2">
-        <v>931</v>
+        <v>526</v>
       </c>
       <c r="O333" s="2"/>
       <c r="P333" s="2"/>
@@ -43493,41 +43497,41 @@
         <v>73</v>
       </c>
       <c r="AG333" t="s" s="2">
-        <v>930</v>
+        <v>371</v>
       </c>
       <c r="AH333" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AI333" t="s" s="2">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="AJ333" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AK333" t="s" s="2">
-        <v>367</v>
+        <v>73</v>
       </c>
     </row>
     <row r="334">
       <c r="A334" t="s" s="2">
-        <v>850</v>
+        <v>853</v>
       </c>
       <c r="B334" t="s" s="2">
-        <v>932</v>
+        <v>931</v>
       </c>
       <c r="C334" t="s" s="2">
-        <v>932</v>
+        <v>931</v>
       </c>
       <c r="D334" s="2"/>
       <c r="E334" t="s" s="2">
-        <v>73</v>
+        <v>373</v>
       </c>
       <c r="F334" s="2"/>
       <c r="G334" t="s" s="2">
         <v>74</v>
       </c>
       <c r="H334" t="s" s="2">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="I334" t="s" s="2">
         <v>73</v>
@@ -43539,15 +43543,17 @@
         <v>73</v>
       </c>
       <c r="L334" t="s" s="2">
-        <v>89</v>
+        <v>374</v>
       </c>
       <c r="M334" t="s" s="2">
-        <v>525</v>
+        <v>375</v>
       </c>
       <c r="N334" t="s" s="2">
-        <v>526</v>
-      </c>
-      <c r="O334" s="2"/>
+        <v>528</v>
+      </c>
+      <c r="O334" t="s" s="2">
+        <v>377</v>
+      </c>
       <c r="P334" s="2"/>
       <c r="Q334" t="s" s="2">
         <v>73</v>
@@ -43584,46 +43590,46 @@
         <v>73</v>
       </c>
       <c r="AC334" t="s" s="2">
-        <v>73</v>
+        <v>529</v>
       </c>
       <c r="AD334" t="s" s="2">
-        <v>73</v>
+        <v>530</v>
       </c>
       <c r="AE334" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AF334" t="s" s="2">
-        <v>73</v>
+        <v>531</v>
       </c>
       <c r="AG334" t="s" s="2">
-        <v>371</v>
+        <v>378</v>
       </c>
       <c r="AH334" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AI334" t="s" s="2">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="AJ334" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AK334" t="s" s="2">
-        <v>73</v>
+        <v>379</v>
       </c>
     </row>
     <row r="335">
       <c r="A335" t="s" s="2">
-        <v>850</v>
+        <v>853</v>
       </c>
       <c r="B335" t="s" s="2">
-        <v>933</v>
+        <v>932</v>
       </c>
       <c r="C335" t="s" s="2">
-        <v>933</v>
+        <v>932</v>
       </c>
       <c r="D335" s="2"/>
       <c r="E335" t="s" s="2">
-        <v>373</v>
+        <v>533</v>
       </c>
       <c r="F335" s="2"/>
       <c r="G335" t="s" s="2">
@@ -43636,24 +43642,26 @@
         <v>73</v>
       </c>
       <c r="J335" t="s" s="2">
-        <v>73</v>
+        <v>534</v>
       </c>
       <c r="K335" t="s" s="2">
-        <v>73</v>
+        <v>534</v>
       </c>
       <c r="L335" t="s" s="2">
         <v>374</v>
       </c>
       <c r="M335" t="s" s="2">
-        <v>375</v>
+        <v>535</v>
       </c>
       <c r="N335" t="s" s="2">
-        <v>528</v>
+        <v>536</v>
       </c>
       <c r="O335" t="s" s="2">
         <v>377</v>
       </c>
-      <c r="P335" s="2"/>
+      <c r="P335" t="s" s="2">
+        <v>537</v>
+      </c>
       <c r="Q335" t="s" s="2">
         <v>73</v>
       </c>
@@ -43689,19 +43697,19 @@
         <v>73</v>
       </c>
       <c r="AC335" t="s" s="2">
-        <v>529</v>
+        <v>73</v>
       </c>
       <c r="AD335" t="s" s="2">
-        <v>530</v>
+        <v>73</v>
       </c>
       <c r="AE335" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AF335" t="s" s="2">
-        <v>531</v>
+        <v>73</v>
       </c>
       <c r="AG335" t="s" s="2">
-        <v>378</v>
+        <v>538</v>
       </c>
       <c r="AH335" t="s" s="2">
         <v>74</v>
@@ -43718,17 +43726,17 @@
     </row>
     <row r="336">
       <c r="A336" t="s" s="2">
-        <v>850</v>
+        <v>853</v>
       </c>
       <c r="B336" t="s" s="2">
-        <v>934</v>
+        <v>933</v>
       </c>
       <c r="C336" t="s" s="2">
-        <v>934</v>
+        <v>933</v>
       </c>
       <c r="D336" s="2"/>
       <c r="E336" t="s" s="2">
-        <v>533</v>
+        <v>73</v>
       </c>
       <c r="F336" s="2"/>
       <c r="G336" t="s" s="2">
@@ -43741,26 +43749,22 @@
         <v>73</v>
       </c>
       <c r="J336" t="s" s="2">
-        <v>534</v>
+        <v>73</v>
       </c>
       <c r="K336" t="s" s="2">
-        <v>534</v>
+        <v>73</v>
       </c>
       <c r="L336" t="s" s="2">
-        <v>374</v>
+        <v>522</v>
       </c>
       <c r="M336" t="s" s="2">
-        <v>535</v>
+        <v>934</v>
       </c>
       <c r="N336" t="s" s="2">
-        <v>536</v>
-      </c>
-      <c r="O336" t="s" s="2">
-        <v>377</v>
-      </c>
-      <c r="P336" t="s" s="2">
-        <v>537</v>
-      </c>
+        <v>934</v>
+      </c>
+      <c r="O336" s="2"/>
+      <c r="P336" s="2"/>
       <c r="Q336" t="s" s="2">
         <v>73</v>
       </c>
@@ -43808,7 +43812,7 @@
         <v>73</v>
       </c>
       <c r="AG336" t="s" s="2">
-        <v>538</v>
+        <v>933</v>
       </c>
       <c r="AH336" t="s" s="2">
         <v>74</v>
@@ -43820,12 +43824,12 @@
         <v>73</v>
       </c>
       <c r="AK336" t="s" s="2">
-        <v>379</v>
+        <v>367</v>
       </c>
     </row>
     <row r="337">
       <c r="A337" t="s" s="2">
-        <v>850</v>
+        <v>853</v>
       </c>
       <c r="B337" t="s" s="2">
         <v>935</v>
@@ -43839,7 +43843,7 @@
       </c>
       <c r="F337" s="2"/>
       <c r="G337" t="s" s="2">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="H337" t="s" s="2">
         <v>79</v>
@@ -43857,10 +43861,10 @@
         <v>89</v>
       </c>
       <c r="M337" t="s" s="2">
-        <v>936</v>
+        <v>525</v>
       </c>
       <c r="N337" t="s" s="2">
-        <v>936</v>
+        <v>526</v>
       </c>
       <c r="O337" s="2"/>
       <c r="P337" s="2"/>
@@ -43911,10 +43915,10 @@
         <v>73</v>
       </c>
       <c r="AG337" t="s" s="2">
-        <v>935</v>
+        <v>371</v>
       </c>
       <c r="AH337" t="s" s="2">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="AI337" t="s" s="2">
         <v>79</v>
@@ -43928,24 +43932,24 @@
     </row>
     <row r="338">
       <c r="A338" t="s" s="2">
-        <v>850</v>
+        <v>853</v>
       </c>
       <c r="B338" t="s" s="2">
-        <v>937</v>
+        <v>936</v>
       </c>
       <c r="C338" t="s" s="2">
-        <v>937</v>
+        <v>936</v>
       </c>
       <c r="D338" s="2"/>
       <c r="E338" t="s" s="2">
-        <v>73</v>
+        <v>373</v>
       </c>
       <c r="F338" s="2"/>
       <c r="G338" t="s" s="2">
         <v>74</v>
       </c>
       <c r="H338" t="s" s="2">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="I338" t="s" s="2">
         <v>73</v>
@@ -43957,15 +43961,17 @@
         <v>73</v>
       </c>
       <c r="L338" t="s" s="2">
-        <v>89</v>
+        <v>374</v>
       </c>
       <c r="M338" t="s" s="2">
-        <v>938</v>
+        <v>375</v>
       </c>
       <c r="N338" t="s" s="2">
-        <v>938</v>
-      </c>
-      <c r="O338" s="2"/>
+        <v>528</v>
+      </c>
+      <c r="O338" t="s" s="2">
+        <v>377</v>
+      </c>
       <c r="P338" s="2"/>
       <c r="Q338" t="s" s="2">
         <v>73</v>
@@ -44002,74 +44008,78 @@
         <v>73</v>
       </c>
       <c r="AC338" t="s" s="2">
-        <v>73</v>
+        <v>529</v>
       </c>
       <c r="AD338" t="s" s="2">
-        <v>73</v>
+        <v>530</v>
       </c>
       <c r="AE338" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AF338" t="s" s="2">
-        <v>73</v>
+        <v>531</v>
       </c>
       <c r="AG338" t="s" s="2">
-        <v>937</v>
+        <v>378</v>
       </c>
       <c r="AH338" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AI338" t="s" s="2">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="AJ338" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AK338" t="s" s="2">
-        <v>73</v>
+        <v>379</v>
       </c>
     </row>
     <row r="339">
       <c r="A339" t="s" s="2">
-        <v>850</v>
+        <v>853</v>
       </c>
       <c r="B339" t="s" s="2">
-        <v>939</v>
+        <v>937</v>
       </c>
       <c r="C339" t="s" s="2">
-        <v>939</v>
+        <v>937</v>
       </c>
       <c r="D339" s="2"/>
       <c r="E339" t="s" s="2">
-        <v>73</v>
+        <v>533</v>
       </c>
       <c r="F339" s="2"/>
       <c r="G339" t="s" s="2">
         <v>74</v>
       </c>
       <c r="H339" t="s" s="2">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="I339" t="s" s="2">
         <v>73</v>
       </c>
       <c r="J339" t="s" s="2">
-        <v>73</v>
+        <v>534</v>
       </c>
       <c r="K339" t="s" s="2">
-        <v>73</v>
+        <v>534</v>
       </c>
       <c r="L339" t="s" s="2">
-        <v>89</v>
+        <v>374</v>
       </c>
       <c r="M339" t="s" s="2">
-        <v>940</v>
+        <v>535</v>
       </c>
       <c r="N339" t="s" s="2">
-        <v>940</v>
-      </c>
-      <c r="O339" s="2"/>
-      <c r="P339" s="2"/>
+        <v>536</v>
+      </c>
+      <c r="O339" t="s" s="2">
+        <v>377</v>
+      </c>
+      <c r="P339" t="s" s="2">
+        <v>537</v>
+      </c>
       <c r="Q339" t="s" s="2">
         <v>73</v>
       </c>
@@ -44117,30 +44127,30 @@
         <v>73</v>
       </c>
       <c r="AG339" t="s" s="2">
-        <v>939</v>
+        <v>538</v>
       </c>
       <c r="AH339" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AI339" t="s" s="2">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="AJ339" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AK339" t="s" s="2">
-        <v>73</v>
+        <v>379</v>
       </c>
     </row>
     <row r="340">
       <c r="A340" t="s" s="2">
-        <v>850</v>
+        <v>853</v>
       </c>
       <c r="B340" t="s" s="2">
-        <v>941</v>
+        <v>938</v>
       </c>
       <c r="C340" t="s" s="2">
-        <v>941</v>
+        <v>938</v>
       </c>
       <c r="D340" s="2"/>
       <c r="E340" t="s" s="2">
@@ -44148,7 +44158,7 @@
       </c>
       <c r="F340" s="2"/>
       <c r="G340" t="s" s="2">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="H340" t="s" s="2">
         <v>79</v>
@@ -44163,13 +44173,13 @@
         <v>73</v>
       </c>
       <c r="L340" t="s" s="2">
-        <v>522</v>
+        <v>89</v>
       </c>
       <c r="M340" t="s" s="2">
-        <v>942</v>
+        <v>939</v>
       </c>
       <c r="N340" t="s" s="2">
-        <v>942</v>
+        <v>939</v>
       </c>
       <c r="O340" s="2"/>
       <c r="P340" s="2"/>
@@ -44220,10 +44230,10 @@
         <v>73</v>
       </c>
       <c r="AG340" t="s" s="2">
-        <v>941</v>
+        <v>938</v>
       </c>
       <c r="AH340" t="s" s="2">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="AI340" t="s" s="2">
         <v>79</v>
@@ -44232,18 +44242,18 @@
         <v>73</v>
       </c>
       <c r="AK340" t="s" s="2">
-        <v>367</v>
+        <v>73</v>
       </c>
     </row>
     <row r="341">
       <c r="A341" t="s" s="2">
-        <v>850</v>
+        <v>853</v>
       </c>
       <c r="B341" t="s" s="2">
-        <v>943</v>
+        <v>940</v>
       </c>
       <c r="C341" t="s" s="2">
-        <v>943</v>
+        <v>940</v>
       </c>
       <c r="D341" s="2"/>
       <c r="E341" t="s" s="2">
@@ -44269,10 +44279,10 @@
         <v>89</v>
       </c>
       <c r="M341" t="s" s="2">
-        <v>525</v>
+        <v>941</v>
       </c>
       <c r="N341" t="s" s="2">
-        <v>526</v>
+        <v>941</v>
       </c>
       <c r="O341" s="2"/>
       <c r="P341" s="2"/>
@@ -44323,7 +44333,7 @@
         <v>73</v>
       </c>
       <c r="AG341" t="s" s="2">
-        <v>371</v>
+        <v>940</v>
       </c>
       <c r="AH341" t="s" s="2">
         <v>74</v>
@@ -44340,24 +44350,24 @@
     </row>
     <row r="342">
       <c r="A342" t="s" s="2">
-        <v>850</v>
+        <v>853</v>
       </c>
       <c r="B342" t="s" s="2">
-        <v>944</v>
+        <v>942</v>
       </c>
       <c r="C342" t="s" s="2">
-        <v>944</v>
+        <v>942</v>
       </c>
       <c r="D342" s="2"/>
       <c r="E342" t="s" s="2">
-        <v>373</v>
+        <v>73</v>
       </c>
       <c r="F342" s="2"/>
       <c r="G342" t="s" s="2">
         <v>74</v>
       </c>
       <c r="H342" t="s" s="2">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="I342" t="s" s="2">
         <v>73</v>
@@ -44369,17 +44379,15 @@
         <v>73</v>
       </c>
       <c r="L342" t="s" s="2">
-        <v>374</v>
+        <v>89</v>
       </c>
       <c r="M342" t="s" s="2">
-        <v>375</v>
+        <v>943</v>
       </c>
       <c r="N342" t="s" s="2">
-        <v>528</v>
-      </c>
-      <c r="O342" t="s" s="2">
-        <v>377</v>
-      </c>
+        <v>943</v>
+      </c>
+      <c r="O342" s="2"/>
       <c r="P342" s="2"/>
       <c r="Q342" t="s" s="2">
         <v>73</v>
@@ -44416,78 +44424,74 @@
         <v>73</v>
       </c>
       <c r="AC342" t="s" s="2">
-        <v>529</v>
+        <v>73</v>
       </c>
       <c r="AD342" t="s" s="2">
-        <v>530</v>
+        <v>73</v>
       </c>
       <c r="AE342" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AF342" t="s" s="2">
-        <v>531</v>
+        <v>73</v>
       </c>
       <c r="AG342" t="s" s="2">
-        <v>378</v>
+        <v>942</v>
       </c>
       <c r="AH342" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AI342" t="s" s="2">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="AJ342" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AK342" t="s" s="2">
-        <v>379</v>
+        <v>73</v>
       </c>
     </row>
     <row r="343">
       <c r="A343" t="s" s="2">
-        <v>850</v>
+        <v>853</v>
       </c>
       <c r="B343" t="s" s="2">
-        <v>945</v>
+        <v>944</v>
       </c>
       <c r="C343" t="s" s="2">
-        <v>945</v>
+        <v>944</v>
       </c>
       <c r="D343" s="2"/>
       <c r="E343" t="s" s="2">
-        <v>533</v>
+        <v>73</v>
       </c>
       <c r="F343" s="2"/>
       <c r="G343" t="s" s="2">
         <v>74</v>
       </c>
       <c r="H343" t="s" s="2">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="I343" t="s" s="2">
         <v>73</v>
       </c>
       <c r="J343" t="s" s="2">
-        <v>534</v>
+        <v>73</v>
       </c>
       <c r="K343" t="s" s="2">
-        <v>534</v>
+        <v>73</v>
       </c>
       <c r="L343" t="s" s="2">
-        <v>374</v>
+        <v>522</v>
       </c>
       <c r="M343" t="s" s="2">
-        <v>535</v>
+        <v>945</v>
       </c>
       <c r="N343" t="s" s="2">
-        <v>536</v>
-      </c>
-      <c r="O343" t="s" s="2">
-        <v>377</v>
-      </c>
-      <c r="P343" t="s" s="2">
-        <v>537</v>
-      </c>
+        <v>945</v>
+      </c>
+      <c r="O343" s="2"/>
+      <c r="P343" s="2"/>
       <c r="Q343" t="s" s="2">
         <v>73</v>
       </c>
@@ -44535,24 +44539,24 @@
         <v>73</v>
       </c>
       <c r="AG343" t="s" s="2">
-        <v>538</v>
+        <v>944</v>
       </c>
       <c r="AH343" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AI343" t="s" s="2">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="AJ343" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AK343" t="s" s="2">
-        <v>379</v>
+        <v>367</v>
       </c>
     </row>
     <row r="344">
       <c r="A344" t="s" s="2">
-        <v>850</v>
+        <v>853</v>
       </c>
       <c r="B344" t="s" s="2">
         <v>946</v>
@@ -44581,13 +44585,13 @@
         <v>73</v>
       </c>
       <c r="L344" t="s" s="2">
-        <v>522</v>
+        <v>89</v>
       </c>
       <c r="M344" t="s" s="2">
-        <v>947</v>
+        <v>525</v>
       </c>
       <c r="N344" t="s" s="2">
-        <v>947</v>
+        <v>526</v>
       </c>
       <c r="O344" s="2"/>
       <c r="P344" s="2"/>
@@ -44638,7 +44642,7 @@
         <v>73</v>
       </c>
       <c r="AG344" t="s" s="2">
-        <v>946</v>
+        <v>371</v>
       </c>
       <c r="AH344" t="s" s="2">
         <v>74</v>
@@ -44650,29 +44654,29 @@
         <v>73</v>
       </c>
       <c r="AK344" t="s" s="2">
-        <v>367</v>
+        <v>73</v>
       </c>
     </row>
     <row r="345">
       <c r="A345" t="s" s="2">
-        <v>850</v>
+        <v>853</v>
       </c>
       <c r="B345" t="s" s="2">
-        <v>948</v>
+        <v>947</v>
       </c>
       <c r="C345" t="s" s="2">
-        <v>948</v>
+        <v>947</v>
       </c>
       <c r="D345" s="2"/>
       <c r="E345" t="s" s="2">
-        <v>73</v>
+        <v>373</v>
       </c>
       <c r="F345" s="2"/>
       <c r="G345" t="s" s="2">
         <v>74</v>
       </c>
       <c r="H345" t="s" s="2">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="I345" t="s" s="2">
         <v>73</v>
@@ -44684,15 +44688,17 @@
         <v>73</v>
       </c>
       <c r="L345" t="s" s="2">
-        <v>89</v>
+        <v>374</v>
       </c>
       <c r="M345" t="s" s="2">
-        <v>525</v>
+        <v>375</v>
       </c>
       <c r="N345" t="s" s="2">
-        <v>526</v>
-      </c>
-      <c r="O345" s="2"/>
+        <v>528</v>
+      </c>
+      <c r="O345" t="s" s="2">
+        <v>377</v>
+      </c>
       <c r="P345" s="2"/>
       <c r="Q345" t="s" s="2">
         <v>73</v>
@@ -44729,46 +44735,46 @@
         <v>73</v>
       </c>
       <c r="AC345" t="s" s="2">
-        <v>73</v>
+        <v>529</v>
       </c>
       <c r="AD345" t="s" s="2">
-        <v>73</v>
+        <v>530</v>
       </c>
       <c r="AE345" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AF345" t="s" s="2">
-        <v>73</v>
+        <v>531</v>
       </c>
       <c r="AG345" t="s" s="2">
-        <v>371</v>
+        <v>378</v>
       </c>
       <c r="AH345" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AI345" t="s" s="2">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="AJ345" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AK345" t="s" s="2">
-        <v>73</v>
+        <v>379</v>
       </c>
     </row>
     <row r="346">
       <c r="A346" t="s" s="2">
-        <v>850</v>
+        <v>853</v>
       </c>
       <c r="B346" t="s" s="2">
-        <v>949</v>
+        <v>948</v>
       </c>
       <c r="C346" t="s" s="2">
-        <v>949</v>
+        <v>948</v>
       </c>
       <c r="D346" s="2"/>
       <c r="E346" t="s" s="2">
-        <v>373</v>
+        <v>533</v>
       </c>
       <c r="F346" s="2"/>
       <c r="G346" t="s" s="2">
@@ -44781,24 +44787,26 @@
         <v>73</v>
       </c>
       <c r="J346" t="s" s="2">
-        <v>73</v>
+        <v>534</v>
       </c>
       <c r="K346" t="s" s="2">
-        <v>73</v>
+        <v>534</v>
       </c>
       <c r="L346" t="s" s="2">
         <v>374</v>
       </c>
       <c r="M346" t="s" s="2">
-        <v>375</v>
+        <v>535</v>
       </c>
       <c r="N346" t="s" s="2">
-        <v>528</v>
+        <v>536</v>
       </c>
       <c r="O346" t="s" s="2">
         <v>377</v>
       </c>
-      <c r="P346" s="2"/>
+      <c r="P346" t="s" s="2">
+        <v>537</v>
+      </c>
       <c r="Q346" t="s" s="2">
         <v>73</v>
       </c>
@@ -44834,19 +44842,19 @@
         <v>73</v>
       </c>
       <c r="AC346" t="s" s="2">
-        <v>529</v>
+        <v>73</v>
       </c>
       <c r="AD346" t="s" s="2">
-        <v>530</v>
+        <v>73</v>
       </c>
       <c r="AE346" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AF346" t="s" s="2">
-        <v>531</v>
+        <v>73</v>
       </c>
       <c r="AG346" t="s" s="2">
-        <v>378</v>
+        <v>538</v>
       </c>
       <c r="AH346" t="s" s="2">
         <v>74</v>
@@ -44863,49 +44871,45 @@
     </row>
     <row r="347">
       <c r="A347" t="s" s="2">
-        <v>850</v>
+        <v>853</v>
       </c>
       <c r="B347" t="s" s="2">
-        <v>950</v>
+        <v>949</v>
       </c>
       <c r="C347" t="s" s="2">
-        <v>950</v>
+        <v>949</v>
       </c>
       <c r="D347" s="2"/>
       <c r="E347" t="s" s="2">
-        <v>533</v>
+        <v>73</v>
       </c>
       <c r="F347" s="2"/>
       <c r="G347" t="s" s="2">
         <v>74</v>
       </c>
       <c r="H347" t="s" s="2">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="I347" t="s" s="2">
         <v>73</v>
       </c>
       <c r="J347" t="s" s="2">
-        <v>534</v>
+        <v>73</v>
       </c>
       <c r="K347" t="s" s="2">
-        <v>534</v>
+        <v>73</v>
       </c>
       <c r="L347" t="s" s="2">
-        <v>374</v>
+        <v>522</v>
       </c>
       <c r="M347" t="s" s="2">
-        <v>535</v>
+        <v>950</v>
       </c>
       <c r="N347" t="s" s="2">
-        <v>536</v>
-      </c>
-      <c r="O347" t="s" s="2">
-        <v>377</v>
-      </c>
-      <c r="P347" t="s" s="2">
-        <v>537</v>
-      </c>
+        <v>950</v>
+      </c>
+      <c r="O347" s="2"/>
+      <c r="P347" s="2"/>
       <c r="Q347" t="s" s="2">
         <v>73</v>
       </c>
@@ -44953,24 +44957,24 @@
         <v>73</v>
       </c>
       <c r="AG347" t="s" s="2">
-        <v>538</v>
+        <v>949</v>
       </c>
       <c r="AH347" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AI347" t="s" s="2">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="AJ347" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AK347" t="s" s="2">
-        <v>379</v>
+        <v>367</v>
       </c>
     </row>
     <row r="348">
       <c r="A348" t="s" s="2">
-        <v>850</v>
+        <v>853</v>
       </c>
       <c r="B348" t="s" s="2">
         <v>951</v>
@@ -44984,7 +44988,7 @@
       </c>
       <c r="F348" s="2"/>
       <c r="G348" t="s" s="2">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="H348" t="s" s="2">
         <v>79</v>
@@ -45002,10 +45006,10 @@
         <v>89</v>
       </c>
       <c r="M348" t="s" s="2">
-        <v>952</v>
+        <v>525</v>
       </c>
       <c r="N348" t="s" s="2">
-        <v>952</v>
+        <v>526</v>
       </c>
       <c r="O348" s="2"/>
       <c r="P348" s="2"/>
@@ -45056,10 +45060,10 @@
         <v>73</v>
       </c>
       <c r="AG348" t="s" s="2">
-        <v>951</v>
+        <v>371</v>
       </c>
       <c r="AH348" t="s" s="2">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="AI348" t="s" s="2">
         <v>79</v>
@@ -45073,24 +45077,24 @@
     </row>
     <row r="349">
       <c r="A349" t="s" s="2">
-        <v>850</v>
+        <v>853</v>
       </c>
       <c r="B349" t="s" s="2">
-        <v>953</v>
+        <v>952</v>
       </c>
       <c r="C349" t="s" s="2">
-        <v>953</v>
+        <v>952</v>
       </c>
       <c r="D349" s="2"/>
       <c r="E349" t="s" s="2">
-        <v>73</v>
+        <v>373</v>
       </c>
       <c r="F349" s="2"/>
       <c r="G349" t="s" s="2">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="H349" t="s" s="2">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="I349" t="s" s="2">
         <v>73</v>
@@ -45102,15 +45106,17 @@
         <v>73</v>
       </c>
       <c r="L349" t="s" s="2">
-        <v>89</v>
+        <v>374</v>
       </c>
       <c r="M349" t="s" s="2">
-        <v>954</v>
+        <v>375</v>
       </c>
       <c r="N349" t="s" s="2">
-        <v>954</v>
-      </c>
-      <c r="O349" s="2"/>
+        <v>528</v>
+      </c>
+      <c r="O349" t="s" s="2">
+        <v>377</v>
+      </c>
       <c r="P349" s="2"/>
       <c r="Q349" t="s" s="2">
         <v>73</v>
@@ -45147,74 +45153,78 @@
         <v>73</v>
       </c>
       <c r="AC349" t="s" s="2">
-        <v>73</v>
+        <v>529</v>
       </c>
       <c r="AD349" t="s" s="2">
-        <v>73</v>
+        <v>530</v>
       </c>
       <c r="AE349" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AF349" t="s" s="2">
-        <v>73</v>
+        <v>531</v>
       </c>
       <c r="AG349" t="s" s="2">
-        <v>953</v>
+        <v>378</v>
       </c>
       <c r="AH349" t="s" s="2">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="AI349" t="s" s="2">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="AJ349" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AK349" t="s" s="2">
-        <v>73</v>
+        <v>379</v>
       </c>
     </row>
     <row r="350">
       <c r="A350" t="s" s="2">
-        <v>850</v>
+        <v>853</v>
       </c>
       <c r="B350" t="s" s="2">
-        <v>955</v>
+        <v>953</v>
       </c>
       <c r="C350" t="s" s="2">
-        <v>955</v>
+        <v>953</v>
       </c>
       <c r="D350" s="2"/>
       <c r="E350" t="s" s="2">
-        <v>73</v>
+        <v>533</v>
       </c>
       <c r="F350" s="2"/>
       <c r="G350" t="s" s="2">
         <v>74</v>
       </c>
       <c r="H350" t="s" s="2">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="I350" t="s" s="2">
         <v>73</v>
       </c>
       <c r="J350" t="s" s="2">
-        <v>73</v>
+        <v>534</v>
       </c>
       <c r="K350" t="s" s="2">
-        <v>73</v>
+        <v>534</v>
       </c>
       <c r="L350" t="s" s="2">
-        <v>522</v>
+        <v>374</v>
       </c>
       <c r="M350" t="s" s="2">
-        <v>956</v>
+        <v>535</v>
       </c>
       <c r="N350" t="s" s="2">
-        <v>956</v>
-      </c>
-      <c r="O350" s="2"/>
-      <c r="P350" s="2"/>
+        <v>536</v>
+      </c>
+      <c r="O350" t="s" s="2">
+        <v>377</v>
+      </c>
+      <c r="P350" t="s" s="2">
+        <v>537</v>
+      </c>
       <c r="Q350" t="s" s="2">
         <v>73</v>
       </c>
@@ -45262,30 +45272,30 @@
         <v>73</v>
       </c>
       <c r="AG350" t="s" s="2">
-        <v>955</v>
+        <v>538</v>
       </c>
       <c r="AH350" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AI350" t="s" s="2">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="AJ350" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AK350" t="s" s="2">
-        <v>367</v>
+        <v>379</v>
       </c>
     </row>
     <row r="351">
       <c r="A351" t="s" s="2">
-        <v>850</v>
+        <v>853</v>
       </c>
       <c r="B351" t="s" s="2">
-        <v>957</v>
+        <v>954</v>
       </c>
       <c r="C351" t="s" s="2">
-        <v>957</v>
+        <v>954</v>
       </c>
       <c r="D351" s="2"/>
       <c r="E351" t="s" s="2">
@@ -45293,7 +45303,7 @@
       </c>
       <c r="F351" s="2"/>
       <c r="G351" t="s" s="2">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="H351" t="s" s="2">
         <v>79</v>
@@ -45311,10 +45321,10 @@
         <v>89</v>
       </c>
       <c r="M351" t="s" s="2">
-        <v>525</v>
+        <v>955</v>
       </c>
       <c r="N351" t="s" s="2">
-        <v>526</v>
+        <v>955</v>
       </c>
       <c r="O351" s="2"/>
       <c r="P351" s="2"/>
@@ -45365,10 +45375,10 @@
         <v>73</v>
       </c>
       <c r="AG351" t="s" s="2">
-        <v>371</v>
+        <v>954</v>
       </c>
       <c r="AH351" t="s" s="2">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="AI351" t="s" s="2">
         <v>79</v>
@@ -45382,24 +45392,24 @@
     </row>
     <row r="352">
       <c r="A352" t="s" s="2">
-        <v>850</v>
+        <v>853</v>
       </c>
       <c r="B352" t="s" s="2">
-        <v>958</v>
+        <v>956</v>
       </c>
       <c r="C352" t="s" s="2">
-        <v>958</v>
+        <v>956</v>
       </c>
       <c r="D352" s="2"/>
       <c r="E352" t="s" s="2">
-        <v>373</v>
+        <v>73</v>
       </c>
       <c r="F352" s="2"/>
       <c r="G352" t="s" s="2">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="H352" t="s" s="2">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="I352" t="s" s="2">
         <v>73</v>
@@ -45411,17 +45421,15 @@
         <v>73</v>
       </c>
       <c r="L352" t="s" s="2">
-        <v>374</v>
+        <v>89</v>
       </c>
       <c r="M352" t="s" s="2">
-        <v>375</v>
+        <v>957</v>
       </c>
       <c r="N352" t="s" s="2">
-        <v>528</v>
-      </c>
-      <c r="O352" t="s" s="2">
-        <v>377</v>
-      </c>
+        <v>957</v>
+      </c>
+      <c r="O352" s="2"/>
       <c r="P352" s="2"/>
       <c r="Q352" t="s" s="2">
         <v>73</v>
@@ -45458,78 +45466,74 @@
         <v>73</v>
       </c>
       <c r="AC352" t="s" s="2">
-        <v>529</v>
+        <v>73</v>
       </c>
       <c r="AD352" t="s" s="2">
-        <v>530</v>
+        <v>73</v>
       </c>
       <c r="AE352" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AF352" t="s" s="2">
-        <v>531</v>
+        <v>73</v>
       </c>
       <c r="AG352" t="s" s="2">
-        <v>378</v>
+        <v>956</v>
       </c>
       <c r="AH352" t="s" s="2">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="AI352" t="s" s="2">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="AJ352" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AK352" t="s" s="2">
-        <v>379</v>
+        <v>73</v>
       </c>
     </row>
     <row r="353">
       <c r="A353" t="s" s="2">
-        <v>850</v>
+        <v>853</v>
       </c>
       <c r="B353" t="s" s="2">
-        <v>959</v>
+        <v>958</v>
       </c>
       <c r="C353" t="s" s="2">
-        <v>959</v>
+        <v>958</v>
       </c>
       <c r="D353" s="2"/>
       <c r="E353" t="s" s="2">
-        <v>533</v>
+        <v>73</v>
       </c>
       <c r="F353" s="2"/>
       <c r="G353" t="s" s="2">
         <v>74</v>
       </c>
       <c r="H353" t="s" s="2">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="I353" t="s" s="2">
         <v>73</v>
       </c>
       <c r="J353" t="s" s="2">
-        <v>534</v>
+        <v>73</v>
       </c>
       <c r="K353" t="s" s="2">
-        <v>534</v>
+        <v>73</v>
       </c>
       <c r="L353" t="s" s="2">
-        <v>374</v>
+        <v>522</v>
       </c>
       <c r="M353" t="s" s="2">
-        <v>535</v>
+        <v>959</v>
       </c>
       <c r="N353" t="s" s="2">
-        <v>536</v>
-      </c>
-      <c r="O353" t="s" s="2">
-        <v>377</v>
-      </c>
-      <c r="P353" t="s" s="2">
-        <v>537</v>
-      </c>
+        <v>959</v>
+      </c>
+      <c r="O353" s="2"/>
+      <c r="P353" s="2"/>
       <c r="Q353" t="s" s="2">
         <v>73</v>
       </c>
@@ -45577,24 +45581,24 @@
         <v>73</v>
       </c>
       <c r="AG353" t="s" s="2">
-        <v>538</v>
+        <v>958</v>
       </c>
       <c r="AH353" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AI353" t="s" s="2">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="AJ353" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AK353" t="s" s="2">
-        <v>379</v>
+        <v>367</v>
       </c>
     </row>
     <row r="354">
       <c r="A354" t="s" s="2">
-        <v>850</v>
+        <v>853</v>
       </c>
       <c r="B354" t="s" s="2">
         <v>960</v>
@@ -45608,10 +45612,10 @@
       </c>
       <c r="F354" s="2"/>
       <c r="G354" t="s" s="2">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="H354" t="s" s="2">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="I354" t="s" s="2">
         <v>73</v>
@@ -45626,10 +45630,10 @@
         <v>89</v>
       </c>
       <c r="M354" t="s" s="2">
-        <v>961</v>
+        <v>525</v>
       </c>
       <c r="N354" t="s" s="2">
-        <v>961</v>
+        <v>526</v>
       </c>
       <c r="O354" s="2"/>
       <c r="P354" s="2"/>
@@ -45680,13 +45684,13 @@
         <v>73</v>
       </c>
       <c r="AG354" t="s" s="2">
-        <v>960</v>
+        <v>371</v>
       </c>
       <c r="AH354" t="s" s="2">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="AI354" t="s" s="2">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="AJ354" t="s" s="2">
         <v>73</v>
@@ -45697,24 +45701,24 @@
     </row>
     <row r="355">
       <c r="A355" t="s" s="2">
-        <v>850</v>
+        <v>853</v>
       </c>
       <c r="B355" t="s" s="2">
-        <v>962</v>
+        <v>961</v>
       </c>
       <c r="C355" t="s" s="2">
-        <v>962</v>
+        <v>961</v>
       </c>
       <c r="D355" s="2"/>
       <c r="E355" t="s" s="2">
-        <v>73</v>
+        <v>373</v>
       </c>
       <c r="F355" s="2"/>
       <c r="G355" t="s" s="2">
         <v>74</v>
       </c>
       <c r="H355" t="s" s="2">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="I355" t="s" s="2">
         <v>73</v>
@@ -45726,15 +45730,17 @@
         <v>73</v>
       </c>
       <c r="L355" t="s" s="2">
-        <v>522</v>
+        <v>374</v>
       </c>
       <c r="M355" t="s" s="2">
-        <v>963</v>
+        <v>375</v>
       </c>
       <c r="N355" t="s" s="2">
-        <v>963</v>
-      </c>
-      <c r="O355" s="2"/>
+        <v>528</v>
+      </c>
+      <c r="O355" t="s" s="2">
+        <v>377</v>
+      </c>
       <c r="P355" s="2"/>
       <c r="Q355" t="s" s="2">
         <v>73</v>
@@ -45771,74 +45777,78 @@
         <v>73</v>
       </c>
       <c r="AC355" t="s" s="2">
-        <v>73</v>
+        <v>529</v>
       </c>
       <c r="AD355" t="s" s="2">
-        <v>73</v>
+        <v>530</v>
       </c>
       <c r="AE355" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AF355" t="s" s="2">
-        <v>73</v>
+        <v>531</v>
       </c>
       <c r="AG355" t="s" s="2">
-        <v>962</v>
+        <v>378</v>
       </c>
       <c r="AH355" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AI355" t="s" s="2">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="AJ355" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AK355" t="s" s="2">
-        <v>367</v>
+        <v>379</v>
       </c>
     </row>
     <row r="356">
       <c r="A356" t="s" s="2">
-        <v>850</v>
+        <v>853</v>
       </c>
       <c r="B356" t="s" s="2">
-        <v>964</v>
+        <v>962</v>
       </c>
       <c r="C356" t="s" s="2">
-        <v>964</v>
+        <v>962</v>
       </c>
       <c r="D356" s="2"/>
       <c r="E356" t="s" s="2">
-        <v>73</v>
+        <v>533</v>
       </c>
       <c r="F356" s="2"/>
       <c r="G356" t="s" s="2">
         <v>74</v>
       </c>
       <c r="H356" t="s" s="2">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="I356" t="s" s="2">
         <v>73</v>
       </c>
       <c r="J356" t="s" s="2">
-        <v>73</v>
+        <v>534</v>
       </c>
       <c r="K356" t="s" s="2">
-        <v>73</v>
+        <v>534</v>
       </c>
       <c r="L356" t="s" s="2">
-        <v>89</v>
+        <v>374</v>
       </c>
       <c r="M356" t="s" s="2">
-        <v>525</v>
+        <v>535</v>
       </c>
       <c r="N356" t="s" s="2">
-        <v>526</v>
-      </c>
-      <c r="O356" s="2"/>
-      <c r="P356" s="2"/>
+        <v>536</v>
+      </c>
+      <c r="O356" t="s" s="2">
+        <v>377</v>
+      </c>
+      <c r="P356" t="s" s="2">
+        <v>537</v>
+      </c>
       <c r="Q356" t="s" s="2">
         <v>73</v>
       </c>
@@ -45886,38 +45896,38 @@
         <v>73</v>
       </c>
       <c r="AG356" t="s" s="2">
-        <v>371</v>
+        <v>538</v>
       </c>
       <c r="AH356" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AI356" t="s" s="2">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="AJ356" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AK356" t="s" s="2">
-        <v>73</v>
+        <v>379</v>
       </c>
     </row>
     <row r="357">
       <c r="A357" t="s" s="2">
-        <v>850</v>
+        <v>853</v>
       </c>
       <c r="B357" t="s" s="2">
-        <v>965</v>
+        <v>963</v>
       </c>
       <c r="C357" t="s" s="2">
-        <v>965</v>
+        <v>963</v>
       </c>
       <c r="D357" s="2"/>
       <c r="E357" t="s" s="2">
-        <v>373</v>
+        <v>73</v>
       </c>
       <c r="F357" s="2"/>
       <c r="G357" t="s" s="2">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="H357" t="s" s="2">
         <v>75</v>
@@ -45932,17 +45942,15 @@
         <v>73</v>
       </c>
       <c r="L357" t="s" s="2">
-        <v>374</v>
+        <v>89</v>
       </c>
       <c r="M357" t="s" s="2">
-        <v>375</v>
+        <v>964</v>
       </c>
       <c r="N357" t="s" s="2">
-        <v>528</v>
-      </c>
-      <c r="O357" t="s" s="2">
-        <v>377</v>
-      </c>
+        <v>964</v>
+      </c>
+      <c r="O357" s="2"/>
       <c r="P357" s="2"/>
       <c r="Q357" t="s" s="2">
         <v>73</v>
@@ -45979,22 +45987,22 @@
         <v>73</v>
       </c>
       <c r="AC357" t="s" s="2">
-        <v>529</v>
+        <v>73</v>
       </c>
       <c r="AD357" t="s" s="2">
-        <v>530</v>
+        <v>73</v>
       </c>
       <c r="AE357" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AF357" t="s" s="2">
-        <v>531</v>
+        <v>73</v>
       </c>
       <c r="AG357" t="s" s="2">
-        <v>378</v>
+        <v>963</v>
       </c>
       <c r="AH357" t="s" s="2">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="AI357" t="s" s="2">
         <v>75</v>
@@ -46003,54 +46011,50 @@
         <v>73</v>
       </c>
       <c r="AK357" t="s" s="2">
-        <v>379</v>
+        <v>73</v>
       </c>
     </row>
     <row r="358">
       <c r="A358" t="s" s="2">
-        <v>850</v>
+        <v>853</v>
       </c>
       <c r="B358" t="s" s="2">
-        <v>966</v>
+        <v>965</v>
       </c>
       <c r="C358" t="s" s="2">
-        <v>966</v>
+        <v>965</v>
       </c>
       <c r="D358" s="2"/>
       <c r="E358" t="s" s="2">
-        <v>533</v>
+        <v>73</v>
       </c>
       <c r="F358" s="2"/>
       <c r="G358" t="s" s="2">
         <v>74</v>
       </c>
       <c r="H358" t="s" s="2">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="I358" t="s" s="2">
         <v>73</v>
       </c>
       <c r="J358" t="s" s="2">
-        <v>534</v>
+        <v>73</v>
       </c>
       <c r="K358" t="s" s="2">
-        <v>534</v>
+        <v>73</v>
       </c>
       <c r="L358" t="s" s="2">
-        <v>374</v>
+        <v>522</v>
       </c>
       <c r="M358" t="s" s="2">
-        <v>535</v>
+        <v>966</v>
       </c>
       <c r="N358" t="s" s="2">
-        <v>536</v>
-      </c>
-      <c r="O358" t="s" s="2">
-        <v>377</v>
-      </c>
-      <c r="P358" t="s" s="2">
-        <v>537</v>
-      </c>
+        <v>966</v>
+      </c>
+      <c r="O358" s="2"/>
+      <c r="P358" s="2"/>
       <c r="Q358" t="s" s="2">
         <v>73</v>
       </c>
@@ -46098,24 +46102,24 @@
         <v>73</v>
       </c>
       <c r="AG358" t="s" s="2">
-        <v>538</v>
+        <v>965</v>
       </c>
       <c r="AH358" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AI358" t="s" s="2">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="AJ358" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AK358" t="s" s="2">
-        <v>379</v>
+        <v>367</v>
       </c>
     </row>
     <row r="359">
       <c r="A359" t="s" s="2">
-        <v>850</v>
+        <v>853</v>
       </c>
       <c r="B359" t="s" s="2">
         <v>967</v>
@@ -46132,7 +46136,7 @@
         <v>74</v>
       </c>
       <c r="H359" t="s" s="2">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="I359" t="s" s="2">
         <v>73</v>
@@ -46147,10 +46151,10 @@
         <v>89</v>
       </c>
       <c r="M359" t="s" s="2">
-        <v>968</v>
+        <v>525</v>
       </c>
       <c r="N359" t="s" s="2">
-        <v>968</v>
+        <v>526</v>
       </c>
       <c r="O359" s="2"/>
       <c r="P359" s="2"/>
@@ -46201,13 +46205,13 @@
         <v>73</v>
       </c>
       <c r="AG359" t="s" s="2">
-        <v>967</v>
+        <v>371</v>
       </c>
       <c r="AH359" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AI359" t="s" s="2">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="AJ359" t="s" s="2">
         <v>73</v>
@@ -46218,17 +46222,17 @@
     </row>
     <row r="360">
       <c r="A360" t="s" s="2">
-        <v>850</v>
+        <v>853</v>
       </c>
       <c r="B360" t="s" s="2">
-        <v>969</v>
+        <v>968</v>
       </c>
       <c r="C360" t="s" s="2">
-        <v>969</v>
+        <v>968</v>
       </c>
       <c r="D360" s="2"/>
       <c r="E360" t="s" s="2">
-        <v>73</v>
+        <v>373</v>
       </c>
       <c r="F360" s="2"/>
       <c r="G360" t="s" s="2">
@@ -46247,15 +46251,17 @@
         <v>73</v>
       </c>
       <c r="L360" t="s" s="2">
-        <v>89</v>
+        <v>374</v>
       </c>
       <c r="M360" t="s" s="2">
-        <v>970</v>
+        <v>375</v>
       </c>
       <c r="N360" t="s" s="2">
-        <v>970</v>
-      </c>
-      <c r="O360" s="2"/>
+        <v>528</v>
+      </c>
+      <c r="O360" t="s" s="2">
+        <v>377</v>
+      </c>
       <c r="P360" s="2"/>
       <c r="Q360" t="s" s="2">
         <v>73</v>
@@ -46292,19 +46298,19 @@
         <v>73</v>
       </c>
       <c r="AC360" t="s" s="2">
-        <v>73</v>
+        <v>529</v>
       </c>
       <c r="AD360" t="s" s="2">
-        <v>73</v>
+        <v>530</v>
       </c>
       <c r="AE360" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AF360" t="s" s="2">
-        <v>73</v>
+        <v>531</v>
       </c>
       <c r="AG360" t="s" s="2">
-        <v>969</v>
+        <v>378</v>
       </c>
       <c r="AH360" t="s" s="2">
         <v>74</v>
@@ -46316,50 +46322,54 @@
         <v>73</v>
       </c>
       <c r="AK360" t="s" s="2">
-        <v>73</v>
+        <v>379</v>
       </c>
     </row>
     <row r="361">
       <c r="A361" t="s" s="2">
-        <v>850</v>
+        <v>853</v>
       </c>
       <c r="B361" t="s" s="2">
-        <v>971</v>
+        <v>969</v>
       </c>
       <c r="C361" t="s" s="2">
-        <v>971</v>
+        <v>969</v>
       </c>
       <c r="D361" s="2"/>
       <c r="E361" t="s" s="2">
-        <v>73</v>
+        <v>533</v>
       </c>
       <c r="F361" s="2"/>
       <c r="G361" t="s" s="2">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="H361" t="s" s="2">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="I361" t="s" s="2">
         <v>73</v>
       </c>
       <c r="J361" t="s" s="2">
-        <v>73</v>
+        <v>534</v>
       </c>
       <c r="K361" t="s" s="2">
-        <v>73</v>
+        <v>534</v>
       </c>
       <c r="L361" t="s" s="2">
-        <v>522</v>
+        <v>374</v>
       </c>
       <c r="M361" t="s" s="2">
-        <v>972</v>
+        <v>535</v>
       </c>
       <c r="N361" t="s" s="2">
-        <v>972</v>
-      </c>
-      <c r="O361" s="2"/>
-      <c r="P361" s="2"/>
+        <v>536</v>
+      </c>
+      <c r="O361" t="s" s="2">
+        <v>377</v>
+      </c>
+      <c r="P361" t="s" s="2">
+        <v>537</v>
+      </c>
       <c r="Q361" t="s" s="2">
         <v>73</v>
       </c>
@@ -46407,30 +46417,30 @@
         <v>73</v>
       </c>
       <c r="AG361" t="s" s="2">
-        <v>971</v>
+        <v>538</v>
       </c>
       <c r="AH361" t="s" s="2">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="AI361" t="s" s="2">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="AJ361" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AK361" t="s" s="2">
-        <v>367</v>
+        <v>379</v>
       </c>
     </row>
     <row r="362">
       <c r="A362" t="s" s="2">
-        <v>850</v>
+        <v>853</v>
       </c>
       <c r="B362" t="s" s="2">
-        <v>973</v>
+        <v>970</v>
       </c>
       <c r="C362" t="s" s="2">
-        <v>973</v>
+        <v>970</v>
       </c>
       <c r="D362" s="2"/>
       <c r="E362" t="s" s="2">
@@ -46441,7 +46451,7 @@
         <v>74</v>
       </c>
       <c r="H362" t="s" s="2">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="I362" t="s" s="2">
         <v>73</v>
@@ -46456,10 +46466,10 @@
         <v>89</v>
       </c>
       <c r="M362" t="s" s="2">
-        <v>525</v>
+        <v>971</v>
       </c>
       <c r="N362" t="s" s="2">
-        <v>526</v>
+        <v>971</v>
       </c>
       <c r="O362" s="2"/>
       <c r="P362" s="2"/>
@@ -46510,13 +46520,13 @@
         <v>73</v>
       </c>
       <c r="AG362" t="s" s="2">
-        <v>371</v>
+        <v>970</v>
       </c>
       <c r="AH362" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AI362" t="s" s="2">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="AJ362" t="s" s="2">
         <v>73</v>
@@ -46527,17 +46537,17 @@
     </row>
     <row r="363">
       <c r="A363" t="s" s="2">
-        <v>850</v>
+        <v>853</v>
       </c>
       <c r="B363" t="s" s="2">
-        <v>974</v>
+        <v>972</v>
       </c>
       <c r="C363" t="s" s="2">
-        <v>974</v>
+        <v>972</v>
       </c>
       <c r="D363" s="2"/>
       <c r="E363" t="s" s="2">
-        <v>373</v>
+        <v>73</v>
       </c>
       <c r="F363" s="2"/>
       <c r="G363" t="s" s="2">
@@ -46556,17 +46566,15 @@
         <v>73</v>
       </c>
       <c r="L363" t="s" s="2">
-        <v>374</v>
+        <v>89</v>
       </c>
       <c r="M363" t="s" s="2">
-        <v>375</v>
+        <v>973</v>
       </c>
       <c r="N363" t="s" s="2">
-        <v>528</v>
-      </c>
-      <c r="O363" t="s" s="2">
-        <v>377</v>
-      </c>
+        <v>973</v>
+      </c>
+      <c r="O363" s="2"/>
       <c r="P363" s="2"/>
       <c r="Q363" t="s" s="2">
         <v>73</v>
@@ -46603,19 +46611,19 @@
         <v>73</v>
       </c>
       <c r="AC363" t="s" s="2">
-        <v>529</v>
+        <v>73</v>
       </c>
       <c r="AD363" t="s" s="2">
-        <v>530</v>
+        <v>73</v>
       </c>
       <c r="AE363" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AF363" t="s" s="2">
-        <v>531</v>
+        <v>73</v>
       </c>
       <c r="AG363" t="s" s="2">
-        <v>378</v>
+        <v>972</v>
       </c>
       <c r="AH363" t="s" s="2">
         <v>74</v>
@@ -46627,54 +46635,50 @@
         <v>73</v>
       </c>
       <c r="AK363" t="s" s="2">
-        <v>379</v>
+        <v>73</v>
       </c>
     </row>
     <row r="364">
       <c r="A364" t="s" s="2">
-        <v>850</v>
+        <v>853</v>
       </c>
       <c r="B364" t="s" s="2">
-        <v>975</v>
+        <v>974</v>
       </c>
       <c r="C364" t="s" s="2">
-        <v>975</v>
+        <v>974</v>
       </c>
       <c r="D364" s="2"/>
       <c r="E364" t="s" s="2">
-        <v>533</v>
+        <v>73</v>
       </c>
       <c r="F364" s="2"/>
       <c r="G364" t="s" s="2">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="H364" t="s" s="2">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="I364" t="s" s="2">
         <v>73</v>
       </c>
       <c r="J364" t="s" s="2">
-        <v>534</v>
+        <v>73</v>
       </c>
       <c r="K364" t="s" s="2">
-        <v>534</v>
+        <v>73</v>
       </c>
       <c r="L364" t="s" s="2">
-        <v>374</v>
+        <v>522</v>
       </c>
       <c r="M364" t="s" s="2">
-        <v>535</v>
+        <v>975</v>
       </c>
       <c r="N364" t="s" s="2">
-        <v>536</v>
-      </c>
-      <c r="O364" t="s" s="2">
-        <v>377</v>
-      </c>
-      <c r="P364" t="s" s="2">
-        <v>537</v>
-      </c>
+        <v>975</v>
+      </c>
+      <c r="O364" s="2"/>
+      <c r="P364" s="2"/>
       <c r="Q364" t="s" s="2">
         <v>73</v>
       </c>
@@ -46722,24 +46726,24 @@
         <v>73</v>
       </c>
       <c r="AG364" t="s" s="2">
-        <v>538</v>
+        <v>974</v>
       </c>
       <c r="AH364" t="s" s="2">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="AI364" t="s" s="2">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="AJ364" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AK364" t="s" s="2">
-        <v>379</v>
+        <v>367</v>
       </c>
     </row>
     <row r="365">
       <c r="A365" t="s" s="2">
-        <v>850</v>
+        <v>853</v>
       </c>
       <c r="B365" t="s" s="2">
         <v>976</v>
@@ -46753,7 +46757,7 @@
       </c>
       <c r="F365" s="2"/>
       <c r="G365" t="s" s="2">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="H365" t="s" s="2">
         <v>79</v>
@@ -46771,10 +46775,10 @@
         <v>89</v>
       </c>
       <c r="M365" t="s" s="2">
-        <v>977</v>
+        <v>525</v>
       </c>
       <c r="N365" t="s" s="2">
-        <v>977</v>
+        <v>526</v>
       </c>
       <c r="O365" s="2"/>
       <c r="P365" s="2"/>
@@ -46825,10 +46829,10 @@
         <v>73</v>
       </c>
       <c r="AG365" t="s" s="2">
-        <v>976</v>
+        <v>371</v>
       </c>
       <c r="AH365" t="s" s="2">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="AI365" t="s" s="2">
         <v>79</v>
@@ -46837,29 +46841,29 @@
         <v>73</v>
       </c>
       <c r="AK365" t="s" s="2">
-        <v>367</v>
+        <v>73</v>
       </c>
     </row>
     <row r="366">
       <c r="A366" t="s" s="2">
-        <v>850</v>
+        <v>853</v>
       </c>
       <c r="B366" t="s" s="2">
-        <v>978</v>
+        <v>977</v>
       </c>
       <c r="C366" t="s" s="2">
-        <v>978</v>
+        <v>977</v>
       </c>
       <c r="D366" s="2"/>
       <c r="E366" t="s" s="2">
-        <v>73</v>
+        <v>373</v>
       </c>
       <c r="F366" s="2"/>
       <c r="G366" t="s" s="2">
         <v>74</v>
       </c>
       <c r="H366" t="s" s="2">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="I366" t="s" s="2">
         <v>73</v>
@@ -46871,15 +46875,17 @@
         <v>73</v>
       </c>
       <c r="L366" t="s" s="2">
-        <v>89</v>
+        <v>374</v>
       </c>
       <c r="M366" t="s" s="2">
-        <v>369</v>
+        <v>375</v>
       </c>
       <c r="N366" t="s" s="2">
-        <v>370</v>
-      </c>
-      <c r="O366" s="2"/>
+        <v>528</v>
+      </c>
+      <c r="O366" t="s" s="2">
+        <v>377</v>
+      </c>
       <c r="P366" s="2"/>
       <c r="Q366" t="s" s="2">
         <v>73</v>
@@ -46916,46 +46922,46 @@
         <v>73</v>
       </c>
       <c r="AC366" t="s" s="2">
-        <v>73</v>
+        <v>529</v>
       </c>
       <c r="AD366" t="s" s="2">
-        <v>73</v>
+        <v>530</v>
       </c>
       <c r="AE366" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AF366" t="s" s="2">
-        <v>73</v>
+        <v>531</v>
       </c>
       <c r="AG366" t="s" s="2">
-        <v>371</v>
+        <v>378</v>
       </c>
       <c r="AH366" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AI366" t="s" s="2">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="AJ366" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AK366" t="s" s="2">
-        <v>73</v>
+        <v>379</v>
       </c>
     </row>
     <row r="367">
       <c r="A367" t="s" s="2">
-        <v>850</v>
+        <v>853</v>
       </c>
       <c r="B367" t="s" s="2">
-        <v>979</v>
+        <v>978</v>
       </c>
       <c r="C367" t="s" s="2">
-        <v>979</v>
+        <v>978</v>
       </c>
       <c r="D367" s="2"/>
       <c r="E367" t="s" s="2">
-        <v>373</v>
+        <v>533</v>
       </c>
       <c r="F367" s="2"/>
       <c r="G367" t="s" s="2">
@@ -46968,24 +46974,26 @@
         <v>73</v>
       </c>
       <c r="J367" t="s" s="2">
-        <v>73</v>
+        <v>534</v>
       </c>
       <c r="K367" t="s" s="2">
-        <v>73</v>
+        <v>534</v>
       </c>
       <c r="L367" t="s" s="2">
         <v>374</v>
       </c>
       <c r="M367" t="s" s="2">
-        <v>375</v>
+        <v>535</v>
       </c>
       <c r="N367" t="s" s="2">
-        <v>376</v>
+        <v>536</v>
       </c>
       <c r="O367" t="s" s="2">
         <v>377</v>
       </c>
-      <c r="P367" s="2"/>
+      <c r="P367" t="s" s="2">
+        <v>537</v>
+      </c>
       <c r="Q367" t="s" s="2">
         <v>73</v>
       </c>
@@ -47033,7 +47041,7 @@
         <v>73</v>
       </c>
       <c r="AG367" t="s" s="2">
-        <v>378</v>
+        <v>538</v>
       </c>
       <c r="AH367" t="s" s="2">
         <v>74</v>
@@ -47050,13 +47058,13 @@
     </row>
     <row r="368">
       <c r="A368" t="s" s="2">
-        <v>850</v>
+        <v>853</v>
       </c>
       <c r="B368" t="s" s="2">
-        <v>980</v>
+        <v>979</v>
       </c>
       <c r="C368" t="s" s="2">
-        <v>980</v>
+        <v>979</v>
       </c>
       <c r="D368" s="2"/>
       <c r="E368" t="s" s="2">
@@ -47064,7 +47072,7 @@
       </c>
       <c r="F368" s="2"/>
       <c r="G368" t="s" s="2">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="H368" t="s" s="2">
         <v>79</v>
@@ -47082,10 +47090,10 @@
         <v>89</v>
       </c>
       <c r="M368" t="s" s="2">
-        <v>381</v>
+        <v>980</v>
       </c>
       <c r="N368" t="s" s="2">
-        <v>382</v>
+        <v>980</v>
       </c>
       <c r="O368" s="2"/>
       <c r="P368" s="2"/>
@@ -47109,7 +47117,7 @@
         <v>73</v>
       </c>
       <c r="X368" t="s" s="2">
-        <v>383</v>
+        <v>73</v>
       </c>
       <c r="Y368" t="s" s="2">
         <v>73</v>
@@ -47136,10 +47144,10 @@
         <v>73</v>
       </c>
       <c r="AG368" t="s" s="2">
-        <v>380</v>
+        <v>979</v>
       </c>
       <c r="AH368" t="s" s="2">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="AI368" t="s" s="2">
         <v>79</v>
@@ -47148,12 +47156,12 @@
         <v>73</v>
       </c>
       <c r="AK368" t="s" s="2">
-        <v>73</v>
+        <v>367</v>
       </c>
     </row>
     <row r="369">
       <c r="A369" t="s" s="2">
-        <v>850</v>
+        <v>853</v>
       </c>
       <c r="B369" t="s" s="2">
         <v>981</v>
@@ -47167,10 +47175,10 @@
       </c>
       <c r="F369" s="2"/>
       <c r="G369" t="s" s="2">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="H369" t="s" s="2">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="I369" t="s" s="2">
         <v>73</v>
@@ -47182,13 +47190,13 @@
         <v>73</v>
       </c>
       <c r="L369" t="s" s="2">
-        <v>522</v>
+        <v>89</v>
       </c>
       <c r="M369" t="s" s="2">
-        <v>982</v>
+        <v>369</v>
       </c>
       <c r="N369" t="s" s="2">
-        <v>982</v>
+        <v>370</v>
       </c>
       <c r="O369" s="2"/>
       <c r="P369" s="2"/>
@@ -47239,41 +47247,41 @@
         <v>73</v>
       </c>
       <c r="AG369" t="s" s="2">
-        <v>981</v>
+        <v>371</v>
       </c>
       <c r="AH369" t="s" s="2">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="AI369" t="s" s="2">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="AJ369" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AK369" t="s" s="2">
-        <v>367</v>
+        <v>73</v>
       </c>
     </row>
     <row r="370">
       <c r="A370" t="s" s="2">
-        <v>850</v>
+        <v>853</v>
       </c>
       <c r="B370" t="s" s="2">
-        <v>983</v>
+        <v>982</v>
       </c>
       <c r="C370" t="s" s="2">
-        <v>983</v>
+        <v>982</v>
       </c>
       <c r="D370" s="2"/>
       <c r="E370" t="s" s="2">
-        <v>73</v>
+        <v>373</v>
       </c>
       <c r="F370" s="2"/>
       <c r="G370" t="s" s="2">
         <v>74</v>
       </c>
       <c r="H370" t="s" s="2">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="I370" t="s" s="2">
         <v>73</v>
@@ -47285,15 +47293,17 @@
         <v>73</v>
       </c>
       <c r="L370" t="s" s="2">
-        <v>89</v>
+        <v>374</v>
       </c>
       <c r="M370" t="s" s="2">
-        <v>525</v>
+        <v>375</v>
       </c>
       <c r="N370" t="s" s="2">
-        <v>526</v>
-      </c>
-      <c r="O370" s="2"/>
+        <v>376</v>
+      </c>
+      <c r="O370" t="s" s="2">
+        <v>377</v>
+      </c>
       <c r="P370" s="2"/>
       <c r="Q370" t="s" s="2">
         <v>73</v>
@@ -47342,41 +47352,41 @@
         <v>73</v>
       </c>
       <c r="AG370" t="s" s="2">
-        <v>371</v>
+        <v>378</v>
       </c>
       <c r="AH370" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AI370" t="s" s="2">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="AJ370" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AK370" t="s" s="2">
-        <v>73</v>
+        <v>379</v>
       </c>
     </row>
     <row r="371">
       <c r="A371" t="s" s="2">
-        <v>850</v>
+        <v>853</v>
       </c>
       <c r="B371" t="s" s="2">
-        <v>984</v>
+        <v>983</v>
       </c>
       <c r="C371" t="s" s="2">
-        <v>984</v>
+        <v>983</v>
       </c>
       <c r="D371" s="2"/>
       <c r="E371" t="s" s="2">
-        <v>373</v>
+        <v>73</v>
       </c>
       <c r="F371" s="2"/>
       <c r="G371" t="s" s="2">
         <v>74</v>
       </c>
       <c r="H371" t="s" s="2">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="I371" t="s" s="2">
         <v>73</v>
@@ -47388,17 +47398,15 @@
         <v>73</v>
       </c>
       <c r="L371" t="s" s="2">
-        <v>374</v>
+        <v>89</v>
       </c>
       <c r="M371" t="s" s="2">
-        <v>375</v>
+        <v>381</v>
       </c>
       <c r="N371" t="s" s="2">
-        <v>528</v>
-      </c>
-      <c r="O371" t="s" s="2">
-        <v>377</v>
-      </c>
+        <v>382</v>
+      </c>
+      <c r="O371" s="2"/>
       <c r="P371" s="2"/>
       <c r="Q371" t="s" s="2">
         <v>73</v>
@@ -47420,7 +47428,7 @@
         <v>73</v>
       </c>
       <c r="X371" t="s" s="2">
-        <v>73</v>
+        <v>383</v>
       </c>
       <c r="Y371" t="s" s="2">
         <v>73</v>
@@ -47435,50 +47443,50 @@
         <v>73</v>
       </c>
       <c r="AC371" t="s" s="2">
-        <v>529</v>
+        <v>73</v>
       </c>
       <c r="AD371" t="s" s="2">
-        <v>530</v>
+        <v>73</v>
       </c>
       <c r="AE371" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AF371" t="s" s="2">
-        <v>531</v>
+        <v>73</v>
       </c>
       <c r="AG371" t="s" s="2">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="AH371" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AI371" t="s" s="2">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="AJ371" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AK371" t="s" s="2">
-        <v>379</v>
+        <v>73</v>
       </c>
     </row>
     <row r="372">
       <c r="A372" t="s" s="2">
-        <v>850</v>
+        <v>853</v>
       </c>
       <c r="B372" t="s" s="2">
-        <v>985</v>
+        <v>984</v>
       </c>
       <c r="C372" t="s" s="2">
-        <v>985</v>
+        <v>984</v>
       </c>
       <c r="D372" s="2"/>
       <c r="E372" t="s" s="2">
-        <v>533</v>
+        <v>73</v>
       </c>
       <c r="F372" s="2"/>
       <c r="G372" t="s" s="2">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="H372" t="s" s="2">
         <v>75</v>
@@ -47487,26 +47495,22 @@
         <v>73</v>
       </c>
       <c r="J372" t="s" s="2">
-        <v>534</v>
+        <v>73</v>
       </c>
       <c r="K372" t="s" s="2">
-        <v>534</v>
+        <v>73</v>
       </c>
       <c r="L372" t="s" s="2">
-        <v>374</v>
+        <v>522</v>
       </c>
       <c r="M372" t="s" s="2">
-        <v>535</v>
+        <v>985</v>
       </c>
       <c r="N372" t="s" s="2">
-        <v>536</v>
-      </c>
-      <c r="O372" t="s" s="2">
-        <v>377</v>
-      </c>
-      <c r="P372" t="s" s="2">
-        <v>537</v>
-      </c>
+        <v>985</v>
+      </c>
+      <c r="O372" s="2"/>
+      <c r="P372" s="2"/>
       <c r="Q372" t="s" s="2">
         <v>73</v>
       </c>
@@ -47554,10 +47558,10 @@
         <v>73</v>
       </c>
       <c r="AG372" t="s" s="2">
-        <v>538</v>
+        <v>984</v>
       </c>
       <c r="AH372" t="s" s="2">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="AI372" t="s" s="2">
         <v>75</v>
@@ -47566,12 +47570,12 @@
         <v>73</v>
       </c>
       <c r="AK372" t="s" s="2">
-        <v>379</v>
+        <v>367</v>
       </c>
     </row>
     <row r="373">
       <c r="A373" t="s" s="2">
-        <v>850</v>
+        <v>853</v>
       </c>
       <c r="B373" t="s" s="2">
         <v>986</v>
@@ -47585,7 +47589,7 @@
       </c>
       <c r="F373" s="2"/>
       <c r="G373" t="s" s="2">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="H373" t="s" s="2">
         <v>79</v>
@@ -47603,10 +47607,10 @@
         <v>89</v>
       </c>
       <c r="M373" t="s" s="2">
-        <v>987</v>
+        <v>525</v>
       </c>
       <c r="N373" t="s" s="2">
-        <v>987</v>
+        <v>526</v>
       </c>
       <c r="O373" s="2"/>
       <c r="P373" s="2"/>
@@ -47657,10 +47661,10 @@
         <v>73</v>
       </c>
       <c r="AG373" t="s" s="2">
-        <v>986</v>
+        <v>371</v>
       </c>
       <c r="AH373" t="s" s="2">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="AI373" t="s" s="2">
         <v>79</v>
@@ -47674,24 +47678,24 @@
     </row>
     <row r="374">
       <c r="A374" t="s" s="2">
-        <v>850</v>
+        <v>853</v>
       </c>
       <c r="B374" t="s" s="2">
-        <v>988</v>
+        <v>987</v>
       </c>
       <c r="C374" t="s" s="2">
-        <v>988</v>
+        <v>987</v>
       </c>
       <c r="D374" s="2"/>
       <c r="E374" t="s" s="2">
-        <v>73</v>
+        <v>373</v>
       </c>
       <c r="F374" s="2"/>
       <c r="G374" t="s" s="2">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="H374" t="s" s="2">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="I374" t="s" s="2">
         <v>73</v>
@@ -47703,15 +47707,17 @@
         <v>73</v>
       </c>
       <c r="L374" t="s" s="2">
-        <v>89</v>
+        <v>374</v>
       </c>
       <c r="M374" t="s" s="2">
-        <v>871</v>
+        <v>375</v>
       </c>
       <c r="N374" t="s" s="2">
-        <v>871</v>
-      </c>
-      <c r="O374" s="2"/>
+        <v>528</v>
+      </c>
+      <c r="O374" t="s" s="2">
+        <v>377</v>
+      </c>
       <c r="P374" s="2"/>
       <c r="Q374" t="s" s="2">
         <v>73</v>
@@ -47748,74 +47754,78 @@
         <v>73</v>
       </c>
       <c r="AC374" t="s" s="2">
-        <v>73</v>
+        <v>529</v>
       </c>
       <c r="AD374" t="s" s="2">
-        <v>73</v>
+        <v>530</v>
       </c>
       <c r="AE374" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AF374" t="s" s="2">
-        <v>73</v>
+        <v>531</v>
       </c>
       <c r="AG374" t="s" s="2">
-        <v>988</v>
+        <v>378</v>
       </c>
       <c r="AH374" t="s" s="2">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="AI374" t="s" s="2">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="AJ374" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AK374" t="s" s="2">
-        <v>73</v>
+        <v>379</v>
       </c>
     </row>
     <row r="375">
       <c r="A375" t="s" s="2">
-        <v>850</v>
+        <v>853</v>
       </c>
       <c r="B375" t="s" s="2">
-        <v>989</v>
+        <v>988</v>
       </c>
       <c r="C375" t="s" s="2">
-        <v>989</v>
+        <v>988</v>
       </c>
       <c r="D375" s="2"/>
       <c r="E375" t="s" s="2">
-        <v>73</v>
+        <v>533</v>
       </c>
       <c r="F375" s="2"/>
       <c r="G375" t="s" s="2">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="H375" t="s" s="2">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="I375" t="s" s="2">
         <v>73</v>
       </c>
       <c r="J375" t="s" s="2">
-        <v>73</v>
+        <v>534</v>
       </c>
       <c r="K375" t="s" s="2">
-        <v>73</v>
+        <v>534</v>
       </c>
       <c r="L375" t="s" s="2">
-        <v>89</v>
+        <v>374</v>
       </c>
       <c r="M375" t="s" s="2">
-        <v>873</v>
+        <v>535</v>
       </c>
       <c r="N375" t="s" s="2">
-        <v>873</v>
-      </c>
-      <c r="O375" s="2"/>
-      <c r="P375" s="2"/>
+        <v>536</v>
+      </c>
+      <c r="O375" t="s" s="2">
+        <v>377</v>
+      </c>
+      <c r="P375" t="s" s="2">
+        <v>537</v>
+      </c>
       <c r="Q375" t="s" s="2">
         <v>73</v>
       </c>
@@ -47863,30 +47873,30 @@
         <v>73</v>
       </c>
       <c r="AG375" t="s" s="2">
-        <v>989</v>
+        <v>538</v>
       </c>
       <c r="AH375" t="s" s="2">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="AI375" t="s" s="2">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="AJ375" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AK375" t="s" s="2">
-        <v>73</v>
+        <v>379</v>
       </c>
     </row>
     <row r="376">
       <c r="A376" t="s" s="2">
-        <v>990</v>
+        <v>853</v>
       </c>
       <c r="B376" t="s" s="2">
-        <v>990</v>
+        <v>989</v>
       </c>
       <c r="C376" t="s" s="2">
-        <v>990</v>
+        <v>989</v>
       </c>
       <c r="D376" s="2"/>
       <c r="E376" t="s" s="2">
@@ -47894,10 +47904,10 @@
       </c>
       <c r="F376" s="2"/>
       <c r="G376" t="s" s="2">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="H376" t="s" s="2">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="I376" t="s" s="2">
         <v>73</v>
@@ -47909,13 +47919,13 @@
         <v>73</v>
       </c>
       <c r="L376" t="s" s="2">
-        <v>76</v>
+        <v>89</v>
       </c>
       <c r="M376" t="s" s="2">
-        <v>993</v>
+        <v>990</v>
       </c>
       <c r="N376" t="s" s="2">
-        <v>994</v>
+        <v>990</v>
       </c>
       <c r="O376" s="2"/>
       <c r="P376" s="2"/>
@@ -47966,13 +47976,13 @@
         <v>73</v>
       </c>
       <c r="AG376" t="s" s="2">
-        <v>77</v>
+        <v>989</v>
       </c>
       <c r="AH376" t="s" s="2">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="AI376" t="s" s="2">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="AJ376" t="s" s="2">
         <v>73</v>
@@ -47983,13 +47993,13 @@
     </row>
     <row r="377">
       <c r="A377" t="s" s="2">
-        <v>990</v>
+        <v>853</v>
       </c>
       <c r="B377" t="s" s="2">
-        <v>995</v>
+        <v>991</v>
       </c>
       <c r="C377" t="s" s="2">
-        <v>995</v>
+        <v>991</v>
       </c>
       <c r="D377" s="2"/>
       <c r="E377" t="s" s="2">
@@ -48015,10 +48025,10 @@
         <v>89</v>
       </c>
       <c r="M377" t="s" s="2">
-        <v>996</v>
+        <v>874</v>
       </c>
       <c r="N377" t="s" s="2">
-        <v>996</v>
+        <v>874</v>
       </c>
       <c r="O377" s="2"/>
       <c r="P377" s="2"/>
@@ -48069,7 +48079,7 @@
         <v>73</v>
       </c>
       <c r="AG377" t="s" s="2">
-        <v>995</v>
+        <v>991</v>
       </c>
       <c r="AH377" t="s" s="2">
         <v>79</v>
@@ -48086,13 +48096,13 @@
     </row>
     <row r="378">
       <c r="A378" t="s" s="2">
-        <v>990</v>
+        <v>853</v>
       </c>
       <c r="B378" t="s" s="2">
-        <v>997</v>
+        <v>992</v>
       </c>
       <c r="C378" t="s" s="2">
-        <v>997</v>
+        <v>992</v>
       </c>
       <c r="D378" s="2"/>
       <c r="E378" t="s" s="2">
@@ -48118,10 +48128,10 @@
         <v>89</v>
       </c>
       <c r="M378" t="s" s="2">
-        <v>998</v>
+        <v>876</v>
       </c>
       <c r="N378" t="s" s="2">
-        <v>998</v>
+        <v>876</v>
       </c>
       <c r="O378" s="2"/>
       <c r="P378" s="2"/>
@@ -48172,7 +48182,7 @@
         <v>73</v>
       </c>
       <c r="AG378" t="s" s="2">
-        <v>997</v>
+        <v>992</v>
       </c>
       <c r="AH378" t="s" s="2">
         <v>79</v>
@@ -48189,13 +48199,13 @@
     </row>
     <row r="379">
       <c r="A379" t="s" s="2">
-        <v>990</v>
+        <v>993</v>
       </c>
       <c r="B379" t="s" s="2">
-        <v>999</v>
+        <v>993</v>
       </c>
       <c r="C379" t="s" s="2">
-        <v>999</v>
+        <v>993</v>
       </c>
       <c r="D379" s="2"/>
       <c r="E379" t="s" s="2">
@@ -48206,7 +48216,7 @@
         <v>74</v>
       </c>
       <c r="H379" t="s" s="2">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="I379" t="s" s="2">
         <v>73</v>
@@ -48218,13 +48228,13 @@
         <v>73</v>
       </c>
       <c r="L379" t="s" s="2">
-        <v>300</v>
+        <v>76</v>
       </c>
       <c r="M379" t="s" s="2">
-        <v>1000</v>
+        <v>996</v>
       </c>
       <c r="N379" t="s" s="2">
-        <v>1000</v>
+        <v>997</v>
       </c>
       <c r="O379" s="2"/>
       <c r="P379" s="2"/>
@@ -48275,18 +48285,327 @@
         <v>73</v>
       </c>
       <c r="AG379" t="s" s="2">
-        <v>999</v>
+        <v>77</v>
       </c>
       <c r="AH379" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AI379" t="s" s="2">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="AJ379" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AK379" t="s" s="2">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="380">
+      <c r="A380" t="s" s="2">
+        <v>993</v>
+      </c>
+      <c r="B380" t="s" s="2">
+        <v>998</v>
+      </c>
+      <c r="C380" t="s" s="2">
+        <v>998</v>
+      </c>
+      <c r="D380" s="2"/>
+      <c r="E380" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="F380" s="2"/>
+      <c r="G380" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="H380" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="I380" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="J380" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="K380" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="L380" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="M380" t="s" s="2">
+        <v>999</v>
+      </c>
+      <c r="N380" t="s" s="2">
+        <v>999</v>
+      </c>
+      <c r="O380" s="2"/>
+      <c r="P380" s="2"/>
+      <c r="Q380" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="R380" s="2"/>
+      <c r="S380" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="T380" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="U380" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="V380" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="W380" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="X380" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Y380" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Z380" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AA380" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AB380" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AC380" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AD380" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AE380" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AF380" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AG380" t="s" s="2">
+        <v>998</v>
+      </c>
+      <c r="AH380" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AI380" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AJ380" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AK380" t="s" s="2">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="381">
+      <c r="A381" t="s" s="2">
+        <v>993</v>
+      </c>
+      <c r="B381" t="s" s="2">
+        <v>1000</v>
+      </c>
+      <c r="C381" t="s" s="2">
+        <v>1000</v>
+      </c>
+      <c r="D381" s="2"/>
+      <c r="E381" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="F381" s="2"/>
+      <c r="G381" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="H381" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="I381" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="J381" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="K381" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="L381" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="M381" t="s" s="2">
+        <v>1001</v>
+      </c>
+      <c r="N381" t="s" s="2">
+        <v>1001</v>
+      </c>
+      <c r="O381" s="2"/>
+      <c r="P381" s="2"/>
+      <c r="Q381" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="R381" s="2"/>
+      <c r="S381" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="T381" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="U381" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="V381" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="W381" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="X381" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Y381" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Z381" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AA381" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AB381" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AC381" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AD381" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AE381" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AF381" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AG381" t="s" s="2">
+        <v>1000</v>
+      </c>
+      <c r="AH381" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AI381" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AJ381" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AK381" t="s" s="2">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="382">
+      <c r="A382" t="s" s="2">
+        <v>993</v>
+      </c>
+      <c r="B382" t="s" s="2">
+        <v>1002</v>
+      </c>
+      <c r="C382" t="s" s="2">
+        <v>1002</v>
+      </c>
+      <c r="D382" s="2"/>
+      <c r="E382" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="F382" s="2"/>
+      <c r="G382" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="H382" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="I382" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="J382" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="K382" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="L382" t="s" s="2">
+        <v>300</v>
+      </c>
+      <c r="M382" t="s" s="2">
+        <v>1003</v>
+      </c>
+      <c r="N382" t="s" s="2">
+        <v>1003</v>
+      </c>
+      <c r="O382" s="2"/>
+      <c r="P382" s="2"/>
+      <c r="Q382" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="R382" s="2"/>
+      <c r="S382" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="T382" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="U382" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="V382" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="W382" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="X382" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Y382" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Z382" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AA382" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AB382" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AC382" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AD382" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AE382" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AF382" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AG382" t="s" s="2">
+        <v>1002</v>
+      </c>
+      <c r="AH382" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AI382" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AJ382" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AK382" t="s" s="2">
         <v>73</v>
       </c>
     </row>

--- a/spec-tech/ig/all-profiles.xlsx
+++ b/spec-tech/ig/all-profiles.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-15T16:11:54+00:00</t>
+    <t>2026-07-16T08:21:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/spec-tech/ig/all-profiles.xlsx
+++ b/spec-tech/ig/all-profiles.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-16T08:21:58+00:00</t>
+    <t>2026-07-16T08:46:36+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/spec-tech/ig/all-profiles.xlsx
+++ b/spec-tech/ig/all-profiles.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-16T08:46:36+00:00</t>
+    <t>2026-07-16T10:52:32+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/spec-tech/ig/all-profiles.xlsx
+++ b/spec-tech/ig/all-profiles.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-16T10:52:32+00:00</t>
+    <t>2026-07-16T11:12:17+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/spec-tech/ig/all-profiles.xlsx
+++ b/spec-tech/ig/all-profiles.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-16T21:31:30+00:00</t>
+    <t>2026-07-17T08:00:04+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -42558,7 +42558,7 @@
         <v>79</v>
       </c>
       <c r="H319" t="s" s="2">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="I319" t="s" s="2">
         <v>73</v>
@@ -42633,7 +42633,7 @@
         <v>79</v>
       </c>
       <c r="AI319" t="s" s="2">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="AJ319" t="s" s="2">
         <v>73</v>
@@ -42973,7 +42973,7 @@
       </c>
       <c r="F323" s="2"/>
       <c r="G323" t="s" s="2">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="H323" t="s" s="2">
         <v>79</v>
@@ -43048,7 +43048,7 @@
         <v>916</v>
       </c>
       <c r="AH323" t="s" s="2">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="AI323" t="s" s="2">
         <v>79</v>
@@ -44221,7 +44221,7 @@
       </c>
       <c r="F335" s="2"/>
       <c r="G335" t="s" s="2">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="H335" t="s" s="2">
         <v>79</v>
@@ -44296,7 +44296,7 @@
         <v>932</v>
       </c>
       <c r="AH335" t="s" s="2">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="AI335" t="s" s="2">
         <v>79</v>

--- a/spec-tech/ig/all-profiles.xlsx
+++ b/spec-tech/ig/all-profiles.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-17T08:00:04+00:00</t>
+    <t>2026-07-17T11:25:46+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/spec-tech/ig/all-profiles.xlsx
+++ b/spec-tech/ig/all-profiles.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-17T11:25:46+00:00</t>
+    <t>2026-07-17T14:49:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/spec-tech/ig/all-profiles.xlsx
+++ b/spec-tech/ig/all-profiles.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-19T17:20:25+00:00</t>
+    <t>2026-07-21T08:40:48+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/spec-tech/ig/all-profiles.xlsx
+++ b/spec-tech/ig/all-profiles.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-21T08:40:48+00:00</t>
+    <t>2026-07-21T15:50:20+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/spec-tech/ig/all-profiles.xlsx
+++ b/spec-tech/ig/all-profiles.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-21T15:50:20+00:00</t>
+    <t>2026-07-21T16:28:50+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/spec-tech/ig/all-profiles.xlsx
+++ b/spec-tech/ig/all-profiles.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-21T16:28:50+00:00</t>
+    <t>2026-07-21T16:53:48+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/spec-tech/ig/all-profiles.xlsx
+++ b/spec-tech/ig/all-profiles.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-22T08:07:11+00:00</t>
+    <t>2026-07-22T10:39:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/spec-tech/ig/all-profiles.xlsx
+++ b/spec-tech/ig/all-profiles.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-22T17:16:50+00:00</t>
+    <t>2026-07-23T08:53:51+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/spec-tech/ig/all-profiles.xlsx
+++ b/spec-tech/ig/all-profiles.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18160" uniqueCount="1215">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18160" uniqueCount="1216">
   <si>
     <t>Property</t>
   </si>
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-23T16:03:49+00:00</t>
+    <t>2026-07-23T16:11:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1186,7 +1186,7 @@
 </t>
   </si>
   <si>
-    <t>Identification nationale de l'Entité juridique initiée pour les besoins du SI-CPS. Cette identification est obtenue par la concaténation du type d'identifiant national de structure (provenant de la nomenclature CodeSystem-TRE-G07-TypeIdentifiantStructure) et de l'identifiant de la structure:** 1 + N° FINESS (entité juridique et entité géographique indéterminées);** 2 + N° Siren.Cas particulier:La notion d’identifiant d'entité juridique n'a pas de sens métier pour un cabinet individuel ou un cabinet de groupe identifié par un RPPS-Rang ou un ADELI-rang (cf. Attribut IdentifiantEG de la classe EntiteGeographique). Si un cas d'usage nécessite d'appliquer la notion générique d'entité juridique et d'entité géographique pour un cabinet individuel ou un cabinet de groupe, alors l'identifiant de l'entité juridique est constitué de la façon suivante: ** pour le cabinet d’un PS ADELI : 0 + IdentifiantEJ;** pour le cabinet d’un PS RPPS : 4 + IdentifiantEJ. Synonyme : Struct_IdNat (CI-SIS).</t>
+    <t>Identification nationale de l'Entité juridique initiée pour les besoins du SI-CPS.</t>
   </si>
   <si>
     <t>pdlgcIndex.raisonSociale</t>
@@ -2498,7 +2498,11 @@
     <t>pdlgcSystem.lgcIdentifiant</t>
   </si>
   <si>
-    <t>SystIdNat</t>
+    <t xml:space="preserve">https://interop.esante.gouv.fr/ig/fhir/pdlgc/StructureDefinition/systIdNat
+</t>
+  </si>
+  <si>
+    <t>Identifiant du système</t>
   </si>
   <si>
     <t>psIdNat</t>
@@ -2572,6 +2576,9 @@
     <t>https://interop.esante.gouv.fr/ig/fhir/pdlgc/StructureDefinition/systIdNat</t>
   </si>
   <si>
+    <t>SystIdNat</t>
+  </si>
+  <si>
     <t xml:space="preserve">Identification d'un systeme
 L’identification du systeme  est construite selon le tableau dessous :
 - 1 + Identifiant cabinet ADELI/Identifiant interne du système dans la structure 
@@ -2878,10 +2885,6 @@
   </si>
   <si>
     <t>xdmActorSystem.XCN1.value[x]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://interop.esante.gouv.fr/ig/fhir/pdlgc/StructureDefinition/systIdNat
-</t>
   </si>
   <si>
     <t>xdmActorSystem.XCN2</t>
@@ -6216,7 +6219,7 @@
         <v>2</v>
       </c>
       <c r="B296" t="s" s="2">
-        <v>811</v>
+        <v>812</v>
       </c>
     </row>
     <row r="297">
@@ -6224,7 +6227,7 @@
         <v>4</v>
       </c>
       <c r="B297" t="s" s="2">
-        <v>812</v>
+        <v>813</v>
       </c>
     </row>
     <row r="298">
@@ -6240,7 +6243,7 @@
         <v>8</v>
       </c>
       <c r="B299" t="s" s="2">
-        <v>813</v>
+        <v>814</v>
       </c>
     </row>
     <row r="300">
@@ -6248,7 +6251,7 @@
         <v>10</v>
       </c>
       <c r="B300" t="s" s="2">
-        <v>813</v>
+        <v>814</v>
       </c>
     </row>
     <row r="301">
@@ -6302,7 +6305,7 @@
         <v>23</v>
       </c>
       <c r="B307" t="s" s="2">
-        <v>814</v>
+        <v>815</v>
       </c>
     </row>
     <row r="308">
@@ -6338,7 +6341,7 @@
         <v>31</v>
       </c>
       <c r="B312" t="s" s="2">
-        <v>812</v>
+        <v>813</v>
       </c>
     </row>
     <row r="313">
@@ -6378,7 +6381,7 @@
         <v>2</v>
       </c>
       <c r="B317" t="s" s="2">
-        <v>817</v>
+        <v>818</v>
       </c>
     </row>
     <row r="318">
@@ -6386,7 +6389,7 @@
         <v>4</v>
       </c>
       <c r="B318" t="s" s="2">
-        <v>818</v>
+        <v>819</v>
       </c>
     </row>
     <row r="319">
@@ -6402,7 +6405,7 @@
         <v>8</v>
       </c>
       <c r="B320" t="s" s="2">
-        <v>819</v>
+        <v>820</v>
       </c>
     </row>
     <row r="321">
@@ -6410,7 +6413,7 @@
         <v>10</v>
       </c>
       <c r="B321" t="s" s="2">
-        <v>819</v>
+        <v>820</v>
       </c>
     </row>
     <row r="322">
@@ -6464,7 +6467,7 @@
         <v>23</v>
       </c>
       <c r="B328" t="s" s="2">
-        <v>820</v>
+        <v>821</v>
       </c>
     </row>
     <row r="329">
@@ -6500,7 +6503,7 @@
         <v>31</v>
       </c>
       <c r="B333" t="s" s="2">
-        <v>818</v>
+        <v>819</v>
       </c>
     </row>
     <row r="334">
@@ -6540,7 +6543,7 @@
         <v>2</v>
       </c>
       <c r="B338" t="s" s="2">
-        <v>822</v>
+        <v>823</v>
       </c>
     </row>
     <row r="339">
@@ -6548,7 +6551,7 @@
         <v>4</v>
       </c>
       <c r="B339" t="s" s="2">
-        <v>823</v>
+        <v>824</v>
       </c>
     </row>
     <row r="340">
@@ -6564,7 +6567,7 @@
         <v>8</v>
       </c>
       <c r="B341" t="s" s="2">
-        <v>824</v>
+        <v>825</v>
       </c>
     </row>
     <row r="342">
@@ -6572,7 +6575,7 @@
         <v>10</v>
       </c>
       <c r="B342" t="s" s="2">
-        <v>824</v>
+        <v>825</v>
       </c>
     </row>
     <row r="343">
@@ -6626,7 +6629,7 @@
         <v>23</v>
       </c>
       <c r="B349" t="s" s="2">
-        <v>825</v>
+        <v>826</v>
       </c>
     </row>
     <row r="350">
@@ -6662,7 +6665,7 @@
         <v>31</v>
       </c>
       <c r="B354" t="s" s="2">
-        <v>823</v>
+        <v>824</v>
       </c>
     </row>
     <row r="355">
@@ -6702,7 +6705,7 @@
         <v>2</v>
       </c>
       <c r="B359" t="s" s="2">
-        <v>827</v>
+        <v>828</v>
       </c>
     </row>
     <row r="360">
@@ -6710,7 +6713,7 @@
         <v>4</v>
       </c>
       <c r="B360" t="s" s="2">
-        <v>828</v>
+        <v>829</v>
       </c>
     </row>
     <row r="361">
@@ -6726,7 +6729,7 @@
         <v>8</v>
       </c>
       <c r="B362" t="s" s="2">
-        <v>810</v>
+        <v>830</v>
       </c>
     </row>
     <row r="363">
@@ -6734,7 +6737,7 @@
         <v>10</v>
       </c>
       <c r="B363" t="s" s="2">
-        <v>810</v>
+        <v>830</v>
       </c>
     </row>
     <row r="364">
@@ -6788,7 +6791,7 @@
         <v>23</v>
       </c>
       <c r="B370" t="s" s="2">
-        <v>829</v>
+        <v>831</v>
       </c>
     </row>
     <row r="371">
@@ -6824,7 +6827,7 @@
         <v>31</v>
       </c>
       <c r="B375" t="s" s="2">
-        <v>828</v>
+        <v>829</v>
       </c>
     </row>
     <row r="376">
@@ -6864,7 +6867,7 @@
         <v>2</v>
       </c>
       <c r="B380" t="s" s="2">
-        <v>832</v>
+        <v>834</v>
       </c>
     </row>
     <row r="381">
@@ -6872,7 +6875,7 @@
         <v>4</v>
       </c>
       <c r="B381" t="s" s="2">
-        <v>833</v>
+        <v>835</v>
       </c>
     </row>
     <row r="382">
@@ -6888,7 +6891,7 @@
         <v>8</v>
       </c>
       <c r="B383" t="s" s="2">
-        <v>834</v>
+        <v>836</v>
       </c>
     </row>
     <row r="384">
@@ -6896,7 +6899,7 @@
         <v>10</v>
       </c>
       <c r="B384" t="s" s="2">
-        <v>835</v>
+        <v>837</v>
       </c>
     </row>
     <row r="385">
@@ -6950,7 +6953,7 @@
         <v>23</v>
       </c>
       <c r="B391" t="s" s="2">
-        <v>836</v>
+        <v>838</v>
       </c>
     </row>
     <row r="392">
@@ -6986,7 +6989,7 @@
         <v>31</v>
       </c>
       <c r="B396" t="s" s="2">
-        <v>833</v>
+        <v>835</v>
       </c>
     </row>
     <row r="397">
@@ -6994,7 +6997,7 @@
         <v>32</v>
       </c>
       <c r="B397" t="s" s="2">
-        <v>837</v>
+        <v>839</v>
       </c>
     </row>
     <row r="398">
@@ -7026,7 +7029,7 @@
         <v>2</v>
       </c>
       <c r="B401" t="s" s="2">
-        <v>876</v>
+        <v>878</v>
       </c>
     </row>
     <row r="402">
@@ -7034,7 +7037,7 @@
         <v>4</v>
       </c>
       <c r="B402" t="s" s="2">
-        <v>877</v>
+        <v>879</v>
       </c>
     </row>
     <row r="403">
@@ -7050,7 +7053,7 @@
         <v>8</v>
       </c>
       <c r="B404" t="s" s="2">
-        <v>878</v>
+        <v>880</v>
       </c>
     </row>
     <row r="405">
@@ -7058,7 +7061,7 @@
         <v>10</v>
       </c>
       <c r="B405" t="s" s="2">
-        <v>879</v>
+        <v>881</v>
       </c>
     </row>
     <row r="406">
@@ -7112,7 +7115,7 @@
         <v>23</v>
       </c>
       <c r="B412" t="s" s="2">
-        <v>880</v>
+        <v>882</v>
       </c>
     </row>
     <row r="413">
@@ -7148,7 +7151,7 @@
         <v>31</v>
       </c>
       <c r="B417" t="s" s="2">
-        <v>877</v>
+        <v>879</v>
       </c>
     </row>
     <row r="418">
@@ -7156,7 +7159,7 @@
         <v>32</v>
       </c>
       <c r="B418" t="s" s="2">
-        <v>837</v>
+        <v>839</v>
       </c>
     </row>
     <row r="419">
@@ -7188,7 +7191,7 @@
         <v>2</v>
       </c>
       <c r="B422" t="s" s="2">
-        <v>897</v>
+        <v>899</v>
       </c>
     </row>
     <row r="423">
@@ -7196,7 +7199,7 @@
         <v>4</v>
       </c>
       <c r="B423" t="s" s="2">
-        <v>898</v>
+        <v>900</v>
       </c>
     </row>
     <row r="424">
@@ -7212,7 +7215,7 @@
         <v>8</v>
       </c>
       <c r="B425" t="s" s="2">
-        <v>899</v>
+        <v>901</v>
       </c>
     </row>
     <row r="426">
@@ -7220,7 +7223,7 @@
         <v>10</v>
       </c>
       <c r="B426" t="s" s="2">
-        <v>900</v>
+        <v>902</v>
       </c>
     </row>
     <row r="427">
@@ -7274,7 +7277,7 @@
         <v>23</v>
       </c>
       <c r="B433" t="s" s="2">
-        <v>901</v>
+        <v>903</v>
       </c>
     </row>
     <row r="434">
@@ -7310,7 +7313,7 @@
         <v>31</v>
       </c>
       <c r="B438" t="s" s="2">
-        <v>898</v>
+        <v>900</v>
       </c>
     </row>
     <row r="439">
@@ -7318,7 +7321,7 @@
         <v>32</v>
       </c>
       <c r="B439" t="s" s="2">
-        <v>837</v>
+        <v>839</v>
       </c>
     </row>
     <row r="440">
@@ -7350,7 +7353,7 @@
         <v>2</v>
       </c>
       <c r="B443" t="s" s="2">
-        <v>920</v>
+        <v>922</v>
       </c>
     </row>
     <row r="444">
@@ -7358,7 +7361,7 @@
         <v>4</v>
       </c>
       <c r="B444" t="s" s="2">
-        <v>921</v>
+        <v>923</v>
       </c>
     </row>
     <row r="445">
@@ -7374,7 +7377,7 @@
         <v>8</v>
       </c>
       <c r="B446" t="s" s="2">
-        <v>922</v>
+        <v>924</v>
       </c>
     </row>
     <row r="447">
@@ -7382,7 +7385,7 @@
         <v>10</v>
       </c>
       <c r="B447" t="s" s="2">
-        <v>923</v>
+        <v>925</v>
       </c>
     </row>
     <row r="448">
@@ -7436,7 +7439,7 @@
         <v>23</v>
       </c>
       <c r="B454" t="s" s="2">
-        <v>924</v>
+        <v>926</v>
       </c>
     </row>
     <row r="455">
@@ -7472,7 +7475,7 @@
         <v>31</v>
       </c>
       <c r="B459" t="s" s="2">
-        <v>921</v>
+        <v>923</v>
       </c>
     </row>
     <row r="460">
@@ -7480,7 +7483,7 @@
         <v>32</v>
       </c>
       <c r="B460" t="s" s="2">
-        <v>837</v>
+        <v>839</v>
       </c>
     </row>
     <row r="461">
@@ -7512,7 +7515,7 @@
         <v>2</v>
       </c>
       <c r="B464" t="s" s="2">
-        <v>937</v>
+        <v>938</v>
       </c>
     </row>
     <row r="465">
@@ -7520,7 +7523,7 @@
         <v>4</v>
       </c>
       <c r="B465" t="s" s="2">
-        <v>938</v>
+        <v>939</v>
       </c>
     </row>
     <row r="466">
@@ -7536,7 +7539,7 @@
         <v>8</v>
       </c>
       <c r="B467" t="s" s="2">
-        <v>939</v>
+        <v>940</v>
       </c>
     </row>
     <row r="468">
@@ -7544,7 +7547,7 @@
         <v>10</v>
       </c>
       <c r="B468" t="s" s="2">
-        <v>940</v>
+        <v>941</v>
       </c>
     </row>
     <row r="469">
@@ -7598,7 +7601,7 @@
         <v>23</v>
       </c>
       <c r="B475" t="s" s="2">
-        <v>941</v>
+        <v>942</v>
       </c>
     </row>
     <row r="476">
@@ -7634,7 +7637,7 @@
         <v>31</v>
       </c>
       <c r="B480" t="s" s="2">
-        <v>938</v>
+        <v>939</v>
       </c>
     </row>
     <row r="481">
@@ -7674,7 +7677,7 @@
         <v>2</v>
       </c>
       <c r="B485" t="s" s="2">
-        <v>942</v>
+        <v>943</v>
       </c>
     </row>
     <row r="486">
@@ -7682,7 +7685,7 @@
         <v>4</v>
       </c>
       <c r="B486" t="s" s="2">
-        <v>943</v>
+        <v>944</v>
       </c>
     </row>
     <row r="487">
@@ -7698,7 +7701,7 @@
         <v>8</v>
       </c>
       <c r="B488" t="s" s="2">
-        <v>944</v>
+        <v>945</v>
       </c>
     </row>
     <row r="489">
@@ -7706,7 +7709,7 @@
         <v>10</v>
       </c>
       <c r="B489" t="s" s="2">
-        <v>945</v>
+        <v>946</v>
       </c>
     </row>
     <row r="490">
@@ -7760,7 +7763,7 @@
         <v>23</v>
       </c>
       <c r="B496" t="s" s="2">
-        <v>946</v>
+        <v>947</v>
       </c>
     </row>
     <row r="497">
@@ -7796,7 +7799,7 @@
         <v>31</v>
       </c>
       <c r="B501" t="s" s="2">
-        <v>943</v>
+        <v>944</v>
       </c>
     </row>
     <row r="502">
@@ -7836,7 +7839,7 @@
         <v>2</v>
       </c>
       <c r="B506" t="s" s="2">
-        <v>950</v>
+        <v>951</v>
       </c>
     </row>
     <row r="507">
@@ -7844,7 +7847,7 @@
         <v>4</v>
       </c>
       <c r="B507" t="s" s="2">
-        <v>951</v>
+        <v>952</v>
       </c>
     </row>
     <row r="508">
@@ -7860,7 +7863,7 @@
         <v>8</v>
       </c>
       <c r="B509" t="s" s="2">
-        <v>952</v>
+        <v>953</v>
       </c>
     </row>
     <row r="510">
@@ -7868,7 +7871,7 @@
         <v>10</v>
       </c>
       <c r="B510" t="s" s="2">
-        <v>953</v>
+        <v>954</v>
       </c>
     </row>
     <row r="511">
@@ -7922,7 +7925,7 @@
         <v>23</v>
       </c>
       <c r="B517" t="s" s="2">
-        <v>954</v>
+        <v>955</v>
       </c>
     </row>
     <row r="518">
@@ -7958,7 +7961,7 @@
         <v>31</v>
       </c>
       <c r="B522" t="s" s="2">
-        <v>951</v>
+        <v>952</v>
       </c>
     </row>
     <row r="523">
@@ -7998,7 +8001,7 @@
         <v>2</v>
       </c>
       <c r="B527" t="s" s="2">
-        <v>963</v>
+        <v>964</v>
       </c>
     </row>
     <row r="528">
@@ -8006,7 +8009,7 @@
         <v>4</v>
       </c>
       <c r="B528" t="s" s="2">
-        <v>964</v>
+        <v>965</v>
       </c>
     </row>
     <row r="529">
@@ -8022,7 +8025,7 @@
         <v>8</v>
       </c>
       <c r="B530" t="s" s="2">
-        <v>965</v>
+        <v>966</v>
       </c>
     </row>
     <row r="531">
@@ -8030,7 +8033,7 @@
         <v>10</v>
       </c>
       <c r="B531" t="s" s="2">
-        <v>966</v>
+        <v>967</v>
       </c>
     </row>
     <row r="532">
@@ -8084,7 +8087,7 @@
         <v>23</v>
       </c>
       <c r="B538" t="s" s="2">
-        <v>967</v>
+        <v>968</v>
       </c>
     </row>
     <row r="539">
@@ -8120,7 +8123,7 @@
         <v>31</v>
       </c>
       <c r="B543" t="s" s="2">
-        <v>964</v>
+        <v>965</v>
       </c>
     </row>
     <row r="544">
@@ -8160,7 +8163,7 @@
         <v>2</v>
       </c>
       <c r="B548" t="s" s="2">
-        <v>983</v>
+        <v>984</v>
       </c>
     </row>
     <row r="549">
@@ -8168,7 +8171,7 @@
         <v>4</v>
       </c>
       <c r="B549" t="s" s="2">
-        <v>984</v>
+        <v>985</v>
       </c>
     </row>
     <row r="550">
@@ -8184,7 +8187,7 @@
         <v>8</v>
       </c>
       <c r="B551" t="s" s="2">
-        <v>985</v>
+        <v>986</v>
       </c>
     </row>
     <row r="552">
@@ -8192,7 +8195,7 @@
         <v>10</v>
       </c>
       <c r="B552" t="s" s="2">
-        <v>986</v>
+        <v>987</v>
       </c>
     </row>
     <row r="553">
@@ -8246,7 +8249,7 @@
         <v>23</v>
       </c>
       <c r="B559" t="s" s="2">
-        <v>987</v>
+        <v>988</v>
       </c>
     </row>
     <row r="560">
@@ -8282,7 +8285,7 @@
         <v>31</v>
       </c>
       <c r="B564" t="s" s="2">
-        <v>984</v>
+        <v>985</v>
       </c>
     </row>
     <row r="565">
@@ -8290,7 +8293,7 @@
         <v>32</v>
       </c>
       <c r="B565" t="s" s="2">
-        <v>988</v>
+        <v>989</v>
       </c>
     </row>
     <row r="566">
@@ -8322,7 +8325,7 @@
         <v>2</v>
       </c>
       <c r="B569" t="s" s="2">
-        <v>996</v>
+        <v>997</v>
       </c>
     </row>
     <row r="570">
@@ -8330,7 +8333,7 @@
         <v>4</v>
       </c>
       <c r="B570" t="s" s="2">
-        <v>997</v>
+        <v>998</v>
       </c>
     </row>
     <row r="571">
@@ -8346,7 +8349,7 @@
         <v>8</v>
       </c>
       <c r="B572" t="s" s="2">
-        <v>998</v>
+        <v>999</v>
       </c>
     </row>
     <row r="573">
@@ -8354,7 +8357,7 @@
         <v>10</v>
       </c>
       <c r="B573" t="s" s="2">
-        <v>999</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="574">
@@ -8408,7 +8411,7 @@
         <v>23</v>
       </c>
       <c r="B580" t="s" s="2">
-        <v>1000</v>
+        <v>1001</v>
       </c>
     </row>
     <row r="581">
@@ -8444,7 +8447,7 @@
         <v>31</v>
       </c>
       <c r="B585" t="s" s="2">
-        <v>997</v>
+        <v>998</v>
       </c>
     </row>
     <row r="586">
@@ -8484,7 +8487,7 @@
         <v>2</v>
       </c>
       <c r="B590" t="s" s="2">
-        <v>1014</v>
+        <v>1015</v>
       </c>
     </row>
     <row r="591">
@@ -8492,7 +8495,7 @@
         <v>4</v>
       </c>
       <c r="B591" t="s" s="2">
-        <v>1015</v>
+        <v>1016</v>
       </c>
     </row>
     <row r="592">
@@ -8508,7 +8511,7 @@
         <v>8</v>
       </c>
       <c r="B593" t="s" s="2">
-        <v>1016</v>
+        <v>1017</v>
       </c>
     </row>
     <row r="594">
@@ -8516,7 +8519,7 @@
         <v>10</v>
       </c>
       <c r="B594" t="s" s="2">
-        <v>1017</v>
+        <v>1018</v>
       </c>
     </row>
     <row r="595">
@@ -8570,7 +8573,7 @@
         <v>23</v>
       </c>
       <c r="B601" t="s" s="2">
-        <v>1018</v>
+        <v>1019</v>
       </c>
     </row>
     <row r="602">
@@ -8606,7 +8609,7 @@
         <v>31</v>
       </c>
       <c r="B606" t="s" s="2">
-        <v>1015</v>
+        <v>1016</v>
       </c>
     </row>
     <row r="607">
@@ -8614,7 +8617,7 @@
         <v>32</v>
       </c>
       <c r="B607" t="s" s="2">
-        <v>988</v>
+        <v>989</v>
       </c>
     </row>
     <row r="608">
@@ -8646,7 +8649,7 @@
         <v>2</v>
       </c>
       <c r="B611" t="s" s="2">
-        <v>1026</v>
+        <v>1027</v>
       </c>
     </row>
     <row r="612">
@@ -8654,7 +8657,7 @@
         <v>4</v>
       </c>
       <c r="B612" t="s" s="2">
-        <v>1027</v>
+        <v>1028</v>
       </c>
     </row>
     <row r="613">
@@ -8670,7 +8673,7 @@
         <v>8</v>
       </c>
       <c r="B614" t="s" s="2">
-        <v>1028</v>
+        <v>1029</v>
       </c>
     </row>
     <row r="615">
@@ -8678,7 +8681,7 @@
         <v>10</v>
       </c>
       <c r="B615" t="s" s="2">
-        <v>1029</v>
+        <v>1030</v>
       </c>
     </row>
     <row r="616">
@@ -8732,7 +8735,7 @@
         <v>23</v>
       </c>
       <c r="B622" t="s" s="2">
-        <v>1030</v>
+        <v>1031</v>
       </c>
     </row>
     <row r="623">
@@ -8768,7 +8771,7 @@
         <v>31</v>
       </c>
       <c r="B627" t="s" s="2">
-        <v>1027</v>
+        <v>1028</v>
       </c>
     </row>
     <row r="628">
@@ -8808,7 +8811,7 @@
         <v>2</v>
       </c>
       <c r="B632" t="s" s="2">
-        <v>1122</v>
+        <v>1123</v>
       </c>
     </row>
     <row r="633">
@@ -8816,7 +8819,7 @@
         <v>4</v>
       </c>
       <c r="B633" t="s" s="2">
-        <v>1123</v>
+        <v>1124</v>
       </c>
     </row>
     <row r="634">
@@ -8832,7 +8835,7 @@
         <v>8</v>
       </c>
       <c r="B635" t="s" s="2">
-        <v>1124</v>
+        <v>1125</v>
       </c>
     </row>
     <row r="636">
@@ -8840,7 +8843,7 @@
         <v>10</v>
       </c>
       <c r="B636" t="s" s="2">
-        <v>1125</v>
+        <v>1126</v>
       </c>
     </row>
     <row r="637">
@@ -8894,7 +8897,7 @@
         <v>23</v>
       </c>
       <c r="B643" t="s" s="2">
-        <v>1126</v>
+        <v>1127</v>
       </c>
     </row>
     <row r="644">
@@ -8930,7 +8933,7 @@
         <v>31</v>
       </c>
       <c r="B648" t="s" s="2">
-        <v>1123</v>
+        <v>1124</v>
       </c>
     </row>
     <row r="649">
@@ -8970,7 +8973,7 @@
         <v>2</v>
       </c>
       <c r="B653" t="s" s="2">
-        <v>1129</v>
+        <v>1130</v>
       </c>
     </row>
     <row r="654">
@@ -8978,7 +8981,7 @@
         <v>4</v>
       </c>
       <c r="B654" t="s" s="2">
-        <v>1130</v>
+        <v>1131</v>
       </c>
     </row>
     <row r="655">
@@ -8994,7 +8997,7 @@
         <v>8</v>
       </c>
       <c r="B656" t="s" s="2">
-        <v>1131</v>
+        <v>1132</v>
       </c>
     </row>
     <row r="657">
@@ -9002,7 +9005,7 @@
         <v>10</v>
       </c>
       <c r="B657" t="s" s="2">
-        <v>1132</v>
+        <v>1133</v>
       </c>
     </row>
     <row r="658">
@@ -9056,7 +9059,7 @@
         <v>23</v>
       </c>
       <c r="B664" t="s" s="2">
-        <v>1133</v>
+        <v>1134</v>
       </c>
     </row>
     <row r="665">
@@ -9092,7 +9095,7 @@
         <v>31</v>
       </c>
       <c r="B669" t="s" s="2">
-        <v>1130</v>
+        <v>1131</v>
       </c>
     </row>
     <row r="670">
@@ -9132,7 +9135,7 @@
         <v>2</v>
       </c>
       <c r="B674" t="s" s="2">
-        <v>1135</v>
+        <v>1136</v>
       </c>
     </row>
     <row r="675">
@@ -9140,7 +9143,7 @@
         <v>4</v>
       </c>
       <c r="B675" t="s" s="2">
-        <v>1136</v>
+        <v>1137</v>
       </c>
     </row>
     <row r="676">
@@ -9156,7 +9159,7 @@
         <v>8</v>
       </c>
       <c r="B677" t="s" s="2">
-        <v>1137</v>
+        <v>1138</v>
       </c>
     </row>
     <row r="678">
@@ -9164,7 +9167,7 @@
         <v>10</v>
       </c>
       <c r="B678" t="s" s="2">
-        <v>1138</v>
+        <v>1139</v>
       </c>
     </row>
     <row r="679">
@@ -9218,7 +9221,7 @@
         <v>23</v>
       </c>
       <c r="B685" t="s" s="2">
-        <v>1139</v>
+        <v>1140</v>
       </c>
     </row>
     <row r="686">
@@ -9254,7 +9257,7 @@
         <v>31</v>
       </c>
       <c r="B690" t="s" s="2">
-        <v>1136</v>
+        <v>1137</v>
       </c>
     </row>
     <row r="691">
@@ -9294,7 +9297,7 @@
         <v>2</v>
       </c>
       <c r="B695" t="s" s="2">
-        <v>1146</v>
+        <v>1147</v>
       </c>
     </row>
     <row r="696">
@@ -9302,7 +9305,7 @@
         <v>4</v>
       </c>
       <c r="B696" t="s" s="2">
-        <v>1147</v>
+        <v>1148</v>
       </c>
     </row>
     <row r="697">
@@ -9318,7 +9321,7 @@
         <v>8</v>
       </c>
       <c r="B698" t="s" s="2">
-        <v>1148</v>
+        <v>1149</v>
       </c>
     </row>
     <row r="699">
@@ -9326,7 +9329,7 @@
         <v>10</v>
       </c>
       <c r="B699" t="s" s="2">
-        <v>1149</v>
+        <v>1150</v>
       </c>
     </row>
     <row r="700">
@@ -9380,7 +9383,7 @@
         <v>23</v>
       </c>
       <c r="B706" t="s" s="2">
-        <v>1150</v>
+        <v>1151</v>
       </c>
     </row>
     <row r="707">
@@ -9416,7 +9419,7 @@
         <v>31</v>
       </c>
       <c r="B711" t="s" s="2">
-        <v>1147</v>
+        <v>1148</v>
       </c>
     </row>
     <row r="712">
@@ -9456,7 +9459,7 @@
         <v>2</v>
       </c>
       <c r="B716" t="s" s="2">
-        <v>1156</v>
+        <v>1157</v>
       </c>
     </row>
     <row r="717">
@@ -9464,7 +9467,7 @@
         <v>4</v>
       </c>
       <c r="B717" t="s" s="2">
-        <v>1157</v>
+        <v>1158</v>
       </c>
     </row>
     <row r="718">
@@ -9480,7 +9483,7 @@
         <v>8</v>
       </c>
       <c r="B719" t="s" s="2">
-        <v>1158</v>
+        <v>1159</v>
       </c>
     </row>
     <row r="720">
@@ -9488,7 +9491,7 @@
         <v>10</v>
       </c>
       <c r="B720" t="s" s="2">
-        <v>1159</v>
+        <v>1160</v>
       </c>
     </row>
     <row r="721">
@@ -9542,7 +9545,7 @@
         <v>23</v>
       </c>
       <c r="B727" t="s" s="2">
-        <v>1160</v>
+        <v>1161</v>
       </c>
     </row>
     <row r="728">
@@ -9578,7 +9581,7 @@
         <v>31</v>
       </c>
       <c r="B732" t="s" s="2">
-        <v>1157</v>
+        <v>1158</v>
       </c>
     </row>
     <row r="733">
@@ -9618,7 +9621,7 @@
         <v>2</v>
       </c>
       <c r="B737" t="s" s="2">
-        <v>1183</v>
+        <v>1184</v>
       </c>
     </row>
     <row r="738">
@@ -9626,7 +9629,7 @@
         <v>4</v>
       </c>
       <c r="B738" t="s" s="2">
-        <v>1184</v>
+        <v>1185</v>
       </c>
     </row>
     <row r="739">
@@ -9642,7 +9645,7 @@
         <v>8</v>
       </c>
       <c r="B740" t="s" s="2">
-        <v>1185</v>
+        <v>1186</v>
       </c>
     </row>
     <row r="741">
@@ -9650,7 +9653,7 @@
         <v>10</v>
       </c>
       <c r="B741" t="s" s="2">
-        <v>1186</v>
+        <v>1187</v>
       </c>
     </row>
     <row r="742">
@@ -9704,7 +9707,7 @@
         <v>23</v>
       </c>
       <c r="B748" t="s" s="2">
-        <v>1187</v>
+        <v>1188</v>
       </c>
     </row>
     <row r="749">
@@ -9740,7 +9743,7 @@
         <v>31</v>
       </c>
       <c r="B753" t="s" s="2">
-        <v>1184</v>
+        <v>1185</v>
       </c>
     </row>
     <row r="754">
@@ -46567,13 +46570,13 @@
         <v>74</v>
       </c>
       <c r="L355" t="s" s="2">
-        <v>187</v>
+        <v>810</v>
       </c>
       <c r="M355" t="s" s="2">
-        <v>810</v>
+        <v>811</v>
       </c>
       <c r="N355" t="s" s="2">
-        <v>810</v>
+        <v>811</v>
       </c>
       <c r="O355" s="2"/>
       <c r="P355" s="2"/>
@@ -46641,13 +46644,13 @@
     </row>
     <row r="356">
       <c r="A356" t="s" s="2">
-        <v>811</v>
+        <v>812</v>
       </c>
       <c r="B356" t="s" s="2">
-        <v>811</v>
+        <v>812</v>
       </c>
       <c r="C356" t="s" s="2">
-        <v>811</v>
+        <v>812</v>
       </c>
       <c r="D356" s="2"/>
       <c r="E356" t="s" s="2">
@@ -46673,10 +46676,10 @@
         <v>77</v>
       </c>
       <c r="M356" t="s" s="2">
-        <v>813</v>
+        <v>814</v>
       </c>
       <c r="N356" t="s" s="2">
-        <v>814</v>
+        <v>815</v>
       </c>
       <c r="O356" s="2"/>
       <c r="P356" s="2"/>
@@ -46744,13 +46747,13 @@
     </row>
     <row r="357">
       <c r="A357" t="s" s="2">
-        <v>811</v>
+        <v>812</v>
       </c>
       <c r="B357" t="s" s="2">
-        <v>815</v>
+        <v>816</v>
       </c>
       <c r="C357" t="s" s="2">
-        <v>815</v>
+        <v>816</v>
       </c>
       <c r="D357" s="2"/>
       <c r="E357" t="s" s="2">
@@ -46773,13 +46776,13 @@
         <v>74</v>
       </c>
       <c r="L357" t="s" s="2">
-        <v>81</v>
+        <v>420</v>
       </c>
       <c r="M357" t="s" s="2">
-        <v>813</v>
+        <v>814</v>
       </c>
       <c r="N357" t="s" s="2">
-        <v>813</v>
+        <v>814</v>
       </c>
       <c r="O357" s="2"/>
       <c r="P357" s="2"/>
@@ -46830,7 +46833,7 @@
         <v>74</v>
       </c>
       <c r="AG357" t="s" s="2">
-        <v>815</v>
+        <v>816</v>
       </c>
       <c r="AH357" t="s" s="2">
         <v>80</v>
@@ -46842,18 +46845,18 @@
         <v>74</v>
       </c>
       <c r="AK357" t="s" s="2">
-        <v>816</v>
+        <v>817</v>
       </c>
     </row>
     <row r="358">
       <c r="A358" t="s" s="2">
-        <v>817</v>
+        <v>818</v>
       </c>
       <c r="B358" t="s" s="2">
-        <v>817</v>
+        <v>818</v>
       </c>
       <c r="C358" t="s" s="2">
-        <v>817</v>
+        <v>818</v>
       </c>
       <c r="D358" s="2"/>
       <c r="E358" t="s" s="2">
@@ -46879,10 +46882,10 @@
         <v>77</v>
       </c>
       <c r="M358" t="s" s="2">
-        <v>819</v>
+        <v>820</v>
       </c>
       <c r="N358" t="s" s="2">
-        <v>820</v>
+        <v>821</v>
       </c>
       <c r="O358" s="2"/>
       <c r="P358" s="2"/>
@@ -46950,13 +46953,13 @@
     </row>
     <row r="359">
       <c r="A359" t="s" s="2">
-        <v>817</v>
+        <v>818</v>
       </c>
       <c r="B359" t="s" s="2">
-        <v>821</v>
+        <v>822</v>
       </c>
       <c r="C359" t="s" s="2">
-        <v>821</v>
+        <v>822</v>
       </c>
       <c r="D359" s="2"/>
       <c r="E359" t="s" s="2">
@@ -46979,13 +46982,13 @@
         <v>74</v>
       </c>
       <c r="L359" t="s" s="2">
-        <v>81</v>
+        <v>420</v>
       </c>
       <c r="M359" t="s" s="2">
-        <v>819</v>
+        <v>820</v>
       </c>
       <c r="N359" t="s" s="2">
-        <v>819</v>
+        <v>820</v>
       </c>
       <c r="O359" s="2"/>
       <c r="P359" s="2"/>
@@ -47036,7 +47039,7 @@
         <v>74</v>
       </c>
       <c r="AG359" t="s" s="2">
-        <v>821</v>
+        <v>822</v>
       </c>
       <c r="AH359" t="s" s="2">
         <v>80</v>
@@ -47053,13 +47056,13 @@
     </row>
     <row r="360">
       <c r="A360" t="s" s="2">
-        <v>822</v>
+        <v>823</v>
       </c>
       <c r="B360" t="s" s="2">
-        <v>822</v>
+        <v>823</v>
       </c>
       <c r="C360" t="s" s="2">
-        <v>822</v>
+        <v>823</v>
       </c>
       <c r="D360" s="2"/>
       <c r="E360" t="s" s="2">
@@ -47085,10 +47088,10 @@
         <v>77</v>
       </c>
       <c r="M360" t="s" s="2">
-        <v>824</v>
+        <v>825</v>
       </c>
       <c r="N360" t="s" s="2">
-        <v>825</v>
+        <v>826</v>
       </c>
       <c r="O360" s="2"/>
       <c r="P360" s="2"/>
@@ -47156,13 +47159,13 @@
     </row>
     <row r="361">
       <c r="A361" t="s" s="2">
-        <v>822</v>
+        <v>823</v>
       </c>
       <c r="B361" t="s" s="2">
-        <v>826</v>
+        <v>827</v>
       </c>
       <c r="C361" t="s" s="2">
-        <v>826</v>
+        <v>827</v>
       </c>
       <c r="D361" s="2"/>
       <c r="E361" t="s" s="2">
@@ -47188,10 +47191,10 @@
         <v>420</v>
       </c>
       <c r="M361" t="s" s="2">
-        <v>824</v>
+        <v>825</v>
       </c>
       <c r="N361" t="s" s="2">
-        <v>824</v>
+        <v>825</v>
       </c>
       <c r="O361" s="2"/>
       <c r="P361" s="2"/>
@@ -47242,7 +47245,7 @@
         <v>74</v>
       </c>
       <c r="AG361" t="s" s="2">
-        <v>826</v>
+        <v>827</v>
       </c>
       <c r="AH361" t="s" s="2">
         <v>80</v>
@@ -47259,13 +47262,13 @@
     </row>
     <row r="362">
       <c r="A362" t="s" s="2">
-        <v>827</v>
+        <v>828</v>
       </c>
       <c r="B362" t="s" s="2">
-        <v>827</v>
+        <v>828</v>
       </c>
       <c r="C362" t="s" s="2">
-        <v>827</v>
+        <v>828</v>
       </c>
       <c r="D362" s="2"/>
       <c r="E362" t="s" s="2">
@@ -47291,10 +47294,10 @@
         <v>77</v>
       </c>
       <c r="M362" t="s" s="2">
-        <v>810</v>
+        <v>830</v>
       </c>
       <c r="N362" t="s" s="2">
-        <v>829</v>
+        <v>831</v>
       </c>
       <c r="O362" s="2"/>
       <c r="P362" s="2"/>
@@ -47362,13 +47365,13 @@
     </row>
     <row r="363">
       <c r="A363" t="s" s="2">
-        <v>827</v>
+        <v>828</v>
       </c>
       <c r="B363" t="s" s="2">
-        <v>830</v>
+        <v>832</v>
       </c>
       <c r="C363" t="s" s="2">
-        <v>830</v>
+        <v>832</v>
       </c>
       <c r="D363" s="2"/>
       <c r="E363" t="s" s="2">
@@ -47391,13 +47394,13 @@
         <v>74</v>
       </c>
       <c r="L363" t="s" s="2">
-        <v>81</v>
+        <v>420</v>
       </c>
       <c r="M363" t="s" s="2">
-        <v>831</v>
+        <v>833</v>
       </c>
       <c r="N363" t="s" s="2">
-        <v>831</v>
+        <v>833</v>
       </c>
       <c r="O363" s="2"/>
       <c r="P363" s="2"/>
@@ -47448,7 +47451,7 @@
         <v>74</v>
       </c>
       <c r="AG363" t="s" s="2">
-        <v>830</v>
+        <v>832</v>
       </c>
       <c r="AH363" t="s" s="2">
         <v>80</v>
@@ -47465,13 +47468,13 @@
     </row>
     <row r="364">
       <c r="A364" t="s" s="2">
-        <v>832</v>
+        <v>834</v>
       </c>
       <c r="B364" t="s" s="2">
-        <v>832</v>
+        <v>834</v>
       </c>
       <c r="C364" t="s" s="2">
-        <v>832</v>
+        <v>834</v>
       </c>
       <c r="D364" s="2"/>
       <c r="E364" t="s" s="2">
@@ -47497,10 +47500,10 @@
         <v>77</v>
       </c>
       <c r="M364" t="s" s="2">
-        <v>835</v>
+        <v>837</v>
       </c>
       <c r="N364" t="s" s="2">
-        <v>836</v>
+        <v>838</v>
       </c>
       <c r="O364" s="2"/>
       <c r="P364" s="2"/>
@@ -47568,13 +47571,13 @@
     </row>
     <row r="365">
       <c r="A365" t="s" s="2">
-        <v>832</v>
+        <v>834</v>
       </c>
       <c r="B365" t="s" s="2">
-        <v>838</v>
+        <v>840</v>
       </c>
       <c r="C365" t="s" s="2">
-        <v>838</v>
+        <v>840</v>
       </c>
       <c r="D365" s="2"/>
       <c r="E365" t="s" s="2">
@@ -47597,13 +47600,13 @@
         <v>74</v>
       </c>
       <c r="L365" t="s" s="2">
-        <v>839</v>
+        <v>841</v>
       </c>
       <c r="M365" t="s" s="2">
-        <v>840</v>
+        <v>842</v>
       </c>
       <c r="N365" t="s" s="2">
-        <v>840</v>
+        <v>842</v>
       </c>
       <c r="O365" s="2"/>
       <c r="P365" s="2"/>
@@ -47618,7 +47621,7 @@
         <v>74</v>
       </c>
       <c r="U365" t="s" s="2">
-        <v>841</v>
+        <v>843</v>
       </c>
       <c r="V365" t="s" s="2">
         <v>74</v>
@@ -47654,7 +47657,7 @@
         <v>74</v>
       </c>
       <c r="AG365" t="s" s="2">
-        <v>842</v>
+        <v>844</v>
       </c>
       <c r="AH365" t="s" s="2">
         <v>80</v>
@@ -47671,13 +47674,13 @@
     </row>
     <row r="366">
       <c r="A366" t="s" s="2">
-        <v>832</v>
+        <v>834</v>
       </c>
       <c r="B366" t="s" s="2">
-        <v>843</v>
+        <v>845</v>
       </c>
       <c r="C366" t="s" s="2">
-        <v>843</v>
+        <v>845</v>
       </c>
       <c r="D366" s="2"/>
       <c r="E366" t="s" s="2">
@@ -47703,10 +47706,10 @@
         <v>441</v>
       </c>
       <c r="M366" t="s" s="2">
-        <v>844</v>
+        <v>846</v>
       </c>
       <c r="N366" t="s" s="2">
-        <v>844</v>
+        <v>846</v>
       </c>
       <c r="O366" s="2"/>
       <c r="P366" s="2"/>
@@ -47757,7 +47760,7 @@
         <v>74</v>
       </c>
       <c r="AG366" t="s" s="2">
-        <v>845</v>
+        <v>847</v>
       </c>
       <c r="AH366" t="s" s="2">
         <v>80</v>
@@ -47774,13 +47777,13 @@
     </row>
     <row r="367">
       <c r="A367" t="s" s="2">
-        <v>832</v>
+        <v>834</v>
       </c>
       <c r="B367" t="s" s="2">
-        <v>846</v>
+        <v>848</v>
       </c>
       <c r="C367" t="s" s="2">
-        <v>846</v>
+        <v>848</v>
       </c>
       <c r="D367" s="2"/>
       <c r="E367" t="s" s="2">
@@ -47806,10 +47809,10 @@
         <v>81</v>
       </c>
       <c r="M367" t="s" s="2">
-        <v>847</v>
+        <v>849</v>
       </c>
       <c r="N367" t="s" s="2">
-        <v>848</v>
+        <v>850</v>
       </c>
       <c r="O367" s="2"/>
       <c r="P367" s="2"/>
@@ -47860,7 +47863,7 @@
         <v>74</v>
       </c>
       <c r="AG367" t="s" s="2">
-        <v>849</v>
+        <v>851</v>
       </c>
       <c r="AH367" t="s" s="2">
         <v>80</v>
@@ -47877,13 +47880,13 @@
     </row>
     <row r="368">
       <c r="A368" t="s" s="2">
-        <v>832</v>
+        <v>834</v>
       </c>
       <c r="B368" t="s" s="2">
-        <v>850</v>
+        <v>852</v>
       </c>
       <c r="C368" t="s" s="2">
-        <v>850</v>
+        <v>852</v>
       </c>
       <c r="D368" s="2"/>
       <c r="E368" t="s" s="2">
@@ -47909,10 +47912,10 @@
         <v>81</v>
       </c>
       <c r="M368" t="s" s="2">
-        <v>851</v>
+        <v>853</v>
       </c>
       <c r="N368" t="s" s="2">
-        <v>852</v>
+        <v>854</v>
       </c>
       <c r="O368" s="2"/>
       <c r="P368" s="2"/>
@@ -47963,7 +47966,7 @@
         <v>74</v>
       </c>
       <c r="AG368" t="s" s="2">
-        <v>853</v>
+        <v>855</v>
       </c>
       <c r="AH368" t="s" s="2">
         <v>80</v>
@@ -47980,13 +47983,13 @@
     </row>
     <row r="369">
       <c r="A369" t="s" s="2">
-        <v>832</v>
+        <v>834</v>
       </c>
       <c r="B369" t="s" s="2">
-        <v>854</v>
+        <v>856</v>
       </c>
       <c r="C369" t="s" s="2">
-        <v>854</v>
+        <v>856</v>
       </c>
       <c r="D369" s="2"/>
       <c r="E369" t="s" s="2">
@@ -48009,13 +48012,13 @@
         <v>74</v>
       </c>
       <c r="L369" t="s" s="2">
-        <v>855</v>
+        <v>857</v>
       </c>
       <c r="M369" t="s" s="2">
-        <v>856</v>
+        <v>858</v>
       </c>
       <c r="N369" t="s" s="2">
-        <v>856</v>
+        <v>858</v>
       </c>
       <c r="O369" s="2"/>
       <c r="P369" s="2"/>
@@ -48066,7 +48069,7 @@
         <v>74</v>
       </c>
       <c r="AG369" t="s" s="2">
-        <v>857</v>
+        <v>859</v>
       </c>
       <c r="AH369" t="s" s="2">
         <v>80</v>
@@ -48083,13 +48086,13 @@
     </row>
     <row r="370">
       <c r="A370" t="s" s="2">
-        <v>832</v>
+        <v>834</v>
       </c>
       <c r="B370" t="s" s="2">
-        <v>858</v>
+        <v>860</v>
       </c>
       <c r="C370" t="s" s="2">
-        <v>858</v>
+        <v>860</v>
       </c>
       <c r="D370" s="2"/>
       <c r="E370" t="s" s="2">
@@ -48115,10 +48118,10 @@
         <v>81</v>
       </c>
       <c r="M370" t="s" s="2">
-        <v>859</v>
+        <v>861</v>
       </c>
       <c r="N370" t="s" s="2">
-        <v>859</v>
+        <v>861</v>
       </c>
       <c r="O370" s="2"/>
       <c r="P370" s="2"/>
@@ -48169,7 +48172,7 @@
         <v>74</v>
       </c>
       <c r="AG370" t="s" s="2">
-        <v>860</v>
+        <v>862</v>
       </c>
       <c r="AH370" t="s" s="2">
         <v>75</v>
@@ -48186,13 +48189,13 @@
     </row>
     <row r="371">
       <c r="A371" t="s" s="2">
-        <v>832</v>
+        <v>834</v>
       </c>
       <c r="B371" t="s" s="2">
-        <v>861</v>
+        <v>863</v>
       </c>
       <c r="C371" t="s" s="2">
-        <v>861</v>
+        <v>863</v>
       </c>
       <c r="D371" s="2"/>
       <c r="E371" t="s" s="2">
@@ -48218,10 +48221,10 @@
         <v>81</v>
       </c>
       <c r="M371" t="s" s="2">
-        <v>862</v>
+        <v>864</v>
       </c>
       <c r="N371" t="s" s="2">
-        <v>863</v>
+        <v>865</v>
       </c>
       <c r="O371" s="2"/>
       <c r="P371" s="2"/>
@@ -48272,7 +48275,7 @@
         <v>74</v>
       </c>
       <c r="AG371" t="s" s="2">
-        <v>864</v>
+        <v>866</v>
       </c>
       <c r="AH371" t="s" s="2">
         <v>80</v>
@@ -48289,13 +48292,13 @@
     </row>
     <row r="372">
       <c r="A372" t="s" s="2">
-        <v>832</v>
+        <v>834</v>
       </c>
       <c r="B372" t="s" s="2">
-        <v>865</v>
+        <v>867</v>
       </c>
       <c r="C372" t="s" s="2">
-        <v>865</v>
+        <v>867</v>
       </c>
       <c r="D372" s="2"/>
       <c r="E372" t="s" s="2">
@@ -48321,10 +48324,10 @@
         <v>81</v>
       </c>
       <c r="M372" t="s" s="2">
-        <v>866</v>
+        <v>868</v>
       </c>
       <c r="N372" t="s" s="2">
-        <v>866</v>
+        <v>868</v>
       </c>
       <c r="O372" s="2"/>
       <c r="P372" s="2"/>
@@ -48375,7 +48378,7 @@
         <v>74</v>
       </c>
       <c r="AG372" t="s" s="2">
-        <v>867</v>
+        <v>869</v>
       </c>
       <c r="AH372" t="s" s="2">
         <v>80</v>
@@ -48392,13 +48395,13 @@
     </row>
     <row r="373">
       <c r="A373" t="s" s="2">
-        <v>832</v>
+        <v>834</v>
       </c>
       <c r="B373" t="s" s="2">
-        <v>868</v>
+        <v>870</v>
       </c>
       <c r="C373" t="s" s="2">
-        <v>868</v>
+        <v>870</v>
       </c>
       <c r="D373" s="2"/>
       <c r="E373" t="s" s="2">
@@ -48424,10 +48427,10 @@
         <v>393</v>
       </c>
       <c r="M373" t="s" s="2">
-        <v>869</v>
+        <v>871</v>
       </c>
       <c r="N373" t="s" s="2">
-        <v>869</v>
+        <v>871</v>
       </c>
       <c r="O373" s="2"/>
       <c r="P373" s="2"/>
@@ -48439,7 +48442,7 @@
         <v>74</v>
       </c>
       <c r="T373" t="s" s="2">
-        <v>870</v>
+        <v>872</v>
       </c>
       <c r="U373" t="s" s="2">
         <v>74</v>
@@ -48478,7 +48481,7 @@
         <v>74</v>
       </c>
       <c r="AG373" t="s" s="2">
-        <v>871</v>
+        <v>873</v>
       </c>
       <c r="AH373" t="s" s="2">
         <v>80</v>
@@ -48495,13 +48498,13 @@
     </row>
     <row r="374">
       <c r="A374" t="s" s="2">
-        <v>832</v>
+        <v>834</v>
       </c>
       <c r="B374" t="s" s="2">
-        <v>872</v>
+        <v>874</v>
       </c>
       <c r="C374" t="s" s="2">
-        <v>872</v>
+        <v>874</v>
       </c>
       <c r="D374" s="2"/>
       <c r="E374" t="s" s="2">
@@ -48527,10 +48530,10 @@
         <v>393</v>
       </c>
       <c r="M374" t="s" s="2">
-        <v>873</v>
+        <v>875</v>
       </c>
       <c r="N374" t="s" s="2">
-        <v>873</v>
+        <v>875</v>
       </c>
       <c r="O374" s="2"/>
       <c r="P374" s="2"/>
@@ -48542,7 +48545,7 @@
         <v>74</v>
       </c>
       <c r="T374" t="s" s="2">
-        <v>874</v>
+        <v>876</v>
       </c>
       <c r="U374" t="s" s="2">
         <v>74</v>
@@ -48581,7 +48584,7 @@
         <v>74</v>
       </c>
       <c r="AG374" t="s" s="2">
-        <v>875</v>
+        <v>877</v>
       </c>
       <c r="AH374" t="s" s="2">
         <v>80</v>
@@ -48598,13 +48601,13 @@
     </row>
     <row r="375">
       <c r="A375" t="s" s="2">
-        <v>876</v>
+        <v>878</v>
       </c>
       <c r="B375" t="s" s="2">
-        <v>876</v>
+        <v>878</v>
       </c>
       <c r="C375" t="s" s="2">
-        <v>876</v>
+        <v>878</v>
       </c>
       <c r="D375" s="2"/>
       <c r="E375" t="s" s="2">
@@ -48630,10 +48633,10 @@
         <v>77</v>
       </c>
       <c r="M375" t="s" s="2">
-        <v>879</v>
+        <v>881</v>
       </c>
       <c r="N375" t="s" s="2">
-        <v>880</v>
+        <v>882</v>
       </c>
       <c r="O375" s="2"/>
       <c r="P375" s="2"/>
@@ -48701,13 +48704,13 @@
     </row>
     <row r="376">
       <c r="A376" t="s" s="2">
-        <v>876</v>
+        <v>878</v>
       </c>
       <c r="B376" t="s" s="2">
-        <v>881</v>
+        <v>883</v>
       </c>
       <c r="C376" t="s" s="2">
-        <v>881</v>
+        <v>883</v>
       </c>
       <c r="D376" s="2"/>
       <c r="E376" t="s" s="2">
@@ -48730,13 +48733,13 @@
         <v>74</v>
       </c>
       <c r="L376" t="s" s="2">
-        <v>839</v>
+        <v>841</v>
       </c>
       <c r="M376" t="s" s="2">
-        <v>840</v>
+        <v>842</v>
       </c>
       <c r="N376" t="s" s="2">
-        <v>840</v>
+        <v>842</v>
       </c>
       <c r="O376" s="2"/>
       <c r="P376" s="2"/>
@@ -48751,7 +48754,7 @@
         <v>74</v>
       </c>
       <c r="U376" t="s" s="2">
-        <v>882</v>
+        <v>884</v>
       </c>
       <c r="V376" t="s" s="2">
         <v>74</v>
@@ -48787,7 +48790,7 @@
         <v>74</v>
       </c>
       <c r="AG376" t="s" s="2">
-        <v>842</v>
+        <v>844</v>
       </c>
       <c r="AH376" t="s" s="2">
         <v>80</v>
@@ -48804,13 +48807,13 @@
     </row>
     <row r="377">
       <c r="A377" t="s" s="2">
-        <v>876</v>
+        <v>878</v>
       </c>
       <c r="B377" t="s" s="2">
-        <v>883</v>
+        <v>885</v>
       </c>
       <c r="C377" t="s" s="2">
-        <v>883</v>
+        <v>885</v>
       </c>
       <c r="D377" s="2"/>
       <c r="E377" t="s" s="2">
@@ -48833,13 +48836,13 @@
         <v>74</v>
       </c>
       <c r="L377" t="s" s="2">
-        <v>884</v>
+        <v>886</v>
       </c>
       <c r="M377" t="s" s="2">
-        <v>844</v>
+        <v>846</v>
       </c>
       <c r="N377" t="s" s="2">
-        <v>844</v>
+        <v>846</v>
       </c>
       <c r="O377" s="2"/>
       <c r="P377" s="2"/>
@@ -48890,7 +48893,7 @@
         <v>74</v>
       </c>
       <c r="AG377" t="s" s="2">
-        <v>845</v>
+        <v>847</v>
       </c>
       <c r="AH377" t="s" s="2">
         <v>80</v>
@@ -48907,13 +48910,13 @@
     </row>
     <row r="378">
       <c r="A378" t="s" s="2">
-        <v>876</v>
+        <v>878</v>
       </c>
       <c r="B378" t="s" s="2">
-        <v>885</v>
+        <v>887</v>
       </c>
       <c r="C378" t="s" s="2">
-        <v>885</v>
+        <v>887</v>
       </c>
       <c r="D378" s="2"/>
       <c r="E378" t="s" s="2">
@@ -48939,10 +48942,10 @@
         <v>81</v>
       </c>
       <c r="M378" t="s" s="2">
-        <v>886</v>
+        <v>888</v>
       </c>
       <c r="N378" t="s" s="2">
-        <v>848</v>
+        <v>850</v>
       </c>
       <c r="O378" s="2"/>
       <c r="P378" s="2"/>
@@ -48993,7 +48996,7 @@
         <v>74</v>
       </c>
       <c r="AG378" t="s" s="2">
-        <v>849</v>
+        <v>851</v>
       </c>
       <c r="AH378" t="s" s="2">
         <v>80</v>
@@ -49010,13 +49013,13 @@
     </row>
     <row r="379">
       <c r="A379" t="s" s="2">
-        <v>876</v>
+        <v>878</v>
       </c>
       <c r="B379" t="s" s="2">
-        <v>887</v>
+        <v>889</v>
       </c>
       <c r="C379" t="s" s="2">
-        <v>887</v>
+        <v>889</v>
       </c>
       <c r="D379" s="2"/>
       <c r="E379" t="s" s="2">
@@ -49042,10 +49045,10 @@
         <v>81</v>
       </c>
       <c r="M379" t="s" s="2">
-        <v>888</v>
+        <v>890</v>
       </c>
       <c r="N379" t="s" s="2">
-        <v>852</v>
+        <v>854</v>
       </c>
       <c r="O379" s="2"/>
       <c r="P379" s="2"/>
@@ -49096,7 +49099,7 @@
         <v>74</v>
       </c>
       <c r="AG379" t="s" s="2">
-        <v>853</v>
+        <v>855</v>
       </c>
       <c r="AH379" t="s" s="2">
         <v>80</v>
@@ -49113,13 +49116,13 @@
     </row>
     <row r="380">
       <c r="A380" t="s" s="2">
-        <v>876</v>
+        <v>878</v>
       </c>
       <c r="B380" t="s" s="2">
-        <v>889</v>
+        <v>891</v>
       </c>
       <c r="C380" t="s" s="2">
-        <v>889</v>
+        <v>891</v>
       </c>
       <c r="D380" s="2"/>
       <c r="E380" t="s" s="2">
@@ -49142,13 +49145,13 @@
         <v>74</v>
       </c>
       <c r="L380" t="s" s="2">
-        <v>855</v>
+        <v>857</v>
       </c>
       <c r="M380" t="s" s="2">
-        <v>856</v>
+        <v>858</v>
       </c>
       <c r="N380" t="s" s="2">
-        <v>856</v>
+        <v>858</v>
       </c>
       <c r="O380" s="2"/>
       <c r="P380" s="2"/>
@@ -49199,7 +49202,7 @@
         <v>74</v>
       </c>
       <c r="AG380" t="s" s="2">
-        <v>857</v>
+        <v>859</v>
       </c>
       <c r="AH380" t="s" s="2">
         <v>80</v>
@@ -49216,13 +49219,13 @@
     </row>
     <row r="381">
       <c r="A381" t="s" s="2">
-        <v>876</v>
+        <v>878</v>
       </c>
       <c r="B381" t="s" s="2">
-        <v>890</v>
+        <v>892</v>
       </c>
       <c r="C381" t="s" s="2">
-        <v>890</v>
+        <v>892</v>
       </c>
       <c r="D381" s="2"/>
       <c r="E381" t="s" s="2">
@@ -49248,10 +49251,10 @@
         <v>81</v>
       </c>
       <c r="M381" t="s" s="2">
-        <v>859</v>
+        <v>861</v>
       </c>
       <c r="N381" t="s" s="2">
-        <v>859</v>
+        <v>861</v>
       </c>
       <c r="O381" s="2"/>
       <c r="P381" s="2"/>
@@ -49302,7 +49305,7 @@
         <v>74</v>
       </c>
       <c r="AG381" t="s" s="2">
-        <v>860</v>
+        <v>862</v>
       </c>
       <c r="AH381" t="s" s="2">
         <v>75</v>
@@ -49319,13 +49322,13 @@
     </row>
     <row r="382">
       <c r="A382" t="s" s="2">
-        <v>876</v>
+        <v>878</v>
       </c>
       <c r="B382" t="s" s="2">
-        <v>891</v>
+        <v>893</v>
       </c>
       <c r="C382" t="s" s="2">
-        <v>891</v>
+        <v>893</v>
       </c>
       <c r="D382" s="2"/>
       <c r="E382" t="s" s="2">
@@ -49351,10 +49354,10 @@
         <v>81</v>
       </c>
       <c r="M382" t="s" s="2">
-        <v>863</v>
+        <v>865</v>
       </c>
       <c r="N382" t="s" s="2">
-        <v>863</v>
+        <v>865</v>
       </c>
       <c r="O382" s="2"/>
       <c r="P382" s="2"/>
@@ -49366,7 +49369,7 @@
         <v>74</v>
       </c>
       <c r="T382" t="s" s="2">
-        <v>892</v>
+        <v>894</v>
       </c>
       <c r="U382" t="s" s="2">
         <v>74</v>
@@ -49405,7 +49408,7 @@
         <v>74</v>
       </c>
       <c r="AG382" t="s" s="2">
-        <v>864</v>
+        <v>866</v>
       </c>
       <c r="AH382" t="s" s="2">
         <v>80</v>
@@ -49422,13 +49425,13 @@
     </row>
     <row r="383">
       <c r="A383" t="s" s="2">
-        <v>876</v>
+        <v>878</v>
       </c>
       <c r="B383" t="s" s="2">
-        <v>893</v>
+        <v>895</v>
       </c>
       <c r="C383" t="s" s="2">
-        <v>893</v>
+        <v>895</v>
       </c>
       <c r="D383" s="2"/>
       <c r="E383" t="s" s="2">
@@ -49454,10 +49457,10 @@
         <v>81</v>
       </c>
       <c r="M383" t="s" s="2">
-        <v>866</v>
+        <v>868</v>
       </c>
       <c r="N383" t="s" s="2">
-        <v>866</v>
+        <v>868</v>
       </c>
       <c r="O383" s="2"/>
       <c r="P383" s="2"/>
@@ -49508,7 +49511,7 @@
         <v>74</v>
       </c>
       <c r="AG383" t="s" s="2">
-        <v>867</v>
+        <v>869</v>
       </c>
       <c r="AH383" t="s" s="2">
         <v>80</v>
@@ -49525,13 +49528,13 @@
     </row>
     <row r="384">
       <c r="A384" t="s" s="2">
-        <v>876</v>
+        <v>878</v>
       </c>
       <c r="B384" t="s" s="2">
-        <v>894</v>
+        <v>896</v>
       </c>
       <c r="C384" t="s" s="2">
-        <v>894</v>
+        <v>896</v>
       </c>
       <c r="D384" s="2"/>
       <c r="E384" t="s" s="2">
@@ -49557,10 +49560,10 @@
         <v>393</v>
       </c>
       <c r="M384" t="s" s="2">
-        <v>869</v>
+        <v>871</v>
       </c>
       <c r="N384" t="s" s="2">
-        <v>869</v>
+        <v>871</v>
       </c>
       <c r="O384" s="2"/>
       <c r="P384" s="2"/>
@@ -49572,7 +49575,7 @@
         <v>74</v>
       </c>
       <c r="T384" t="s" s="2">
-        <v>870</v>
+        <v>872</v>
       </c>
       <c r="U384" t="s" s="2">
         <v>74</v>
@@ -49611,7 +49614,7 @@
         <v>74</v>
       </c>
       <c r="AG384" t="s" s="2">
-        <v>871</v>
+        <v>873</v>
       </c>
       <c r="AH384" t="s" s="2">
         <v>80</v>
@@ -49628,13 +49631,13 @@
     </row>
     <row r="385">
       <c r="A385" t="s" s="2">
-        <v>876</v>
+        <v>878</v>
       </c>
       <c r="B385" t="s" s="2">
-        <v>895</v>
+        <v>897</v>
       </c>
       <c r="C385" t="s" s="2">
-        <v>895</v>
+        <v>897</v>
       </c>
       <c r="D385" s="2"/>
       <c r="E385" t="s" s="2">
@@ -49660,10 +49663,10 @@
         <v>393</v>
       </c>
       <c r="M385" t="s" s="2">
-        <v>873</v>
+        <v>875</v>
       </c>
       <c r="N385" t="s" s="2">
-        <v>873</v>
+        <v>875</v>
       </c>
       <c r="O385" s="2"/>
       <c r="P385" s="2"/>
@@ -49675,7 +49678,7 @@
         <v>74</v>
       </c>
       <c r="T385" t="s" s="2">
-        <v>896</v>
+        <v>898</v>
       </c>
       <c r="U385" t="s" s="2">
         <v>74</v>
@@ -49714,7 +49717,7 @@
         <v>74</v>
       </c>
       <c r="AG385" t="s" s="2">
-        <v>875</v>
+        <v>877</v>
       </c>
       <c r="AH385" t="s" s="2">
         <v>80</v>
@@ -49731,13 +49734,13 @@
     </row>
     <row r="386">
       <c r="A386" t="s" s="2">
-        <v>897</v>
+        <v>899</v>
       </c>
       <c r="B386" t="s" s="2">
-        <v>897</v>
+        <v>899</v>
       </c>
       <c r="C386" t="s" s="2">
-        <v>897</v>
+        <v>899</v>
       </c>
       <c r="D386" s="2"/>
       <c r="E386" t="s" s="2">
@@ -49763,10 +49766,10 @@
         <v>77</v>
       </c>
       <c r="M386" t="s" s="2">
-        <v>900</v>
+        <v>902</v>
       </c>
       <c r="N386" t="s" s="2">
-        <v>901</v>
+        <v>903</v>
       </c>
       <c r="O386" s="2"/>
       <c r="P386" s="2"/>
@@ -49834,13 +49837,13 @@
     </row>
     <row r="387">
       <c r="A387" t="s" s="2">
-        <v>897</v>
+        <v>899</v>
       </c>
       <c r="B387" t="s" s="2">
-        <v>902</v>
+        <v>904</v>
       </c>
       <c r="C387" t="s" s="2">
-        <v>902</v>
+        <v>904</v>
       </c>
       <c r="D387" s="2"/>
       <c r="E387" t="s" s="2">
@@ -49863,13 +49866,13 @@
         <v>74</v>
       </c>
       <c r="L387" t="s" s="2">
-        <v>839</v>
+        <v>841</v>
       </c>
       <c r="M387" t="s" s="2">
-        <v>840</v>
+        <v>842</v>
       </c>
       <c r="N387" t="s" s="2">
-        <v>840</v>
+        <v>842</v>
       </c>
       <c r="O387" s="2"/>
       <c r="P387" s="2"/>
@@ -49884,7 +49887,7 @@
         <v>74</v>
       </c>
       <c r="U387" t="s" s="2">
-        <v>903</v>
+        <v>905</v>
       </c>
       <c r="V387" t="s" s="2">
         <v>74</v>
@@ -49920,7 +49923,7 @@
         <v>74</v>
       </c>
       <c r="AG387" t="s" s="2">
-        <v>842</v>
+        <v>844</v>
       </c>
       <c r="AH387" t="s" s="2">
         <v>80</v>
@@ -49937,13 +49940,13 @@
     </row>
     <row r="388">
       <c r="A388" t="s" s="2">
-        <v>897</v>
+        <v>899</v>
       </c>
       <c r="B388" t="s" s="2">
-        <v>904</v>
+        <v>906</v>
       </c>
       <c r="C388" t="s" s="2">
-        <v>904</v>
+        <v>906</v>
       </c>
       <c r="D388" s="2"/>
       <c r="E388" t="s" s="2">
@@ -49966,13 +49969,13 @@
         <v>74</v>
       </c>
       <c r="L388" t="s" s="2">
-        <v>905</v>
+        <v>907</v>
       </c>
       <c r="M388" t="s" s="2">
-        <v>844</v>
+        <v>846</v>
       </c>
       <c r="N388" t="s" s="2">
-        <v>844</v>
+        <v>846</v>
       </c>
       <c r="O388" s="2"/>
       <c r="P388" s="2"/>
@@ -50023,7 +50026,7 @@
         <v>74</v>
       </c>
       <c r="AG388" t="s" s="2">
-        <v>845</v>
+        <v>847</v>
       </c>
       <c r="AH388" t="s" s="2">
         <v>80</v>
@@ -50040,13 +50043,13 @@
     </row>
     <row r="389">
       <c r="A389" t="s" s="2">
-        <v>897</v>
+        <v>899</v>
       </c>
       <c r="B389" t="s" s="2">
-        <v>906</v>
+        <v>908</v>
       </c>
       <c r="C389" t="s" s="2">
-        <v>906</v>
+        <v>908</v>
       </c>
       <c r="D389" s="2"/>
       <c r="E389" t="s" s="2">
@@ -50072,10 +50075,10 @@
         <v>81</v>
       </c>
       <c r="M389" t="s" s="2">
-        <v>907</v>
+        <v>909</v>
       </c>
       <c r="N389" t="s" s="2">
-        <v>848</v>
+        <v>850</v>
       </c>
       <c r="O389" s="2"/>
       <c r="P389" s="2"/>
@@ -50126,7 +50129,7 @@
         <v>74</v>
       </c>
       <c r="AG389" t="s" s="2">
-        <v>849</v>
+        <v>851</v>
       </c>
       <c r="AH389" t="s" s="2">
         <v>80</v>
@@ -50143,13 +50146,13 @@
     </row>
     <row r="390">
       <c r="A390" t="s" s="2">
-        <v>897</v>
+        <v>899</v>
       </c>
       <c r="B390" t="s" s="2">
-        <v>908</v>
+        <v>910</v>
       </c>
       <c r="C390" t="s" s="2">
-        <v>908</v>
+        <v>910</v>
       </c>
       <c r="D390" s="2"/>
       <c r="E390" t="s" s="2">
@@ -50175,10 +50178,10 @@
         <v>81</v>
       </c>
       <c r="M390" t="s" s="2">
-        <v>909</v>
+        <v>911</v>
       </c>
       <c r="N390" t="s" s="2">
-        <v>852</v>
+        <v>854</v>
       </c>
       <c r="O390" s="2"/>
       <c r="P390" s="2"/>
@@ -50229,7 +50232,7 @@
         <v>74</v>
       </c>
       <c r="AG390" t="s" s="2">
-        <v>853</v>
+        <v>855</v>
       </c>
       <c r="AH390" t="s" s="2">
         <v>80</v>
@@ -50246,13 +50249,13 @@
     </row>
     <row r="391">
       <c r="A391" t="s" s="2">
-        <v>897</v>
+        <v>899</v>
       </c>
       <c r="B391" t="s" s="2">
-        <v>910</v>
+        <v>912</v>
       </c>
       <c r="C391" t="s" s="2">
-        <v>910</v>
+        <v>912</v>
       </c>
       <c r="D391" s="2"/>
       <c r="E391" t="s" s="2">
@@ -50275,13 +50278,13 @@
         <v>74</v>
       </c>
       <c r="L391" t="s" s="2">
-        <v>855</v>
+        <v>857</v>
       </c>
       <c r="M391" t="s" s="2">
-        <v>856</v>
+        <v>858</v>
       </c>
       <c r="N391" t="s" s="2">
-        <v>856</v>
+        <v>858</v>
       </c>
       <c r="O391" s="2"/>
       <c r="P391" s="2"/>
@@ -50332,7 +50335,7 @@
         <v>74</v>
       </c>
       <c r="AG391" t="s" s="2">
-        <v>857</v>
+        <v>859</v>
       </c>
       <c r="AH391" t="s" s="2">
         <v>80</v>
@@ -50349,13 +50352,13 @@
     </row>
     <row r="392">
       <c r="A392" t="s" s="2">
-        <v>897</v>
+        <v>899</v>
       </c>
       <c r="B392" t="s" s="2">
-        <v>911</v>
+        <v>913</v>
       </c>
       <c r="C392" t="s" s="2">
-        <v>911</v>
+        <v>913</v>
       </c>
       <c r="D392" s="2"/>
       <c r="E392" t="s" s="2">
@@ -50381,10 +50384,10 @@
         <v>81</v>
       </c>
       <c r="M392" t="s" s="2">
-        <v>859</v>
+        <v>861</v>
       </c>
       <c r="N392" t="s" s="2">
-        <v>859</v>
+        <v>861</v>
       </c>
       <c r="O392" s="2"/>
       <c r="P392" s="2"/>
@@ -50435,7 +50438,7 @@
         <v>74</v>
       </c>
       <c r="AG392" t="s" s="2">
-        <v>860</v>
+        <v>862</v>
       </c>
       <c r="AH392" t="s" s="2">
         <v>75</v>
@@ -50452,13 +50455,13 @@
     </row>
     <row r="393">
       <c r="A393" t="s" s="2">
-        <v>897</v>
+        <v>899</v>
       </c>
       <c r="B393" t="s" s="2">
-        <v>912</v>
+        <v>914</v>
       </c>
       <c r="C393" t="s" s="2">
-        <v>912</v>
+        <v>914</v>
       </c>
       <c r="D393" s="2"/>
       <c r="E393" t="s" s="2">
@@ -50484,10 +50487,10 @@
         <v>81</v>
       </c>
       <c r="M393" t="s" s="2">
-        <v>913</v>
+        <v>915</v>
       </c>
       <c r="N393" t="s" s="2">
-        <v>863</v>
+        <v>865</v>
       </c>
       <c r="O393" s="2"/>
       <c r="P393" s="2"/>
@@ -50502,7 +50505,7 @@
         <v>74</v>
       </c>
       <c r="U393" t="s" s="2">
-        <v>914</v>
+        <v>916</v>
       </c>
       <c r="V393" t="s" s="2">
         <v>74</v>
@@ -50538,7 +50541,7 @@
         <v>74</v>
       </c>
       <c r="AG393" t="s" s="2">
-        <v>864</v>
+        <v>866</v>
       </c>
       <c r="AH393" t="s" s="2">
         <v>80</v>
@@ -50555,13 +50558,13 @@
     </row>
     <row r="394">
       <c r="A394" t="s" s="2">
-        <v>897</v>
+        <v>899</v>
       </c>
       <c r="B394" t="s" s="2">
-        <v>915</v>
+        <v>917</v>
       </c>
       <c r="C394" t="s" s="2">
-        <v>915</v>
+        <v>917</v>
       </c>
       <c r="D394" s="2"/>
       <c r="E394" t="s" s="2">
@@ -50587,10 +50590,10 @@
         <v>81</v>
       </c>
       <c r="M394" t="s" s="2">
-        <v>866</v>
+        <v>868</v>
       </c>
       <c r="N394" t="s" s="2">
-        <v>866</v>
+        <v>868</v>
       </c>
       <c r="O394" s="2"/>
       <c r="P394" s="2"/>
@@ -50641,7 +50644,7 @@
         <v>74</v>
       </c>
       <c r="AG394" t="s" s="2">
-        <v>867</v>
+        <v>869</v>
       </c>
       <c r="AH394" t="s" s="2">
         <v>80</v>
@@ -50658,13 +50661,13 @@
     </row>
     <row r="395">
       <c r="A395" t="s" s="2">
-        <v>897</v>
+        <v>899</v>
       </c>
       <c r="B395" t="s" s="2">
-        <v>916</v>
+        <v>918</v>
       </c>
       <c r="C395" t="s" s="2">
-        <v>916</v>
+        <v>918</v>
       </c>
       <c r="D395" s="2"/>
       <c r="E395" t="s" s="2">
@@ -50690,10 +50693,10 @@
         <v>393</v>
       </c>
       <c r="M395" t="s" s="2">
-        <v>869</v>
+        <v>871</v>
       </c>
       <c r="N395" t="s" s="2">
-        <v>869</v>
+        <v>871</v>
       </c>
       <c r="O395" s="2"/>
       <c r="P395" s="2"/>
@@ -50705,7 +50708,7 @@
         <v>74</v>
       </c>
       <c r="T395" t="s" s="2">
-        <v>917</v>
+        <v>919</v>
       </c>
       <c r="U395" t="s" s="2">
         <v>74</v>
@@ -50744,7 +50747,7 @@
         <v>74</v>
       </c>
       <c r="AG395" t="s" s="2">
-        <v>871</v>
+        <v>873</v>
       </c>
       <c r="AH395" t="s" s="2">
         <v>80</v>
@@ -50761,13 +50764,13 @@
     </row>
     <row r="396">
       <c r="A396" t="s" s="2">
-        <v>897</v>
+        <v>899</v>
       </c>
       <c r="B396" t="s" s="2">
-        <v>918</v>
+        <v>920</v>
       </c>
       <c r="C396" t="s" s="2">
-        <v>918</v>
+        <v>920</v>
       </c>
       <c r="D396" s="2"/>
       <c r="E396" t="s" s="2">
@@ -50793,10 +50796,10 @@
         <v>393</v>
       </c>
       <c r="M396" t="s" s="2">
-        <v>873</v>
+        <v>875</v>
       </c>
       <c r="N396" t="s" s="2">
-        <v>873</v>
+        <v>875</v>
       </c>
       <c r="O396" s="2"/>
       <c r="P396" s="2"/>
@@ -50808,7 +50811,7 @@
         <v>74</v>
       </c>
       <c r="T396" t="s" s="2">
-        <v>919</v>
+        <v>921</v>
       </c>
       <c r="U396" t="s" s="2">
         <v>74</v>
@@ -50847,7 +50850,7 @@
         <v>74</v>
       </c>
       <c r="AG396" t="s" s="2">
-        <v>875</v>
+        <v>877</v>
       </c>
       <c r="AH396" t="s" s="2">
         <v>80</v>
@@ -50864,13 +50867,13 @@
     </row>
     <row r="397">
       <c r="A397" t="s" s="2">
-        <v>920</v>
+        <v>922</v>
       </c>
       <c r="B397" t="s" s="2">
-        <v>920</v>
+        <v>922</v>
       </c>
       <c r="C397" t="s" s="2">
-        <v>920</v>
+        <v>922</v>
       </c>
       <c r="D397" s="2"/>
       <c r="E397" t="s" s="2">
@@ -50896,10 +50899,10 @@
         <v>77</v>
       </c>
       <c r="M397" t="s" s="2">
-        <v>923</v>
+        <v>925</v>
       </c>
       <c r="N397" t="s" s="2">
-        <v>924</v>
+        <v>926</v>
       </c>
       <c r="O397" s="2"/>
       <c r="P397" s="2"/>
@@ -50967,13 +50970,13 @@
     </row>
     <row r="398">
       <c r="A398" t="s" s="2">
-        <v>920</v>
+        <v>922</v>
       </c>
       <c r="B398" t="s" s="2">
-        <v>925</v>
+        <v>927</v>
       </c>
       <c r="C398" t="s" s="2">
-        <v>925</v>
+        <v>927</v>
       </c>
       <c r="D398" s="2"/>
       <c r="E398" t="s" s="2">
@@ -50996,13 +50999,13 @@
         <v>74</v>
       </c>
       <c r="L398" t="s" s="2">
-        <v>839</v>
+        <v>841</v>
       </c>
       <c r="M398" t="s" s="2">
-        <v>840</v>
+        <v>842</v>
       </c>
       <c r="N398" t="s" s="2">
-        <v>840</v>
+        <v>842</v>
       </c>
       <c r="O398" s="2"/>
       <c r="P398" s="2"/>
@@ -51017,7 +51020,7 @@
         <v>74</v>
       </c>
       <c r="U398" t="s" s="2">
-        <v>926</v>
+        <v>928</v>
       </c>
       <c r="V398" t="s" s="2">
         <v>74</v>
@@ -51053,7 +51056,7 @@
         <v>74</v>
       </c>
       <c r="AG398" t="s" s="2">
-        <v>842</v>
+        <v>844</v>
       </c>
       <c r="AH398" t="s" s="2">
         <v>80</v>
@@ -51070,13 +51073,13 @@
     </row>
     <row r="399">
       <c r="A399" t="s" s="2">
-        <v>920</v>
+        <v>922</v>
       </c>
       <c r="B399" t="s" s="2">
-        <v>927</v>
+        <v>929</v>
       </c>
       <c r="C399" t="s" s="2">
-        <v>927</v>
+        <v>929</v>
       </c>
       <c r="D399" s="2"/>
       <c r="E399" t="s" s="2">
@@ -51099,13 +51102,13 @@
         <v>74</v>
       </c>
       <c r="L399" t="s" s="2">
-        <v>928</v>
+        <v>810</v>
       </c>
       <c r="M399" t="s" s="2">
-        <v>844</v>
+        <v>846</v>
       </c>
       <c r="N399" t="s" s="2">
-        <v>844</v>
+        <v>846</v>
       </c>
       <c r="O399" s="2"/>
       <c r="P399" s="2"/>
@@ -51156,7 +51159,7 @@
         <v>74</v>
       </c>
       <c r="AG399" t="s" s="2">
-        <v>845</v>
+        <v>847</v>
       </c>
       <c r="AH399" t="s" s="2">
         <v>80</v>
@@ -51173,13 +51176,13 @@
     </row>
     <row r="400">
       <c r="A400" t="s" s="2">
-        <v>920</v>
+        <v>922</v>
       </c>
       <c r="B400" t="s" s="2">
-        <v>929</v>
+        <v>930</v>
       </c>
       <c r="C400" t="s" s="2">
-        <v>929</v>
+        <v>930</v>
       </c>
       <c r="D400" s="2"/>
       <c r="E400" t="s" s="2">
@@ -51205,10 +51208,10 @@
         <v>81</v>
       </c>
       <c r="M400" t="s" s="2">
-        <v>907</v>
+        <v>909</v>
       </c>
       <c r="N400" t="s" s="2">
-        <v>848</v>
+        <v>850</v>
       </c>
       <c r="O400" s="2"/>
       <c r="P400" s="2"/>
@@ -51259,7 +51262,7 @@
         <v>74</v>
       </c>
       <c r="AG400" t="s" s="2">
-        <v>849</v>
+        <v>851</v>
       </c>
       <c r="AH400" t="s" s="2">
         <v>80</v>
@@ -51276,13 +51279,13 @@
     </row>
     <row r="401">
       <c r="A401" t="s" s="2">
-        <v>920</v>
+        <v>922</v>
       </c>
       <c r="B401" t="s" s="2">
-        <v>930</v>
+        <v>931</v>
       </c>
       <c r="C401" t="s" s="2">
-        <v>930</v>
+        <v>931</v>
       </c>
       <c r="D401" s="2"/>
       <c r="E401" t="s" s="2">
@@ -51308,10 +51311,10 @@
         <v>81</v>
       </c>
       <c r="M401" t="s" s="2">
-        <v>909</v>
+        <v>911</v>
       </c>
       <c r="N401" t="s" s="2">
-        <v>852</v>
+        <v>854</v>
       </c>
       <c r="O401" s="2"/>
       <c r="P401" s="2"/>
@@ -51362,7 +51365,7 @@
         <v>74</v>
       </c>
       <c r="AG401" t="s" s="2">
-        <v>853</v>
+        <v>855</v>
       </c>
       <c r="AH401" t="s" s="2">
         <v>80</v>
@@ -51379,13 +51382,13 @@
     </row>
     <row r="402">
       <c r="A402" t="s" s="2">
-        <v>920</v>
+        <v>922</v>
       </c>
       <c r="B402" t="s" s="2">
-        <v>931</v>
+        <v>932</v>
       </c>
       <c r="C402" t="s" s="2">
-        <v>931</v>
+        <v>932</v>
       </c>
       <c r="D402" s="2"/>
       <c r="E402" t="s" s="2">
@@ -51408,13 +51411,13 @@
         <v>74</v>
       </c>
       <c r="L402" t="s" s="2">
-        <v>855</v>
+        <v>857</v>
       </c>
       <c r="M402" t="s" s="2">
-        <v>856</v>
+        <v>858</v>
       </c>
       <c r="N402" t="s" s="2">
-        <v>856</v>
+        <v>858</v>
       </c>
       <c r="O402" s="2"/>
       <c r="P402" s="2"/>
@@ -51465,7 +51468,7 @@
         <v>74</v>
       </c>
       <c r="AG402" t="s" s="2">
-        <v>857</v>
+        <v>859</v>
       </c>
       <c r="AH402" t="s" s="2">
         <v>80</v>
@@ -51482,13 +51485,13 @@
     </row>
     <row r="403">
       <c r="A403" t="s" s="2">
-        <v>920</v>
+        <v>922</v>
       </c>
       <c r="B403" t="s" s="2">
-        <v>932</v>
+        <v>933</v>
       </c>
       <c r="C403" t="s" s="2">
-        <v>932</v>
+        <v>933</v>
       </c>
       <c r="D403" s="2"/>
       <c r="E403" t="s" s="2">
@@ -51514,10 +51517,10 @@
         <v>81</v>
       </c>
       <c r="M403" t="s" s="2">
-        <v>859</v>
+        <v>861</v>
       </c>
       <c r="N403" t="s" s="2">
-        <v>859</v>
+        <v>861</v>
       </c>
       <c r="O403" s="2"/>
       <c r="P403" s="2"/>
@@ -51568,7 +51571,7 @@
         <v>74</v>
       </c>
       <c r="AG403" t="s" s="2">
-        <v>860</v>
+        <v>862</v>
       </c>
       <c r="AH403" t="s" s="2">
         <v>75</v>
@@ -51585,13 +51588,13 @@
     </row>
     <row r="404">
       <c r="A404" t="s" s="2">
-        <v>920</v>
+        <v>922</v>
       </c>
       <c r="B404" t="s" s="2">
-        <v>933</v>
+        <v>934</v>
       </c>
       <c r="C404" t="s" s="2">
-        <v>933</v>
+        <v>934</v>
       </c>
       <c r="D404" s="2"/>
       <c r="E404" t="s" s="2">
@@ -51617,10 +51620,10 @@
         <v>81</v>
       </c>
       <c r="M404" t="s" s="2">
-        <v>863</v>
+        <v>865</v>
       </c>
       <c r="N404" t="s" s="2">
-        <v>863</v>
+        <v>865</v>
       </c>
       <c r="O404" s="2"/>
       <c r="P404" s="2"/>
@@ -51632,7 +51635,7 @@
         <v>74</v>
       </c>
       <c r="T404" t="s" s="2">
-        <v>892</v>
+        <v>894</v>
       </c>
       <c r="U404" t="s" s="2">
         <v>74</v>
@@ -51671,7 +51674,7 @@
         <v>74</v>
       </c>
       <c r="AG404" t="s" s="2">
-        <v>864</v>
+        <v>866</v>
       </c>
       <c r="AH404" t="s" s="2">
         <v>80</v>
@@ -51688,13 +51691,13 @@
     </row>
     <row r="405">
       <c r="A405" t="s" s="2">
-        <v>920</v>
+        <v>922</v>
       </c>
       <c r="B405" t="s" s="2">
-        <v>934</v>
+        <v>935</v>
       </c>
       <c r="C405" t="s" s="2">
-        <v>934</v>
+        <v>935</v>
       </c>
       <c r="D405" s="2"/>
       <c r="E405" t="s" s="2">
@@ -51720,10 +51723,10 @@
         <v>81</v>
       </c>
       <c r="M405" t="s" s="2">
-        <v>866</v>
+        <v>868</v>
       </c>
       <c r="N405" t="s" s="2">
-        <v>866</v>
+        <v>868</v>
       </c>
       <c r="O405" s="2"/>
       <c r="P405" s="2"/>
@@ -51774,7 +51777,7 @@
         <v>74</v>
       </c>
       <c r="AG405" t="s" s="2">
-        <v>867</v>
+        <v>869</v>
       </c>
       <c r="AH405" t="s" s="2">
         <v>80</v>
@@ -51791,13 +51794,13 @@
     </row>
     <row r="406">
       <c r="A406" t="s" s="2">
-        <v>920</v>
+        <v>922</v>
       </c>
       <c r="B406" t="s" s="2">
-        <v>935</v>
+        <v>936</v>
       </c>
       <c r="C406" t="s" s="2">
-        <v>935</v>
+        <v>936</v>
       </c>
       <c r="D406" s="2"/>
       <c r="E406" t="s" s="2">
@@ -51823,10 +51826,10 @@
         <v>393</v>
       </c>
       <c r="M406" t="s" s="2">
-        <v>869</v>
+        <v>871</v>
       </c>
       <c r="N406" t="s" s="2">
-        <v>869</v>
+        <v>871</v>
       </c>
       <c r="O406" s="2"/>
       <c r="P406" s="2"/>
@@ -51838,7 +51841,7 @@
         <v>74</v>
       </c>
       <c r="T406" t="s" s="2">
-        <v>917</v>
+        <v>919</v>
       </c>
       <c r="U406" t="s" s="2">
         <v>74</v>
@@ -51877,7 +51880,7 @@
         <v>74</v>
       </c>
       <c r="AG406" t="s" s="2">
-        <v>871</v>
+        <v>873</v>
       </c>
       <c r="AH406" t="s" s="2">
         <v>80</v>
@@ -51894,13 +51897,13 @@
     </row>
     <row r="407">
       <c r="A407" t="s" s="2">
-        <v>920</v>
+        <v>922</v>
       </c>
       <c r="B407" t="s" s="2">
-        <v>936</v>
+        <v>937</v>
       </c>
       <c r="C407" t="s" s="2">
-        <v>936</v>
+        <v>937</v>
       </c>
       <c r="D407" s="2"/>
       <c r="E407" t="s" s="2">
@@ -51926,10 +51929,10 @@
         <v>393</v>
       </c>
       <c r="M407" t="s" s="2">
-        <v>873</v>
+        <v>875</v>
       </c>
       <c r="N407" t="s" s="2">
-        <v>873</v>
+        <v>875</v>
       </c>
       <c r="O407" s="2"/>
       <c r="P407" s="2"/>
@@ -51941,7 +51944,7 @@
         <v>74</v>
       </c>
       <c r="T407" t="s" s="2">
-        <v>919</v>
+        <v>921</v>
       </c>
       <c r="U407" t="s" s="2">
         <v>74</v>
@@ -51980,7 +51983,7 @@
         <v>74</v>
       </c>
       <c r="AG407" t="s" s="2">
-        <v>875</v>
+        <v>877</v>
       </c>
       <c r="AH407" t="s" s="2">
         <v>80</v>
@@ -51997,13 +52000,13 @@
     </row>
     <row r="408">
       <c r="A408" t="s" s="2">
-        <v>937</v>
+        <v>938</v>
       </c>
       <c r="B408" t="s" s="2">
-        <v>937</v>
+        <v>938</v>
       </c>
       <c r="C408" t="s" s="2">
-        <v>937</v>
+        <v>938</v>
       </c>
       <c r="D408" s="2"/>
       <c r="E408" t="s" s="2">
@@ -52029,10 +52032,10 @@
         <v>77</v>
       </c>
       <c r="M408" t="s" s="2">
-        <v>940</v>
+        <v>941</v>
       </c>
       <c r="N408" t="s" s="2">
-        <v>941</v>
+        <v>942</v>
       </c>
       <c r="O408" s="2"/>
       <c r="P408" s="2"/>
@@ -52100,13 +52103,13 @@
     </row>
     <row r="409">
       <c r="A409" t="s" s="2">
-        <v>937</v>
+        <v>938</v>
       </c>
       <c r="B409" t="s" s="2">
-        <v>842</v>
+        <v>844</v>
       </c>
       <c r="C409" t="s" s="2">
-        <v>842</v>
+        <v>844</v>
       </c>
       <c r="D409" s="2"/>
       <c r="E409" t="s" s="2">
@@ -52129,13 +52132,13 @@
         <v>74</v>
       </c>
       <c r="L409" t="s" s="2">
-        <v>839</v>
+        <v>841</v>
       </c>
       <c r="M409" t="s" s="2">
-        <v>840</v>
+        <v>842</v>
       </c>
       <c r="N409" t="s" s="2">
-        <v>840</v>
+        <v>842</v>
       </c>
       <c r="O409" s="2"/>
       <c r="P409" s="2"/>
@@ -52186,7 +52189,7 @@
         <v>74</v>
       </c>
       <c r="AG409" t="s" s="2">
-        <v>842</v>
+        <v>844</v>
       </c>
       <c r="AH409" t="s" s="2">
         <v>80</v>
@@ -52203,13 +52206,13 @@
     </row>
     <row r="410">
       <c r="A410" t="s" s="2">
-        <v>937</v>
+        <v>938</v>
       </c>
       <c r="B410" t="s" s="2">
-        <v>849</v>
+        <v>851</v>
       </c>
       <c r="C410" t="s" s="2">
-        <v>849</v>
+        <v>851</v>
       </c>
       <c r="D410" s="2"/>
       <c r="E410" t="s" s="2">
@@ -52235,10 +52238,10 @@
         <v>81</v>
       </c>
       <c r="M410" t="s" s="2">
-        <v>848</v>
+        <v>850</v>
       </c>
       <c r="N410" t="s" s="2">
-        <v>848</v>
+        <v>850</v>
       </c>
       <c r="O410" s="2"/>
       <c r="P410" s="2"/>
@@ -52289,7 +52292,7 @@
         <v>74</v>
       </c>
       <c r="AG410" t="s" s="2">
-        <v>849</v>
+        <v>851</v>
       </c>
       <c r="AH410" t="s" s="2">
         <v>80</v>
@@ -52306,13 +52309,13 @@
     </row>
     <row r="411">
       <c r="A411" t="s" s="2">
-        <v>937</v>
+        <v>938</v>
       </c>
       <c r="B411" t="s" s="2">
-        <v>853</v>
+        <v>855</v>
       </c>
       <c r="C411" t="s" s="2">
-        <v>853</v>
+        <v>855</v>
       </c>
       <c r="D411" s="2"/>
       <c r="E411" t="s" s="2">
@@ -52338,10 +52341,10 @@
         <v>81</v>
       </c>
       <c r="M411" t="s" s="2">
-        <v>852</v>
+        <v>854</v>
       </c>
       <c r="N411" t="s" s="2">
-        <v>852</v>
+        <v>854</v>
       </c>
       <c r="O411" s="2"/>
       <c r="P411" s="2"/>
@@ -52392,7 +52395,7 @@
         <v>74</v>
       </c>
       <c r="AG411" t="s" s="2">
-        <v>853</v>
+        <v>855</v>
       </c>
       <c r="AH411" t="s" s="2">
         <v>80</v>
@@ -52409,13 +52412,13 @@
     </row>
     <row r="412">
       <c r="A412" t="s" s="2">
-        <v>937</v>
+        <v>938</v>
       </c>
       <c r="B412" t="s" s="2">
-        <v>857</v>
+        <v>859</v>
       </c>
       <c r="C412" t="s" s="2">
-        <v>857</v>
+        <v>859</v>
       </c>
       <c r="D412" s="2"/>
       <c r="E412" t="s" s="2">
@@ -52438,13 +52441,13 @@
         <v>74</v>
       </c>
       <c r="L412" t="s" s="2">
-        <v>855</v>
+        <v>857</v>
       </c>
       <c r="M412" t="s" s="2">
-        <v>856</v>
+        <v>858</v>
       </c>
       <c r="N412" t="s" s="2">
-        <v>856</v>
+        <v>858</v>
       </c>
       <c r="O412" s="2"/>
       <c r="P412" s="2"/>
@@ -52495,7 +52498,7 @@
         <v>74</v>
       </c>
       <c r="AG412" t="s" s="2">
-        <v>857</v>
+        <v>859</v>
       </c>
       <c r="AH412" t="s" s="2">
         <v>80</v>
@@ -52512,13 +52515,13 @@
     </row>
     <row r="413">
       <c r="A413" t="s" s="2">
-        <v>937</v>
+        <v>938</v>
       </c>
       <c r="B413" t="s" s="2">
-        <v>860</v>
+        <v>862</v>
       </c>
       <c r="C413" t="s" s="2">
-        <v>860</v>
+        <v>862</v>
       </c>
       <c r="D413" s="2"/>
       <c r="E413" t="s" s="2">
@@ -52544,10 +52547,10 @@
         <v>81</v>
       </c>
       <c r="M413" t="s" s="2">
-        <v>859</v>
+        <v>861</v>
       </c>
       <c r="N413" t="s" s="2">
-        <v>859</v>
+        <v>861</v>
       </c>
       <c r="O413" s="2"/>
       <c r="P413" s="2"/>
@@ -52598,7 +52601,7 @@
         <v>74</v>
       </c>
       <c r="AG413" t="s" s="2">
-        <v>860</v>
+        <v>862</v>
       </c>
       <c r="AH413" t="s" s="2">
         <v>75</v>
@@ -52615,13 +52618,13 @@
     </row>
     <row r="414">
       <c r="A414" t="s" s="2">
-        <v>937</v>
+        <v>938</v>
       </c>
       <c r="B414" t="s" s="2">
-        <v>864</v>
+        <v>866</v>
       </c>
       <c r="C414" t="s" s="2">
-        <v>864</v>
+        <v>866</v>
       </c>
       <c r="D414" s="2"/>
       <c r="E414" t="s" s="2">
@@ -52647,10 +52650,10 @@
         <v>81</v>
       </c>
       <c r="M414" t="s" s="2">
-        <v>863</v>
+        <v>865</v>
       </c>
       <c r="N414" t="s" s="2">
-        <v>863</v>
+        <v>865</v>
       </c>
       <c r="O414" s="2"/>
       <c r="P414" s="2"/>
@@ -52701,7 +52704,7 @@
         <v>74</v>
       </c>
       <c r="AG414" t="s" s="2">
-        <v>864</v>
+        <v>866</v>
       </c>
       <c r="AH414" t="s" s="2">
         <v>80</v>
@@ -52718,13 +52721,13 @@
     </row>
     <row r="415">
       <c r="A415" t="s" s="2">
-        <v>937</v>
+        <v>938</v>
       </c>
       <c r="B415" t="s" s="2">
-        <v>867</v>
+        <v>869</v>
       </c>
       <c r="C415" t="s" s="2">
-        <v>867</v>
+        <v>869</v>
       </c>
       <c r="D415" s="2"/>
       <c r="E415" t="s" s="2">
@@ -52750,10 +52753,10 @@
         <v>81</v>
       </c>
       <c r="M415" t="s" s="2">
-        <v>866</v>
+        <v>868</v>
       </c>
       <c r="N415" t="s" s="2">
-        <v>866</v>
+        <v>868</v>
       </c>
       <c r="O415" s="2"/>
       <c r="P415" s="2"/>
@@ -52804,7 +52807,7 @@
         <v>74</v>
       </c>
       <c r="AG415" t="s" s="2">
-        <v>867</v>
+        <v>869</v>
       </c>
       <c r="AH415" t="s" s="2">
         <v>80</v>
@@ -52821,13 +52824,13 @@
     </row>
     <row r="416">
       <c r="A416" t="s" s="2">
-        <v>937</v>
+        <v>938</v>
       </c>
       <c r="B416" t="s" s="2">
-        <v>871</v>
+        <v>873</v>
       </c>
       <c r="C416" t="s" s="2">
-        <v>871</v>
+        <v>873</v>
       </c>
       <c r="D416" s="2"/>
       <c r="E416" t="s" s="2">
@@ -52853,10 +52856,10 @@
         <v>393</v>
       </c>
       <c r="M416" t="s" s="2">
-        <v>869</v>
+        <v>871</v>
       </c>
       <c r="N416" t="s" s="2">
-        <v>869</v>
+        <v>871</v>
       </c>
       <c r="O416" s="2"/>
       <c r="P416" s="2"/>
@@ -52907,7 +52910,7 @@
         <v>74</v>
       </c>
       <c r="AG416" t="s" s="2">
-        <v>871</v>
+        <v>873</v>
       </c>
       <c r="AH416" t="s" s="2">
         <v>80</v>
@@ -52924,13 +52927,13 @@
     </row>
     <row r="417">
       <c r="A417" t="s" s="2">
-        <v>937</v>
+        <v>938</v>
       </c>
       <c r="B417" t="s" s="2">
-        <v>875</v>
+        <v>877</v>
       </c>
       <c r="C417" t="s" s="2">
-        <v>875</v>
+        <v>877</v>
       </c>
       <c r="D417" s="2"/>
       <c r="E417" t="s" s="2">
@@ -52956,10 +52959,10 @@
         <v>393</v>
       </c>
       <c r="M417" t="s" s="2">
-        <v>873</v>
+        <v>875</v>
       </c>
       <c r="N417" t="s" s="2">
-        <v>873</v>
+        <v>875</v>
       </c>
       <c r="O417" s="2"/>
       <c r="P417" s="2"/>
@@ -53010,7 +53013,7 @@
         <v>74</v>
       </c>
       <c r="AG417" t="s" s="2">
-        <v>875</v>
+        <v>877</v>
       </c>
       <c r="AH417" t="s" s="2">
         <v>80</v>
@@ -53027,13 +53030,13 @@
     </row>
     <row r="418">
       <c r="A418" t="s" s="2">
-        <v>942</v>
+        <v>943</v>
       </c>
       <c r="B418" t="s" s="2">
-        <v>942</v>
+        <v>943</v>
       </c>
       <c r="C418" t="s" s="2">
-        <v>942</v>
+        <v>943</v>
       </c>
       <c r="D418" s="2"/>
       <c r="E418" t="s" s="2">
@@ -53059,10 +53062,10 @@
         <v>77</v>
       </c>
       <c r="M418" t="s" s="2">
-        <v>945</v>
+        <v>946</v>
       </c>
       <c r="N418" t="s" s="2">
-        <v>946</v>
+        <v>947</v>
       </c>
       <c r="O418" s="2"/>
       <c r="P418" s="2"/>
@@ -53130,13 +53133,13 @@
     </row>
     <row r="419">
       <c r="A419" t="s" s="2">
-        <v>942</v>
+        <v>943</v>
       </c>
       <c r="B419" t="s" s="2">
-        <v>947</v>
+        <v>948</v>
       </c>
       <c r="C419" t="s" s="2">
-        <v>947</v>
+        <v>948</v>
       </c>
       <c r="D419" s="2"/>
       <c r="E419" t="s" s="2">
@@ -53216,7 +53219,7 @@
         <v>74</v>
       </c>
       <c r="AG419" t="s" s="2">
-        <v>947</v>
+        <v>948</v>
       </c>
       <c r="AH419" t="s" s="2">
         <v>80</v>
@@ -53233,13 +53236,13 @@
     </row>
     <row r="420">
       <c r="A420" t="s" s="2">
-        <v>942</v>
+        <v>943</v>
       </c>
       <c r="B420" t="s" s="2">
-        <v>948</v>
+        <v>949</v>
       </c>
       <c r="C420" t="s" s="2">
-        <v>948</v>
+        <v>949</v>
       </c>
       <c r="D420" s="2"/>
       <c r="E420" t="s" s="2">
@@ -53319,7 +53322,7 @@
         <v>74</v>
       </c>
       <c r="AG420" t="s" s="2">
-        <v>948</v>
+        <v>949</v>
       </c>
       <c r="AH420" t="s" s="2">
         <v>80</v>
@@ -53336,13 +53339,13 @@
     </row>
     <row r="421">
       <c r="A421" t="s" s="2">
-        <v>942</v>
+        <v>943</v>
       </c>
       <c r="B421" t="s" s="2">
-        <v>949</v>
+        <v>950</v>
       </c>
       <c r="C421" t="s" s="2">
-        <v>949</v>
+        <v>950</v>
       </c>
       <c r="D421" s="2"/>
       <c r="E421" t="s" s="2">
@@ -53422,7 +53425,7 @@
         <v>74</v>
       </c>
       <c r="AG421" t="s" s="2">
-        <v>949</v>
+        <v>950</v>
       </c>
       <c r="AH421" t="s" s="2">
         <v>80</v>
@@ -53439,13 +53442,13 @@
     </row>
     <row r="422">
       <c r="A422" t="s" s="2">
-        <v>950</v>
+        <v>951</v>
       </c>
       <c r="B422" t="s" s="2">
-        <v>950</v>
+        <v>951</v>
       </c>
       <c r="C422" t="s" s="2">
-        <v>950</v>
+        <v>951</v>
       </c>
       <c r="D422" s="2"/>
       <c r="E422" t="s" s="2">
@@ -53471,10 +53474,10 @@
         <v>77</v>
       </c>
       <c r="M422" t="s" s="2">
-        <v>953</v>
+        <v>954</v>
       </c>
       <c r="N422" t="s" s="2">
-        <v>954</v>
+        <v>955</v>
       </c>
       <c r="O422" s="2"/>
       <c r="P422" s="2"/>
@@ -53542,13 +53545,13 @@
     </row>
     <row r="423">
       <c r="A423" t="s" s="2">
-        <v>950</v>
+        <v>951</v>
       </c>
       <c r="B423" t="s" s="2">
-        <v>955</v>
+        <v>956</v>
       </c>
       <c r="C423" t="s" s="2">
-        <v>955</v>
+        <v>956</v>
       </c>
       <c r="D423" s="2"/>
       <c r="E423" t="s" s="2">
@@ -53574,10 +53577,10 @@
         <v>393</v>
       </c>
       <c r="M423" t="s" s="2">
-        <v>956</v>
+        <v>957</v>
       </c>
       <c r="N423" t="s" s="2">
-        <v>956</v>
+        <v>957</v>
       </c>
       <c r="O423" s="2"/>
       <c r="P423" s="2"/>
@@ -53608,7 +53611,7 @@
       </c>
       <c r="Z423" s="2"/>
       <c r="AA423" t="s" s="2">
-        <v>957</v>
+        <v>958</v>
       </c>
       <c r="AB423" t="s" s="2">
         <v>74</v>
@@ -53626,7 +53629,7 @@
         <v>74</v>
       </c>
       <c r="AG423" t="s" s="2">
-        <v>955</v>
+        <v>956</v>
       </c>
       <c r="AH423" t="s" s="2">
         <v>80</v>
@@ -53643,13 +53646,13 @@
     </row>
     <row r="424">
       <c r="A424" t="s" s="2">
-        <v>950</v>
+        <v>951</v>
       </c>
       <c r="B424" t="s" s="2">
-        <v>958</v>
+        <v>959</v>
       </c>
       <c r="C424" t="s" s="2">
-        <v>958</v>
+        <v>959</v>
       </c>
       <c r="D424" s="2"/>
       <c r="E424" t="s" s="2">
@@ -53672,13 +53675,13 @@
         <v>74</v>
       </c>
       <c r="L424" t="s" s="2">
-        <v>959</v>
+        <v>960</v>
       </c>
       <c r="M424" t="s" s="2">
-        <v>960</v>
+        <v>961</v>
       </c>
       <c r="N424" t="s" s="2">
-        <v>960</v>
+        <v>961</v>
       </c>
       <c r="O424" s="2"/>
       <c r="P424" s="2"/>
@@ -53729,7 +53732,7 @@
         <v>74</v>
       </c>
       <c r="AG424" t="s" s="2">
-        <v>958</v>
+        <v>959</v>
       </c>
       <c r="AH424" t="s" s="2">
         <v>80</v>
@@ -53746,13 +53749,13 @@
     </row>
     <row r="425">
       <c r="A425" t="s" s="2">
-        <v>950</v>
+        <v>951</v>
       </c>
       <c r="B425" t="s" s="2">
-        <v>961</v>
+        <v>962</v>
       </c>
       <c r="C425" t="s" s="2">
-        <v>961</v>
+        <v>962</v>
       </c>
       <c r="D425" s="2"/>
       <c r="E425" t="s" s="2">
@@ -53775,13 +53778,13 @@
         <v>74</v>
       </c>
       <c r="L425" t="s" s="2">
-        <v>959</v>
+        <v>960</v>
       </c>
       <c r="M425" t="s" s="2">
-        <v>962</v>
+        <v>963</v>
       </c>
       <c r="N425" t="s" s="2">
-        <v>962</v>
+        <v>963</v>
       </c>
       <c r="O425" s="2"/>
       <c r="P425" s="2"/>
@@ -53832,7 +53835,7 @@
         <v>74</v>
       </c>
       <c r="AG425" t="s" s="2">
-        <v>961</v>
+        <v>962</v>
       </c>
       <c r="AH425" t="s" s="2">
         <v>80</v>
@@ -53849,13 +53852,13 @@
     </row>
     <row r="426">
       <c r="A426" t="s" s="2">
-        <v>963</v>
+        <v>964</v>
       </c>
       <c r="B426" t="s" s="2">
-        <v>963</v>
+        <v>964</v>
       </c>
       <c r="C426" t="s" s="2">
-        <v>963</v>
+        <v>964</v>
       </c>
       <c r="D426" s="2"/>
       <c r="E426" t="s" s="2">
@@ -53881,10 +53884,10 @@
         <v>77</v>
       </c>
       <c r="M426" t="s" s="2">
-        <v>966</v>
+        <v>967</v>
       </c>
       <c r="N426" t="s" s="2">
-        <v>967</v>
+        <v>968</v>
       </c>
       <c r="O426" s="2"/>
       <c r="P426" s="2"/>
@@ -53952,13 +53955,13 @@
     </row>
     <row r="427">
       <c r="A427" t="s" s="2">
-        <v>963</v>
+        <v>964</v>
       </c>
       <c r="B427" t="s" s="2">
-        <v>968</v>
+        <v>969</v>
       </c>
       <c r="C427" t="s" s="2">
-        <v>968</v>
+        <v>969</v>
       </c>
       <c r="D427" s="2"/>
       <c r="E427" t="s" s="2">
@@ -53981,13 +53984,13 @@
         <v>74</v>
       </c>
       <c r="L427" t="s" s="2">
-        <v>969</v>
+        <v>970</v>
       </c>
       <c r="M427" t="s" s="2">
-        <v>970</v>
+        <v>971</v>
       </c>
       <c r="N427" t="s" s="2">
-        <v>970</v>
+        <v>971</v>
       </c>
       <c r="O427" s="2"/>
       <c r="P427" s="2"/>
@@ -54038,7 +54041,7 @@
         <v>74</v>
       </c>
       <c r="AG427" t="s" s="2">
-        <v>968</v>
+        <v>969</v>
       </c>
       <c r="AH427" t="s" s="2">
         <v>75</v>
@@ -54055,13 +54058,13 @@
     </row>
     <row r="428">
       <c r="A428" t="s" s="2">
-        <v>963</v>
+        <v>964</v>
       </c>
       <c r="B428" t="s" s="2">
-        <v>971</v>
+        <v>972</v>
       </c>
       <c r="C428" t="s" s="2">
-        <v>971</v>
+        <v>972</v>
       </c>
       <c r="D428" s="2"/>
       <c r="E428" t="s" s="2">
@@ -54084,13 +54087,13 @@
         <v>74</v>
       </c>
       <c r="L428" t="s" s="2">
-        <v>972</v>
+        <v>973</v>
       </c>
       <c r="M428" t="s" s="2">
-        <v>973</v>
+        <v>974</v>
       </c>
       <c r="N428" t="s" s="2">
-        <v>973</v>
+        <v>974</v>
       </c>
       <c r="O428" s="2"/>
       <c r="P428" s="2"/>
@@ -54141,7 +54144,7 @@
         <v>74</v>
       </c>
       <c r="AG428" t="s" s="2">
-        <v>971</v>
+        <v>972</v>
       </c>
       <c r="AH428" t="s" s="2">
         <v>80</v>
@@ -54158,13 +54161,13 @@
     </row>
     <row r="429">
       <c r="A429" t="s" s="2">
-        <v>963</v>
+        <v>964</v>
       </c>
       <c r="B429" t="s" s="2">
-        <v>974</v>
+        <v>975</v>
       </c>
       <c r="C429" t="s" s="2">
-        <v>974</v>
+        <v>975</v>
       </c>
       <c r="D429" s="2"/>
       <c r="E429" t="s" s="2">
@@ -54187,13 +54190,13 @@
         <v>74</v>
       </c>
       <c r="L429" t="s" s="2">
-        <v>975</v>
+        <v>976</v>
       </c>
       <c r="M429" t="s" s="2">
-        <v>976</v>
+        <v>977</v>
       </c>
       <c r="N429" t="s" s="2">
-        <v>977</v>
+        <v>978</v>
       </c>
       <c r="O429" s="2"/>
       <c r="P429" s="2"/>
@@ -54224,7 +54227,7 @@
       </c>
       <c r="Z429" s="2"/>
       <c r="AA429" t="s" s="2">
-        <v>978</v>
+        <v>979</v>
       </c>
       <c r="AB429" t="s" s="2">
         <v>74</v>
@@ -54242,7 +54245,7 @@
         <v>74</v>
       </c>
       <c r="AG429" t="s" s="2">
-        <v>974</v>
+        <v>975</v>
       </c>
       <c r="AH429" t="s" s="2">
         <v>75</v>
@@ -54259,13 +54262,13 @@
     </row>
     <row r="430">
       <c r="A430" t="s" s="2">
-        <v>963</v>
+        <v>964</v>
       </c>
       <c r="B430" t="s" s="2">
-        <v>979</v>
+        <v>980</v>
       </c>
       <c r="C430" t="s" s="2">
-        <v>979</v>
+        <v>980</v>
       </c>
       <c r="D430" s="2"/>
       <c r="E430" t="s" s="2">
@@ -54288,13 +54291,13 @@
         <v>74</v>
       </c>
       <c r="L430" t="s" s="2">
-        <v>975</v>
+        <v>976</v>
       </c>
       <c r="M430" t="s" s="2">
-        <v>980</v>
+        <v>981</v>
       </c>
       <c r="N430" t="s" s="2">
-        <v>981</v>
+        <v>982</v>
       </c>
       <c r="O430" s="2"/>
       <c r="P430" s="2"/>
@@ -54325,7 +54328,7 @@
       </c>
       <c r="Z430" s="2"/>
       <c r="AA430" t="s" s="2">
-        <v>982</v>
+        <v>983</v>
       </c>
       <c r="AB430" t="s" s="2">
         <v>74</v>
@@ -54343,7 +54346,7 @@
         <v>74</v>
       </c>
       <c r="AG430" t="s" s="2">
-        <v>979</v>
+        <v>980</v>
       </c>
       <c r="AH430" t="s" s="2">
         <v>75</v>
@@ -54360,13 +54363,13 @@
     </row>
     <row r="431">
       <c r="A431" t="s" s="2">
-        <v>983</v>
+        <v>984</v>
       </c>
       <c r="B431" t="s" s="2">
-        <v>983</v>
+        <v>984</v>
       </c>
       <c r="C431" t="s" s="2">
-        <v>983</v>
+        <v>984</v>
       </c>
       <c r="D431" s="2"/>
       <c r="E431" t="s" s="2">
@@ -54392,10 +54395,10 @@
         <v>77</v>
       </c>
       <c r="M431" t="s" s="2">
-        <v>986</v>
+        <v>987</v>
       </c>
       <c r="N431" t="s" s="2">
-        <v>987</v>
+        <v>988</v>
       </c>
       <c r="O431" s="2"/>
       <c r="P431" s="2"/>
@@ -54463,13 +54466,13 @@
     </row>
     <row r="432">
       <c r="A432" t="s" s="2">
-        <v>983</v>
+        <v>984</v>
       </c>
       <c r="B432" t="s" s="2">
-        <v>989</v>
+        <v>990</v>
       </c>
       <c r="C432" t="s" s="2">
-        <v>989</v>
+        <v>990</v>
       </c>
       <c r="D432" s="2"/>
       <c r="E432" t="s" s="2">
@@ -54492,13 +54495,13 @@
         <v>74</v>
       </c>
       <c r="L432" t="s" s="2">
-        <v>969</v>
+        <v>970</v>
       </c>
       <c r="M432" t="s" s="2">
-        <v>990</v>
+        <v>991</v>
       </c>
       <c r="N432" t="s" s="2">
-        <v>970</v>
+        <v>971</v>
       </c>
       <c r="O432" s="2"/>
       <c r="P432" s="2"/>
@@ -54549,7 +54552,7 @@
         <v>74</v>
       </c>
       <c r="AG432" t="s" s="2">
-        <v>968</v>
+        <v>969</v>
       </c>
       <c r="AH432" t="s" s="2">
         <v>75</v>
@@ -54566,13 +54569,13 @@
     </row>
     <row r="433">
       <c r="A433" t="s" s="2">
-        <v>983</v>
+        <v>984</v>
       </c>
       <c r="B433" t="s" s="2">
-        <v>991</v>
+        <v>992</v>
       </c>
       <c r="C433" t="s" s="2">
-        <v>991</v>
+        <v>992</v>
       </c>
       <c r="D433" s="2"/>
       <c r="E433" t="s" s="2">
@@ -54595,13 +54598,13 @@
         <v>74</v>
       </c>
       <c r="L433" t="s" s="2">
-        <v>972</v>
+        <v>973</v>
       </c>
       <c r="M433" t="s" s="2">
-        <v>992</v>
+        <v>993</v>
       </c>
       <c r="N433" t="s" s="2">
-        <v>973</v>
+        <v>974</v>
       </c>
       <c r="O433" s="2"/>
       <c r="P433" s="2"/>
@@ -54652,7 +54655,7 @@
         <v>74</v>
       </c>
       <c r="AG433" t="s" s="2">
-        <v>971</v>
+        <v>972</v>
       </c>
       <c r="AH433" t="s" s="2">
         <v>80</v>
@@ -54669,13 +54672,13 @@
     </row>
     <row r="434">
       <c r="A434" t="s" s="2">
-        <v>983</v>
+        <v>984</v>
       </c>
       <c r="B434" t="s" s="2">
-        <v>993</v>
+        <v>994</v>
       </c>
       <c r="C434" t="s" s="2">
-        <v>993</v>
+        <v>994</v>
       </c>
       <c r="D434" s="2"/>
       <c r="E434" t="s" s="2">
@@ -54698,13 +54701,13 @@
         <v>74</v>
       </c>
       <c r="L434" t="s" s="2">
-        <v>975</v>
+        <v>976</v>
       </c>
       <c r="M434" t="s" s="2">
-        <v>994</v>
+        <v>995</v>
       </c>
       <c r="N434" t="s" s="2">
-        <v>977</v>
+        <v>978</v>
       </c>
       <c r="O434" s="2"/>
       <c r="P434" s="2"/>
@@ -54735,7 +54738,7 @@
       </c>
       <c r="Z434" s="2"/>
       <c r="AA434" t="s" s="2">
-        <v>978</v>
+        <v>979</v>
       </c>
       <c r="AB434" t="s" s="2">
         <v>74</v>
@@ -54753,7 +54756,7 @@
         <v>74</v>
       </c>
       <c r="AG434" t="s" s="2">
-        <v>974</v>
+        <v>975</v>
       </c>
       <c r="AH434" t="s" s="2">
         <v>75</v>
@@ -54770,13 +54773,13 @@
     </row>
     <row r="435">
       <c r="A435" t="s" s="2">
-        <v>983</v>
+        <v>984</v>
       </c>
       <c r="B435" t="s" s="2">
-        <v>995</v>
+        <v>996</v>
       </c>
       <c r="C435" t="s" s="2">
-        <v>995</v>
+        <v>996</v>
       </c>
       <c r="D435" s="2"/>
       <c r="E435" t="s" s="2">
@@ -54799,13 +54802,13 @@
         <v>74</v>
       </c>
       <c r="L435" t="s" s="2">
-        <v>975</v>
+        <v>976</v>
       </c>
       <c r="M435" t="s" s="2">
-        <v>980</v>
+        <v>981</v>
       </c>
       <c r="N435" t="s" s="2">
-        <v>981</v>
+        <v>982</v>
       </c>
       <c r="O435" s="2"/>
       <c r="P435" s="2"/>
@@ -54836,7 +54839,7 @@
       </c>
       <c r="Z435" s="2"/>
       <c r="AA435" t="s" s="2">
-        <v>982</v>
+        <v>983</v>
       </c>
       <c r="AB435" t="s" s="2">
         <v>74</v>
@@ -54854,7 +54857,7 @@
         <v>74</v>
       </c>
       <c r="AG435" t="s" s="2">
-        <v>979</v>
+        <v>980</v>
       </c>
       <c r="AH435" t="s" s="2">
         <v>75</v>
@@ -54871,13 +54874,13 @@
     </row>
     <row r="436">
       <c r="A436" t="s" s="2">
-        <v>996</v>
+        <v>997</v>
       </c>
       <c r="B436" t="s" s="2">
-        <v>996</v>
+        <v>997</v>
       </c>
       <c r="C436" t="s" s="2">
-        <v>996</v>
+        <v>997</v>
       </c>
       <c r="D436" s="2"/>
       <c r="E436" t="s" s="2">
@@ -54903,10 +54906,10 @@
         <v>77</v>
       </c>
       <c r="M436" t="s" s="2">
-        <v>999</v>
+        <v>1000</v>
       </c>
       <c r="N436" t="s" s="2">
-        <v>1000</v>
+        <v>1001</v>
       </c>
       <c r="O436" s="2"/>
       <c r="P436" s="2"/>
@@ -54974,13 +54977,13 @@
     </row>
     <row r="437">
       <c r="A437" t="s" s="2">
-        <v>996</v>
+        <v>997</v>
       </c>
       <c r="B437" t="s" s="2">
-        <v>1001</v>
+        <v>1002</v>
       </c>
       <c r="C437" t="s" s="2">
-        <v>1001</v>
+        <v>1002</v>
       </c>
       <c r="D437" s="2"/>
       <c r="E437" t="s" s="2">
@@ -55006,10 +55009,10 @@
         <v>81</v>
       </c>
       <c r="M437" t="s" s="2">
-        <v>1002</v>
+        <v>1003</v>
       </c>
       <c r="N437" t="s" s="2">
-        <v>1002</v>
+        <v>1003</v>
       </c>
       <c r="O437" s="2"/>
       <c r="P437" s="2"/>
@@ -55024,7 +55027,7 @@
         <v>74</v>
       </c>
       <c r="U437" t="s" s="2">
-        <v>1003</v>
+        <v>1004</v>
       </c>
       <c r="V437" t="s" s="2">
         <v>74</v>
@@ -55060,7 +55063,7 @@
         <v>74</v>
       </c>
       <c r="AG437" t="s" s="2">
-        <v>1001</v>
+        <v>1002</v>
       </c>
       <c r="AH437" t="s" s="2">
         <v>80</v>
@@ -55077,13 +55080,13 @@
     </row>
     <row r="438">
       <c r="A438" t="s" s="2">
-        <v>996</v>
+        <v>997</v>
       </c>
       <c r="B438" t="s" s="2">
-        <v>1004</v>
+        <v>1005</v>
       </c>
       <c r="C438" t="s" s="2">
-        <v>1004</v>
+        <v>1005</v>
       </c>
       <c r="D438" s="2"/>
       <c r="E438" t="s" s="2">
@@ -55106,13 +55109,13 @@
         <v>74</v>
       </c>
       <c r="L438" t="s" s="2">
-        <v>855</v>
+        <v>857</v>
       </c>
       <c r="M438" t="s" s="2">
-        <v>856</v>
+        <v>858</v>
       </c>
       <c r="N438" t="s" s="2">
-        <v>1005</v>
+        <v>1006</v>
       </c>
       <c r="O438" s="2"/>
       <c r="P438" s="2"/>
@@ -55163,7 +55166,7 @@
         <v>74</v>
       </c>
       <c r="AG438" t="s" s="2">
-        <v>1004</v>
+        <v>1005</v>
       </c>
       <c r="AH438" t="s" s="2">
         <v>80</v>
@@ -55180,13 +55183,13 @@
     </row>
     <row r="439">
       <c r="A439" t="s" s="2">
-        <v>996</v>
+        <v>997</v>
       </c>
       <c r="B439" t="s" s="2">
-        <v>1006</v>
+        <v>1007</v>
       </c>
       <c r="C439" t="s" s="2">
-        <v>1006</v>
+        <v>1007</v>
       </c>
       <c r="D439" s="2"/>
       <c r="E439" t="s" s="2">
@@ -55212,10 +55215,10 @@
         <v>81</v>
       </c>
       <c r="M439" t="s" s="2">
-        <v>859</v>
+        <v>861</v>
       </c>
       <c r="N439" t="s" s="2">
-        <v>859</v>
+        <v>861</v>
       </c>
       <c r="O439" s="2"/>
       <c r="P439" s="2"/>
@@ -55266,7 +55269,7 @@
         <v>74</v>
       </c>
       <c r="AG439" t="s" s="2">
-        <v>1006</v>
+        <v>1007</v>
       </c>
       <c r="AH439" t="s" s="2">
         <v>75</v>
@@ -55283,13 +55286,13 @@
     </row>
     <row r="440">
       <c r="A440" t="s" s="2">
-        <v>996</v>
+        <v>997</v>
       </c>
       <c r="B440" t="s" s="2">
-        <v>1007</v>
+        <v>1008</v>
       </c>
       <c r="C440" t="s" s="2">
-        <v>1007</v>
+        <v>1008</v>
       </c>
       <c r="D440" s="2"/>
       <c r="E440" t="s" s="2">
@@ -55315,10 +55318,10 @@
         <v>81</v>
       </c>
       <c r="M440" t="s" s="2">
-        <v>863</v>
+        <v>865</v>
       </c>
       <c r="N440" t="s" s="2">
-        <v>863</v>
+        <v>865</v>
       </c>
       <c r="O440" s="2"/>
       <c r="P440" s="2"/>
@@ -55333,43 +55336,43 @@
         <v>74</v>
       </c>
       <c r="U440" t="s" s="2">
+        <v>1009</v>
+      </c>
+      <c r="V440" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="W440" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="X440" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Y440" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Z440" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AA440" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AB440" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AC440" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AD440" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AE440" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AF440" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AG440" t="s" s="2">
         <v>1008</v>
-      </c>
-      <c r="V440" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="W440" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="X440" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="Y440" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="Z440" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AA440" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AB440" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AC440" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AD440" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AE440" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AF440" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AG440" t="s" s="2">
-        <v>1007</v>
       </c>
       <c r="AH440" t="s" s="2">
         <v>80</v>
@@ -55386,13 +55389,13 @@
     </row>
     <row r="441">
       <c r="A441" t="s" s="2">
-        <v>996</v>
+        <v>997</v>
       </c>
       <c r="B441" t="s" s="2">
-        <v>1009</v>
+        <v>1010</v>
       </c>
       <c r="C441" t="s" s="2">
-        <v>1009</v>
+        <v>1010</v>
       </c>
       <c r="D441" s="2"/>
       <c r="E441" t="s" s="2">
@@ -55418,10 +55421,10 @@
         <v>81</v>
       </c>
       <c r="M441" t="s" s="2">
-        <v>866</v>
+        <v>868</v>
       </c>
       <c r="N441" t="s" s="2">
-        <v>866</v>
+        <v>868</v>
       </c>
       <c r="O441" s="2"/>
       <c r="P441" s="2"/>
@@ -55472,7 +55475,7 @@
         <v>74</v>
       </c>
       <c r="AG441" t="s" s="2">
-        <v>1009</v>
+        <v>1010</v>
       </c>
       <c r="AH441" t="s" s="2">
         <v>80</v>
@@ -55489,13 +55492,13 @@
     </row>
     <row r="442">
       <c r="A442" t="s" s="2">
-        <v>996</v>
+        <v>997</v>
       </c>
       <c r="B442" t="s" s="2">
-        <v>1010</v>
+        <v>1011</v>
       </c>
       <c r="C442" t="s" s="2">
-        <v>1010</v>
+        <v>1011</v>
       </c>
       <c r="D442" s="2"/>
       <c r="E442" t="s" s="2">
@@ -55521,10 +55524,10 @@
         <v>393</v>
       </c>
       <c r="M442" t="s" s="2">
-        <v>873</v>
+        <v>875</v>
       </c>
       <c r="N442" t="s" s="2">
-        <v>873</v>
+        <v>875</v>
       </c>
       <c r="O442" s="2"/>
       <c r="P442" s="2"/>
@@ -55539,43 +55542,43 @@
         <v>74</v>
       </c>
       <c r="U442" t="s" s="2">
+        <v>1012</v>
+      </c>
+      <c r="V442" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="W442" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="X442" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Y442" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Z442" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AA442" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AB442" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AC442" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AD442" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AE442" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AF442" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AG442" t="s" s="2">
         <v>1011</v>
-      </c>
-      <c r="V442" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="W442" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="X442" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="Y442" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="Z442" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AA442" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AB442" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AC442" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AD442" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AE442" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AF442" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AG442" t="s" s="2">
-        <v>1010</v>
       </c>
       <c r="AH442" t="s" s="2">
         <v>80</v>
@@ -55592,13 +55595,13 @@
     </row>
     <row r="443">
       <c r="A443" t="s" s="2">
-        <v>996</v>
+        <v>997</v>
       </c>
       <c r="B443" t="s" s="2">
-        <v>1012</v>
+        <v>1013</v>
       </c>
       <c r="C443" t="s" s="2">
-        <v>1012</v>
+        <v>1013</v>
       </c>
       <c r="D443" s="2"/>
       <c r="E443" t="s" s="2">
@@ -55624,10 +55627,10 @@
         <v>377</v>
       </c>
       <c r="M443" t="s" s="2">
-        <v>1013</v>
+        <v>1014</v>
       </c>
       <c r="N443" t="s" s="2">
-        <v>1013</v>
+        <v>1014</v>
       </c>
       <c r="O443" s="2"/>
       <c r="P443" s="2"/>
@@ -55678,7 +55681,7 @@
         <v>74</v>
       </c>
       <c r="AG443" t="s" s="2">
-        <v>1012</v>
+        <v>1013</v>
       </c>
       <c r="AH443" t="s" s="2">
         <v>80</v>
@@ -55695,13 +55698,13 @@
     </row>
     <row r="444">
       <c r="A444" t="s" s="2">
-        <v>1014</v>
+        <v>1015</v>
       </c>
       <c r="B444" t="s" s="2">
-        <v>1014</v>
+        <v>1015</v>
       </c>
       <c r="C444" t="s" s="2">
-        <v>1014</v>
+        <v>1015</v>
       </c>
       <c r="D444" s="2"/>
       <c r="E444" t="s" s="2">
@@ -55727,10 +55730,10 @@
         <v>77</v>
       </c>
       <c r="M444" t="s" s="2">
-        <v>1017</v>
+        <v>1018</v>
       </c>
       <c r="N444" t="s" s="2">
-        <v>1018</v>
+        <v>1019</v>
       </c>
       <c r="O444" s="2"/>
       <c r="P444" s="2"/>
@@ -55798,13 +55801,13 @@
     </row>
     <row r="445">
       <c r="A445" t="s" s="2">
-        <v>1014</v>
+        <v>1015</v>
       </c>
       <c r="B445" t="s" s="2">
-        <v>1019</v>
+        <v>1020</v>
       </c>
       <c r="C445" t="s" s="2">
-        <v>1019</v>
+        <v>1020</v>
       </c>
       <c r="D445" s="2"/>
       <c r="E445" t="s" s="2">
@@ -55827,13 +55830,13 @@
         <v>74</v>
       </c>
       <c r="L445" t="s" s="2">
-        <v>969</v>
+        <v>970</v>
       </c>
       <c r="M445" t="s" s="2">
-        <v>1020</v>
+        <v>1021</v>
       </c>
       <c r="N445" t="s" s="2">
-        <v>970</v>
+        <v>971</v>
       </c>
       <c r="O445" s="2"/>
       <c r="P445" s="2"/>
@@ -55884,7 +55887,7 @@
         <v>74</v>
       </c>
       <c r="AG445" t="s" s="2">
-        <v>968</v>
+        <v>969</v>
       </c>
       <c r="AH445" t="s" s="2">
         <v>75</v>
@@ -55901,13 +55904,13 @@
     </row>
     <row r="446">
       <c r="A446" t="s" s="2">
-        <v>1014</v>
+        <v>1015</v>
       </c>
       <c r="B446" t="s" s="2">
-        <v>1021</v>
+        <v>1022</v>
       </c>
       <c r="C446" t="s" s="2">
-        <v>1021</v>
+        <v>1022</v>
       </c>
       <c r="D446" s="2"/>
       <c r="E446" t="s" s="2">
@@ -55930,13 +55933,13 @@
         <v>74</v>
       </c>
       <c r="L446" t="s" s="2">
-        <v>972</v>
+        <v>973</v>
       </c>
       <c r="M446" t="s" s="2">
-        <v>1022</v>
+        <v>1023</v>
       </c>
       <c r="N446" t="s" s="2">
-        <v>973</v>
+        <v>974</v>
       </c>
       <c r="O446" s="2"/>
       <c r="P446" s="2"/>
@@ -55987,7 +55990,7 @@
         <v>74</v>
       </c>
       <c r="AG446" t="s" s="2">
-        <v>971</v>
+        <v>972</v>
       </c>
       <c r="AH446" t="s" s="2">
         <v>80</v>
@@ -56004,13 +56007,13 @@
     </row>
     <row r="447">
       <c r="A447" t="s" s="2">
-        <v>1014</v>
+        <v>1015</v>
       </c>
       <c r="B447" t="s" s="2">
-        <v>1023</v>
+        <v>1024</v>
       </c>
       <c r="C447" t="s" s="2">
-        <v>1023</v>
+        <v>1024</v>
       </c>
       <c r="D447" s="2"/>
       <c r="E447" t="s" s="2">
@@ -56033,13 +56036,13 @@
         <v>74</v>
       </c>
       <c r="L447" t="s" s="2">
-        <v>975</v>
+        <v>976</v>
       </c>
       <c r="M447" t="s" s="2">
-        <v>1024</v>
+        <v>1025</v>
       </c>
       <c r="N447" t="s" s="2">
-        <v>977</v>
+        <v>978</v>
       </c>
       <c r="O447" s="2"/>
       <c r="P447" s="2"/>
@@ -56070,7 +56073,7 @@
       </c>
       <c r="Z447" s="2"/>
       <c r="AA447" t="s" s="2">
-        <v>978</v>
+        <v>979</v>
       </c>
       <c r="AB447" t="s" s="2">
         <v>74</v>
@@ -56088,7 +56091,7 @@
         <v>74</v>
       </c>
       <c r="AG447" t="s" s="2">
-        <v>974</v>
+        <v>975</v>
       </c>
       <c r="AH447" t="s" s="2">
         <v>75</v>
@@ -56105,13 +56108,13 @@
     </row>
     <row r="448">
       <c r="A448" t="s" s="2">
-        <v>1014</v>
+        <v>1015</v>
       </c>
       <c r="B448" t="s" s="2">
-        <v>1025</v>
+        <v>1026</v>
       </c>
       <c r="C448" t="s" s="2">
-        <v>1025</v>
+        <v>1026</v>
       </c>
       <c r="D448" s="2"/>
       <c r="E448" t="s" s="2">
@@ -56134,13 +56137,13 @@
         <v>74</v>
       </c>
       <c r="L448" t="s" s="2">
-        <v>975</v>
+        <v>976</v>
       </c>
       <c r="M448" t="s" s="2">
-        <v>980</v>
+        <v>981</v>
       </c>
       <c r="N448" t="s" s="2">
-        <v>981</v>
+        <v>982</v>
       </c>
       <c r="O448" s="2"/>
       <c r="P448" s="2"/>
@@ -56171,7 +56174,7 @@
       </c>
       <c r="Z448" s="2"/>
       <c r="AA448" t="s" s="2">
-        <v>982</v>
+        <v>983</v>
       </c>
       <c r="AB448" t="s" s="2">
         <v>74</v>
@@ -56189,7 +56192,7 @@
         <v>74</v>
       </c>
       <c r="AG448" t="s" s="2">
-        <v>979</v>
+        <v>980</v>
       </c>
       <c r="AH448" t="s" s="2">
         <v>75</v>
@@ -56206,13 +56209,13 @@
     </row>
     <row r="449">
       <c r="A449" t="s" s="2">
-        <v>1026</v>
+        <v>1027</v>
       </c>
       <c r="B449" t="s" s="2">
-        <v>1026</v>
+        <v>1027</v>
       </c>
       <c r="C449" t="s" s="2">
-        <v>1026</v>
+        <v>1027</v>
       </c>
       <c r="D449" s="2"/>
       <c r="E449" t="s" s="2">
@@ -56238,10 +56241,10 @@
         <v>77</v>
       </c>
       <c r="M449" t="s" s="2">
-        <v>1029</v>
+        <v>1030</v>
       </c>
       <c r="N449" t="s" s="2">
-        <v>1030</v>
+        <v>1031</v>
       </c>
       <c r="O449" s="2"/>
       <c r="P449" s="2"/>
@@ -56309,13 +56312,13 @@
     </row>
     <row r="450">
       <c r="A450" t="s" s="2">
-        <v>1026</v>
+        <v>1027</v>
       </c>
       <c r="B450" t="s" s="2">
-        <v>1031</v>
+        <v>1032</v>
       </c>
       <c r="C450" t="s" s="2">
-        <v>1031</v>
+        <v>1032</v>
       </c>
       <c r="D450" s="2"/>
       <c r="E450" t="s" s="2">
@@ -56338,13 +56341,13 @@
         <v>74</v>
       </c>
       <c r="L450" t="s" s="2">
-        <v>959</v>
+        <v>960</v>
       </c>
       <c r="M450" t="s" s="2">
-        <v>1032</v>
+        <v>1033</v>
       </c>
       <c r="N450" t="s" s="2">
-        <v>1033</v>
+        <v>1034</v>
       </c>
       <c r="O450" s="2"/>
       <c r="P450" s="2"/>
@@ -56395,7 +56398,7 @@
         <v>74</v>
       </c>
       <c r="AG450" t="s" s="2">
-        <v>1031</v>
+        <v>1032</v>
       </c>
       <c r="AH450" t="s" s="2">
         <v>80</v>
@@ -56412,13 +56415,13 @@
     </row>
     <row r="451">
       <c r="A451" t="s" s="2">
-        <v>1026</v>
+        <v>1027</v>
       </c>
       <c r="B451" t="s" s="2">
-        <v>1034</v>
+        <v>1035</v>
       </c>
       <c r="C451" t="s" s="2">
-        <v>1034</v>
+        <v>1035</v>
       </c>
       <c r="D451" s="2"/>
       <c r="E451" t="s" s="2">
@@ -56441,13 +56444,13 @@
         <v>74</v>
       </c>
       <c r="L451" t="s" s="2">
-        <v>959</v>
+        <v>960</v>
       </c>
       <c r="M451" t="s" s="2">
-        <v>1035</v>
+        <v>1036</v>
       </c>
       <c r="N451" t="s" s="2">
-        <v>1035</v>
+        <v>1036</v>
       </c>
       <c r="O451" s="2"/>
       <c r="P451" s="2"/>
@@ -56498,7 +56501,7 @@
         <v>74</v>
       </c>
       <c r="AG451" t="s" s="2">
-        <v>1034</v>
+        <v>1035</v>
       </c>
       <c r="AH451" t="s" s="2">
         <v>80</v>
@@ -56515,13 +56518,13 @@
     </row>
     <row r="452">
       <c r="A452" t="s" s="2">
-        <v>1026</v>
+        <v>1027</v>
       </c>
       <c r="B452" t="s" s="2">
-        <v>1036</v>
+        <v>1037</v>
       </c>
       <c r="C452" t="s" s="2">
-        <v>1036</v>
+        <v>1037</v>
       </c>
       <c r="D452" s="2"/>
       <c r="E452" t="s" s="2">
@@ -56547,10 +56550,10 @@
         <v>81</v>
       </c>
       <c r="M452" t="s" s="2">
-        <v>1037</v>
+        <v>1038</v>
       </c>
       <c r="N452" t="s" s="2">
-        <v>1037</v>
+        <v>1038</v>
       </c>
       <c r="O452" s="2"/>
       <c r="P452" s="2"/>
@@ -56601,7 +56604,7 @@
         <v>74</v>
       </c>
       <c r="AG452" t="s" s="2">
-        <v>1036</v>
+        <v>1037</v>
       </c>
       <c r="AH452" t="s" s="2">
         <v>80</v>
@@ -56618,13 +56621,13 @@
     </row>
     <row r="453">
       <c r="A453" t="s" s="2">
-        <v>1026</v>
+        <v>1027</v>
       </c>
       <c r="B453" t="s" s="2">
-        <v>1038</v>
+        <v>1039</v>
       </c>
       <c r="C453" t="s" s="2">
-        <v>1038</v>
+        <v>1039</v>
       </c>
       <c r="D453" s="2"/>
       <c r="E453" t="s" s="2">
@@ -56647,13 +56650,13 @@
         <v>74</v>
       </c>
       <c r="L453" t="s" s="2">
-        <v>975</v>
+        <v>976</v>
       </c>
       <c r="M453" t="s" s="2">
-        <v>1039</v>
+        <v>1040</v>
       </c>
       <c r="N453" t="s" s="2">
-        <v>1040</v>
+        <v>1041</v>
       </c>
       <c r="O453" s="2"/>
       <c r="P453" s="2"/>
@@ -56684,7 +56687,7 @@
       </c>
       <c r="Z453" s="2"/>
       <c r="AA453" t="s" s="2">
-        <v>1041</v>
+        <v>1042</v>
       </c>
       <c r="AB453" t="s" s="2">
         <v>74</v>
@@ -56702,7 +56705,7 @@
         <v>74</v>
       </c>
       <c r="AG453" t="s" s="2">
-        <v>1038</v>
+        <v>1039</v>
       </c>
       <c r="AH453" t="s" s="2">
         <v>80</v>
@@ -56719,13 +56722,13 @@
     </row>
     <row r="454">
       <c r="A454" t="s" s="2">
-        <v>1026</v>
+        <v>1027</v>
       </c>
       <c r="B454" t="s" s="2">
-        <v>1042</v>
+        <v>1043</v>
       </c>
       <c r="C454" t="s" s="2">
-        <v>1042</v>
+        <v>1043</v>
       </c>
       <c r="D454" s="2"/>
       <c r="E454" t="s" s="2">
@@ -56751,10 +56754,10 @@
         <v>81</v>
       </c>
       <c r="M454" t="s" s="2">
-        <v>1043</v>
+        <v>1044</v>
       </c>
       <c r="N454" t="s" s="2">
-        <v>1043</v>
+        <v>1044</v>
       </c>
       <c r="O454" s="2"/>
       <c r="P454" s="2"/>
@@ -56805,7 +56808,7 @@
         <v>74</v>
       </c>
       <c r="AG454" t="s" s="2">
-        <v>1042</v>
+        <v>1043</v>
       </c>
       <c r="AH454" t="s" s="2">
         <v>80</v>
@@ -56822,13 +56825,13 @@
     </row>
     <row r="455">
       <c r="A455" t="s" s="2">
-        <v>1026</v>
+        <v>1027</v>
       </c>
       <c r="B455" t="s" s="2">
-        <v>1044</v>
+        <v>1045</v>
       </c>
       <c r="C455" t="s" s="2">
-        <v>1044</v>
+        <v>1045</v>
       </c>
       <c r="D455" s="2"/>
       <c r="E455" t="s" s="2">
@@ -56854,10 +56857,10 @@
         <v>428</v>
       </c>
       <c r="M455" t="s" s="2">
-        <v>1045</v>
+        <v>1046</v>
       </c>
       <c r="N455" t="s" s="2">
-        <v>1045</v>
+        <v>1046</v>
       </c>
       <c r="O455" s="2"/>
       <c r="P455" s="2"/>
@@ -56908,7 +56911,7 @@
         <v>74</v>
       </c>
       <c r="AG455" t="s" s="2">
-        <v>1044</v>
+        <v>1045</v>
       </c>
       <c r="AH455" t="s" s="2">
         <v>80</v>
@@ -56925,13 +56928,13 @@
     </row>
     <row r="456">
       <c r="A456" t="s" s="2">
-        <v>1026</v>
+        <v>1027</v>
       </c>
       <c r="B456" t="s" s="2">
-        <v>1046</v>
+        <v>1047</v>
       </c>
       <c r="C456" t="s" s="2">
-        <v>1046</v>
+        <v>1047</v>
       </c>
       <c r="D456" s="2"/>
       <c r="E456" t="s" s="2">
@@ -56957,10 +56960,10 @@
         <v>81</v>
       </c>
       <c r="M456" t="s" s="2">
-        <v>1047</v>
+        <v>1048</v>
       </c>
       <c r="N456" t="s" s="2">
-        <v>1048</v>
+        <v>1049</v>
       </c>
       <c r="O456" s="2"/>
       <c r="P456" s="2"/>
@@ -57011,7 +57014,7 @@
         <v>74</v>
       </c>
       <c r="AG456" t="s" s="2">
-        <v>1046</v>
+        <v>1047</v>
       </c>
       <c r="AH456" t="s" s="2">
         <v>80</v>
@@ -57028,13 +57031,13 @@
     </row>
     <row r="457">
       <c r="A457" t="s" s="2">
-        <v>1026</v>
+        <v>1027</v>
       </c>
       <c r="B457" t="s" s="2">
-        <v>1049</v>
+        <v>1050</v>
       </c>
       <c r="C457" t="s" s="2">
-        <v>1049</v>
+        <v>1050</v>
       </c>
       <c r="D457" s="2"/>
       <c r="E457" t="s" s="2">
@@ -57057,13 +57060,13 @@
         <v>74</v>
       </c>
       <c r="L457" t="s" s="2">
-        <v>1050</v>
+        <v>1051</v>
       </c>
       <c r="M457" t="s" s="2">
-        <v>1051</v>
+        <v>1052</v>
       </c>
       <c r="N457" t="s" s="2">
-        <v>1051</v>
+        <v>1052</v>
       </c>
       <c r="O457" s="2"/>
       <c r="P457" s="2"/>
@@ -57114,7 +57117,7 @@
         <v>74</v>
       </c>
       <c r="AG457" t="s" s="2">
-        <v>1049</v>
+        <v>1050</v>
       </c>
       <c r="AH457" t="s" s="2">
         <v>80</v>
@@ -57131,13 +57134,13 @@
     </row>
     <row r="458">
       <c r="A458" t="s" s="2">
-        <v>1026</v>
+        <v>1027</v>
       </c>
       <c r="B458" t="s" s="2">
-        <v>1052</v>
+        <v>1053</v>
       </c>
       <c r="C458" t="s" s="2">
-        <v>1052</v>
+        <v>1053</v>
       </c>
       <c r="D458" s="2"/>
       <c r="E458" t="s" s="2">
@@ -57160,13 +57163,13 @@
         <v>74</v>
       </c>
       <c r="L458" t="s" s="2">
-        <v>1053</v>
+        <v>1054</v>
       </c>
       <c r="M458" t="s" s="2">
-        <v>1054</v>
+        <v>1055</v>
       </c>
       <c r="N458" t="s" s="2">
-        <v>1055</v>
+        <v>1056</v>
       </c>
       <c r="O458" s="2"/>
       <c r="P458" s="2"/>
@@ -57217,7 +57220,7 @@
         <v>74</v>
       </c>
       <c r="AG458" t="s" s="2">
-        <v>1052</v>
+        <v>1053</v>
       </c>
       <c r="AH458" t="s" s="2">
         <v>80</v>
@@ -57234,13 +57237,13 @@
     </row>
     <row r="459">
       <c r="A459" t="s" s="2">
-        <v>1026</v>
+        <v>1027</v>
       </c>
       <c r="B459" t="s" s="2">
-        <v>1056</v>
+        <v>1057</v>
       </c>
       <c r="C459" t="s" s="2">
-        <v>1056</v>
+        <v>1057</v>
       </c>
       <c r="D459" s="2"/>
       <c r="E459" t="s" s="2">
@@ -57263,13 +57266,13 @@
         <v>74</v>
       </c>
       <c r="L459" t="s" s="2">
-        <v>1057</v>
+        <v>1058</v>
       </c>
       <c r="M459" t="s" s="2">
-        <v>1058</v>
+        <v>1059</v>
       </c>
       <c r="N459" t="s" s="2">
-        <v>1058</v>
+        <v>1059</v>
       </c>
       <c r="O459" s="2"/>
       <c r="P459" s="2"/>
@@ -57320,7 +57323,7 @@
         <v>74</v>
       </c>
       <c r="AG459" t="s" s="2">
-        <v>1056</v>
+        <v>1057</v>
       </c>
       <c r="AH459" t="s" s="2">
         <v>80</v>
@@ -57337,13 +57340,13 @@
     </row>
     <row r="460">
       <c r="A460" t="s" s="2">
-        <v>1026</v>
+        <v>1027</v>
       </c>
       <c r="B460" t="s" s="2">
-        <v>1059</v>
+        <v>1060</v>
       </c>
       <c r="C460" t="s" s="2">
-        <v>1059</v>
+        <v>1060</v>
       </c>
       <c r="D460" s="2"/>
       <c r="E460" t="s" s="2">
@@ -57369,10 +57372,10 @@
         <v>226</v>
       </c>
       <c r="M460" t="s" s="2">
-        <v>1060</v>
+        <v>1061</v>
       </c>
       <c r="N460" t="s" s="2">
-        <v>1060</v>
+        <v>1061</v>
       </c>
       <c r="O460" s="2"/>
       <c r="P460" s="2"/>
@@ -57423,7 +57426,7 @@
         <v>74</v>
       </c>
       <c r="AG460" t="s" s="2">
-        <v>1059</v>
+        <v>1060</v>
       </c>
       <c r="AH460" t="s" s="2">
         <v>80</v>
@@ -57440,13 +57443,13 @@
     </row>
     <row r="461">
       <c r="A461" t="s" s="2">
-        <v>1026</v>
+        <v>1027</v>
       </c>
       <c r="B461" t="s" s="2">
-        <v>1061</v>
+        <v>1062</v>
       </c>
       <c r="C461" t="s" s="2">
-        <v>1061</v>
+        <v>1062</v>
       </c>
       <c r="D461" s="2"/>
       <c r="E461" t="s" s="2">
@@ -57472,10 +57475,10 @@
         <v>226</v>
       </c>
       <c r="M461" t="s" s="2">
-        <v>1062</v>
+        <v>1063</v>
       </c>
       <c r="N461" t="s" s="2">
-        <v>1062</v>
+        <v>1063</v>
       </c>
       <c r="O461" s="2"/>
       <c r="P461" s="2"/>
@@ -57526,7 +57529,7 @@
         <v>74</v>
       </c>
       <c r="AG461" t="s" s="2">
-        <v>1061</v>
+        <v>1062</v>
       </c>
       <c r="AH461" t="s" s="2">
         <v>75</v>
@@ -57543,13 +57546,13 @@
     </row>
     <row r="462">
       <c r="A462" t="s" s="2">
-        <v>1026</v>
+        <v>1027</v>
       </c>
       <c r="B462" t="s" s="2">
-        <v>1063</v>
+        <v>1064</v>
       </c>
       <c r="C462" t="s" s="2">
-        <v>1063</v>
+        <v>1064</v>
       </c>
       <c r="D462" s="2"/>
       <c r="E462" t="s" s="2">
@@ -57572,13 +57575,13 @@
         <v>74</v>
       </c>
       <c r="L462" t="s" s="2">
-        <v>1064</v>
+        <v>1065</v>
       </c>
       <c r="M462" t="s" s="2">
-        <v>1065</v>
+        <v>1066</v>
       </c>
       <c r="N462" t="s" s="2">
-        <v>1065</v>
+        <v>1066</v>
       </c>
       <c r="O462" s="2"/>
       <c r="P462" s="2"/>
@@ -57629,7 +57632,7 @@
         <v>74</v>
       </c>
       <c r="AG462" t="s" s="2">
-        <v>1063</v>
+        <v>1064</v>
       </c>
       <c r="AH462" t="s" s="2">
         <v>80</v>
@@ -57646,13 +57649,13 @@
     </row>
     <row r="463">
       <c r="A463" t="s" s="2">
-        <v>1026</v>
+        <v>1027</v>
       </c>
       <c r="B463" t="s" s="2">
-        <v>1066</v>
+        <v>1067</v>
       </c>
       <c r="C463" t="s" s="2">
-        <v>1066</v>
+        <v>1067</v>
       </c>
       <c r="D463" s="2"/>
       <c r="E463" t="s" s="2">
@@ -57675,13 +57678,13 @@
         <v>74</v>
       </c>
       <c r="L463" t="s" s="2">
-        <v>1067</v>
+        <v>1068</v>
       </c>
       <c r="M463" t="s" s="2">
-        <v>1068</v>
+        <v>1069</v>
       </c>
       <c r="N463" t="s" s="2">
-        <v>1068</v>
+        <v>1069</v>
       </c>
       <c r="O463" s="2"/>
       <c r="P463" s="2"/>
@@ -57732,7 +57735,7 @@
         <v>74</v>
       </c>
       <c r="AG463" t="s" s="2">
-        <v>1066</v>
+        <v>1067</v>
       </c>
       <c r="AH463" t="s" s="2">
         <v>80</v>
@@ -57749,13 +57752,13 @@
     </row>
     <row r="464">
       <c r="A464" t="s" s="2">
-        <v>1026</v>
+        <v>1027</v>
       </c>
       <c r="B464" t="s" s="2">
-        <v>1069</v>
+        <v>1070</v>
       </c>
       <c r="C464" t="s" s="2">
-        <v>1069</v>
+        <v>1070</v>
       </c>
       <c r="D464" s="2"/>
       <c r="E464" t="s" s="2">
@@ -57781,10 +57784,10 @@
         <v>484</v>
       </c>
       <c r="M464" t="s" s="2">
-        <v>1070</v>
+        <v>1071</v>
       </c>
       <c r="N464" t="s" s="2">
-        <v>1070</v>
+        <v>1071</v>
       </c>
       <c r="O464" s="2"/>
       <c r="P464" s="2"/>
@@ -57835,7 +57838,7 @@
         <v>74</v>
       </c>
       <c r="AG464" t="s" s="2">
-        <v>1069</v>
+        <v>1070</v>
       </c>
       <c r="AH464" t="s" s="2">
         <v>80</v>
@@ -57852,13 +57855,13 @@
     </row>
     <row r="465">
       <c r="A465" t="s" s="2">
-        <v>1026</v>
+        <v>1027</v>
       </c>
       <c r="B465" t="s" s="2">
-        <v>1071</v>
+        <v>1072</v>
       </c>
       <c r="C465" t="s" s="2">
-        <v>1071</v>
+        <v>1072</v>
       </c>
       <c r="D465" s="2"/>
       <c r="E465" t="s" s="2">
@@ -57884,10 +57887,10 @@
         <v>81</v>
       </c>
       <c r="M465" t="s" s="2">
-        <v>1072</v>
+        <v>1073</v>
       </c>
       <c r="N465" t="s" s="2">
-        <v>1072</v>
+        <v>1073</v>
       </c>
       <c r="O465" s="2"/>
       <c r="P465" s="2"/>
@@ -57938,7 +57941,7 @@
         <v>74</v>
       </c>
       <c r="AG465" t="s" s="2">
-        <v>1071</v>
+        <v>1072</v>
       </c>
       <c r="AH465" t="s" s="2">
         <v>80</v>
@@ -57955,13 +57958,13 @@
     </row>
     <row r="466">
       <c r="A466" t="s" s="2">
-        <v>1026</v>
+        <v>1027</v>
       </c>
       <c r="B466" t="s" s="2">
-        <v>1073</v>
+        <v>1074</v>
       </c>
       <c r="C466" t="s" s="2">
-        <v>1073</v>
+        <v>1074</v>
       </c>
       <c r="D466" s="2"/>
       <c r="E466" t="s" s="2">
@@ -57987,10 +57990,10 @@
         <v>81</v>
       </c>
       <c r="M466" t="s" s="2">
-        <v>1074</v>
+        <v>1075</v>
       </c>
       <c r="N466" t="s" s="2">
-        <v>1074</v>
+        <v>1075</v>
       </c>
       <c r="O466" s="2"/>
       <c r="P466" s="2"/>
@@ -58041,7 +58044,7 @@
         <v>74</v>
       </c>
       <c r="AG466" t="s" s="2">
-        <v>1073</v>
+        <v>1074</v>
       </c>
       <c r="AH466" t="s" s="2">
         <v>75</v>
@@ -58058,13 +58061,13 @@
     </row>
     <row r="467">
       <c r="A467" t="s" s="2">
-        <v>1026</v>
+        <v>1027</v>
       </c>
       <c r="B467" t="s" s="2">
-        <v>1075</v>
+        <v>1076</v>
       </c>
       <c r="C467" t="s" s="2">
-        <v>1075</v>
+        <v>1076</v>
       </c>
       <c r="D467" s="2"/>
       <c r="E467" t="s" s="2">
@@ -58087,13 +58090,13 @@
         <v>74</v>
       </c>
       <c r="L467" t="s" s="2">
-        <v>1076</v>
+        <v>1077</v>
       </c>
       <c r="M467" t="s" s="2">
-        <v>1077</v>
+        <v>1078</v>
       </c>
       <c r="N467" t="s" s="2">
-        <v>1077</v>
+        <v>1078</v>
       </c>
       <c r="O467" s="2"/>
       <c r="P467" s="2"/>
@@ -58144,7 +58147,7 @@
         <v>74</v>
       </c>
       <c r="AG467" t="s" s="2">
-        <v>1075</v>
+        <v>1076</v>
       </c>
       <c r="AH467" t="s" s="2">
         <v>80</v>
@@ -58161,13 +58164,13 @@
     </row>
     <row r="468">
       <c r="A468" t="s" s="2">
-        <v>1026</v>
+        <v>1027</v>
       </c>
       <c r="B468" t="s" s="2">
-        <v>1078</v>
+        <v>1079</v>
       </c>
       <c r="C468" t="s" s="2">
-        <v>1078</v>
+        <v>1079</v>
       </c>
       <c r="D468" s="2"/>
       <c r="E468" t="s" s="2">
@@ -58193,10 +58196,10 @@
         <v>187</v>
       </c>
       <c r="M468" t="s" s="2">
-        <v>1079</v>
+        <v>1080</v>
       </c>
       <c r="N468" t="s" s="2">
-        <v>1079</v>
+        <v>1080</v>
       </c>
       <c r="O468" s="2"/>
       <c r="P468" s="2"/>
@@ -58247,7 +58250,7 @@
         <v>74</v>
       </c>
       <c r="AG468" t="s" s="2">
-        <v>1078</v>
+        <v>1079</v>
       </c>
       <c r="AH468" t="s" s="2">
         <v>80</v>
@@ -58264,13 +58267,13 @@
     </row>
     <row r="469">
       <c r="A469" t="s" s="2">
-        <v>1026</v>
+        <v>1027</v>
       </c>
       <c r="B469" t="s" s="2">
-        <v>1080</v>
+        <v>1081</v>
       </c>
       <c r="C469" t="s" s="2">
-        <v>1080</v>
+        <v>1081</v>
       </c>
       <c r="D469" s="2"/>
       <c r="E469" t="s" s="2">
@@ -58293,13 +58296,13 @@
         <v>74</v>
       </c>
       <c r="L469" t="s" s="2">
-        <v>975</v>
+        <v>976</v>
       </c>
       <c r="M469" t="s" s="2">
-        <v>1081</v>
+        <v>1082</v>
       </c>
       <c r="N469" t="s" s="2">
-        <v>1082</v>
+        <v>1083</v>
       </c>
       <c r="O469" s="2"/>
       <c r="P469" s="2"/>
@@ -58330,7 +58333,7 @@
       </c>
       <c r="Z469" s="2"/>
       <c r="AA469" t="s" s="2">
-        <v>1083</v>
+        <v>1084</v>
       </c>
       <c r="AB469" t="s" s="2">
         <v>74</v>
@@ -58348,7 +58351,7 @@
         <v>74</v>
       </c>
       <c r="AG469" t="s" s="2">
-        <v>1080</v>
+        <v>1081</v>
       </c>
       <c r="AH469" t="s" s="2">
         <v>80</v>
@@ -58365,13 +58368,13 @@
     </row>
     <row r="470">
       <c r="A470" t="s" s="2">
-        <v>1026</v>
+        <v>1027</v>
       </c>
       <c r="B470" t="s" s="2">
-        <v>1084</v>
+        <v>1085</v>
       </c>
       <c r="C470" t="s" s="2">
-        <v>1084</v>
+        <v>1085</v>
       </c>
       <c r="D470" s="2"/>
       <c r="E470" t="s" s="2">
@@ -58382,7 +58385,7 @@
         <v>80</v>
       </c>
       <c r="H470" t="s" s="2">
-        <v>1085</v>
+        <v>1086</v>
       </c>
       <c r="I470" t="s" s="2">
         <v>74</v>
@@ -58394,13 +58397,13 @@
         <v>74</v>
       </c>
       <c r="L470" t="s" s="2">
-        <v>975</v>
+        <v>976</v>
       </c>
       <c r="M470" t="s" s="2">
-        <v>1086</v>
+        <v>1087</v>
       </c>
       <c r="N470" t="s" s="2">
-        <v>1087</v>
+        <v>1088</v>
       </c>
       <c r="O470" s="2"/>
       <c r="P470" s="2"/>
@@ -58431,7 +58434,7 @@
       </c>
       <c r="Z470" s="2"/>
       <c r="AA470" t="s" s="2">
-        <v>1088</v>
+        <v>1089</v>
       </c>
       <c r="AB470" t="s" s="2">
         <v>74</v>
@@ -58449,13 +58452,13 @@
         <v>74</v>
       </c>
       <c r="AG470" t="s" s="2">
-        <v>1084</v>
+        <v>1085</v>
       </c>
       <c r="AH470" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AI470" t="s" s="2">
-        <v>1085</v>
+        <v>1086</v>
       </c>
       <c r="AJ470" t="s" s="2">
         <v>74</v>
@@ -58466,13 +58469,13 @@
     </row>
     <row r="471">
       <c r="A471" t="s" s="2">
-        <v>1026</v>
+        <v>1027</v>
       </c>
       <c r="B471" t="s" s="2">
-        <v>1089</v>
+        <v>1090</v>
       </c>
       <c r="C471" t="s" s="2">
-        <v>1089</v>
+        <v>1090</v>
       </c>
       <c r="D471" s="2"/>
       <c r="E471" t="s" s="2">
@@ -58495,13 +58498,13 @@
         <v>74</v>
       </c>
       <c r="L471" t="s" s="2">
-        <v>1090</v>
+        <v>1091</v>
       </c>
       <c r="M471" t="s" s="2">
-        <v>1091</v>
+        <v>1092</v>
       </c>
       <c r="N471" t="s" s="2">
-        <v>1091</v>
+        <v>1092</v>
       </c>
       <c r="O471" s="2"/>
       <c r="P471" s="2"/>
@@ -58552,7 +58555,7 @@
         <v>74</v>
       </c>
       <c r="AG471" t="s" s="2">
-        <v>1089</v>
+        <v>1090</v>
       </c>
       <c r="AH471" t="s" s="2">
         <v>75</v>
@@ -58569,13 +58572,13 @@
     </row>
     <row r="472">
       <c r="A472" t="s" s="2">
-        <v>1026</v>
+        <v>1027</v>
       </c>
       <c r="B472" t="s" s="2">
-        <v>1092</v>
+        <v>1093</v>
       </c>
       <c r="C472" t="s" s="2">
-        <v>1092</v>
+        <v>1093</v>
       </c>
       <c r="D472" s="2"/>
       <c r="E472" t="s" s="2">
@@ -58598,13 +58601,13 @@
         <v>74</v>
       </c>
       <c r="L472" t="s" s="2">
-        <v>975</v>
+        <v>976</v>
       </c>
       <c r="M472" t="s" s="2">
-        <v>1093</v>
+        <v>1094</v>
       </c>
       <c r="N472" t="s" s="2">
-        <v>1094</v>
+        <v>1095</v>
       </c>
       <c r="O472" s="2"/>
       <c r="P472" s="2"/>
@@ -58635,7 +58638,7 @@
       </c>
       <c r="Z472" s="2"/>
       <c r="AA472" t="s" s="2">
-        <v>1095</v>
+        <v>1096</v>
       </c>
       <c r="AB472" t="s" s="2">
         <v>74</v>
@@ -58653,7 +58656,7 @@
         <v>74</v>
       </c>
       <c r="AG472" t="s" s="2">
-        <v>1092</v>
+        <v>1093</v>
       </c>
       <c r="AH472" t="s" s="2">
         <v>80</v>
@@ -58670,13 +58673,13 @@
     </row>
     <row r="473">
       <c r="A473" t="s" s="2">
-        <v>1026</v>
+        <v>1027</v>
       </c>
       <c r="B473" t="s" s="2">
-        <v>1096</v>
+        <v>1097</v>
       </c>
       <c r="C473" t="s" s="2">
-        <v>1096</v>
+        <v>1097</v>
       </c>
       <c r="D473" s="2"/>
       <c r="E473" t="s" s="2">
@@ -58699,13 +58702,13 @@
         <v>74</v>
       </c>
       <c r="L473" t="s" s="2">
-        <v>975</v>
+        <v>976</v>
       </c>
       <c r="M473" t="s" s="2">
-        <v>1097</v>
+        <v>1098</v>
       </c>
       <c r="N473" t="s" s="2">
-        <v>1098</v>
+        <v>1099</v>
       </c>
       <c r="O473" s="2"/>
       <c r="P473" s="2"/>
@@ -58736,7 +58739,7 @@
       </c>
       <c r="Z473" s="2"/>
       <c r="AA473" t="s" s="2">
-        <v>1099</v>
+        <v>1100</v>
       </c>
       <c r="AB473" t="s" s="2">
         <v>74</v>
@@ -58754,7 +58757,7 @@
         <v>74</v>
       </c>
       <c r="AG473" t="s" s="2">
-        <v>1096</v>
+        <v>1097</v>
       </c>
       <c r="AH473" t="s" s="2">
         <v>80</v>
@@ -58771,13 +58774,13 @@
     </row>
     <row r="474">
       <c r="A474" t="s" s="2">
-        <v>1026</v>
+        <v>1027</v>
       </c>
       <c r="B474" t="s" s="2">
-        <v>1100</v>
+        <v>1101</v>
       </c>
       <c r="C474" t="s" s="2">
-        <v>1100</v>
+        <v>1101</v>
       </c>
       <c r="D474" s="2"/>
       <c r="E474" t="s" s="2">
@@ -58800,13 +58803,13 @@
         <v>74</v>
       </c>
       <c r="L474" t="s" s="2">
-        <v>975</v>
+        <v>976</v>
       </c>
       <c r="M474" t="s" s="2">
-        <v>1101</v>
+        <v>1102</v>
       </c>
       <c r="N474" t="s" s="2">
-        <v>1102</v>
+        <v>1103</v>
       </c>
       <c r="O474" s="2"/>
       <c r="P474" s="2"/>
@@ -58837,7 +58840,7 @@
       </c>
       <c r="Z474" s="2"/>
       <c r="AA474" t="s" s="2">
-        <v>1103</v>
+        <v>1104</v>
       </c>
       <c r="AB474" t="s" s="2">
         <v>74</v>
@@ -58855,7 +58858,7 @@
         <v>74</v>
       </c>
       <c r="AG474" t="s" s="2">
-        <v>1100</v>
+        <v>1101</v>
       </c>
       <c r="AH474" t="s" s="2">
         <v>80</v>
@@ -58872,13 +58875,13 @@
     </row>
     <row r="475">
       <c r="A475" t="s" s="2">
-        <v>1026</v>
+        <v>1027</v>
       </c>
       <c r="B475" t="s" s="2">
-        <v>1104</v>
+        <v>1105</v>
       </c>
       <c r="C475" t="s" s="2">
-        <v>1104</v>
+        <v>1105</v>
       </c>
       <c r="D475" s="2"/>
       <c r="E475" t="s" s="2">
@@ -58901,13 +58904,13 @@
         <v>74</v>
       </c>
       <c r="L475" t="s" s="2">
-        <v>975</v>
+        <v>976</v>
       </c>
       <c r="M475" t="s" s="2">
-        <v>1105</v>
+        <v>1106</v>
       </c>
       <c r="N475" t="s" s="2">
-        <v>1106</v>
+        <v>1107</v>
       </c>
       <c r="O475" s="2"/>
       <c r="P475" s="2"/>
@@ -58938,7 +58941,7 @@
       </c>
       <c r="Z475" s="2"/>
       <c r="AA475" t="s" s="2">
-        <v>1107</v>
+        <v>1108</v>
       </c>
       <c r="AB475" t="s" s="2">
         <v>74</v>
@@ -58956,7 +58959,7 @@
         <v>74</v>
       </c>
       <c r="AG475" t="s" s="2">
-        <v>1104</v>
+        <v>1105</v>
       </c>
       <c r="AH475" t="s" s="2">
         <v>80</v>
@@ -58973,13 +58976,13 @@
     </row>
     <row r="476">
       <c r="A476" t="s" s="2">
-        <v>1026</v>
+        <v>1027</v>
       </c>
       <c r="B476" t="s" s="2">
-        <v>1108</v>
+        <v>1109</v>
       </c>
       <c r="C476" t="s" s="2">
-        <v>1108</v>
+        <v>1109</v>
       </c>
       <c r="D476" s="2"/>
       <c r="E476" t="s" s="2">
@@ -59005,10 +59008,10 @@
         <v>81</v>
       </c>
       <c r="M476" t="s" s="2">
-        <v>1109</v>
+        <v>1110</v>
       </c>
       <c r="N476" t="s" s="2">
-        <v>1109</v>
+        <v>1110</v>
       </c>
       <c r="O476" s="2"/>
       <c r="P476" s="2"/>
@@ -59059,7 +59062,7 @@
         <v>74</v>
       </c>
       <c r="AG476" t="s" s="2">
-        <v>1108</v>
+        <v>1109</v>
       </c>
       <c r="AH476" t="s" s="2">
         <v>75</v>
@@ -59076,13 +59079,13 @@
     </row>
     <row r="477">
       <c r="A477" t="s" s="2">
-        <v>1026</v>
+        <v>1027</v>
       </c>
       <c r="B477" t="s" s="2">
-        <v>1110</v>
+        <v>1111</v>
       </c>
       <c r="C477" t="s" s="2">
-        <v>1110</v>
+        <v>1111</v>
       </c>
       <c r="D477" s="2"/>
       <c r="E477" t="s" s="2">
@@ -59105,13 +59108,13 @@
         <v>74</v>
       </c>
       <c r="L477" t="s" s="2">
-        <v>1057</v>
+        <v>1058</v>
       </c>
       <c r="M477" t="s" s="2">
-        <v>1111</v>
+        <v>1112</v>
       </c>
       <c r="N477" t="s" s="2">
-        <v>1111</v>
+        <v>1112</v>
       </c>
       <c r="O477" s="2"/>
       <c r="P477" s="2"/>
@@ -59162,7 +59165,7 @@
         <v>74</v>
       </c>
       <c r="AG477" t="s" s="2">
-        <v>1110</v>
+        <v>1111</v>
       </c>
       <c r="AH477" t="s" s="2">
         <v>75</v>
@@ -59179,13 +59182,13 @@
     </row>
     <row r="478">
       <c r="A478" t="s" s="2">
-        <v>1026</v>
+        <v>1027</v>
       </c>
       <c r="B478" t="s" s="2">
-        <v>1112</v>
+        <v>1113</v>
       </c>
       <c r="C478" t="s" s="2">
-        <v>1112</v>
+        <v>1113</v>
       </c>
       <c r="D478" s="2"/>
       <c r="E478" t="s" s="2">
@@ -59211,10 +59214,10 @@
         <v>226</v>
       </c>
       <c r="M478" t="s" s="2">
-        <v>1113</v>
+        <v>1114</v>
       </c>
       <c r="N478" t="s" s="2">
-        <v>1113</v>
+        <v>1114</v>
       </c>
       <c r="O478" s="2"/>
       <c r="P478" s="2"/>
@@ -59265,7 +59268,7 @@
         <v>74</v>
       </c>
       <c r="AG478" t="s" s="2">
-        <v>1112</v>
+        <v>1113</v>
       </c>
       <c r="AH478" t="s" s="2">
         <v>80</v>
@@ -59282,13 +59285,13 @@
     </row>
     <row r="479">
       <c r="A479" t="s" s="2">
-        <v>1026</v>
+        <v>1027</v>
       </c>
       <c r="B479" t="s" s="2">
-        <v>1114</v>
+        <v>1115</v>
       </c>
       <c r="C479" t="s" s="2">
-        <v>1114</v>
+        <v>1115</v>
       </c>
       <c r="D479" s="2"/>
       <c r="E479" t="s" s="2">
@@ -59311,13 +59314,13 @@
         <v>74</v>
       </c>
       <c r="L479" t="s" s="2">
-        <v>855</v>
+        <v>857</v>
       </c>
       <c r="M479" t="s" s="2">
-        <v>1115</v>
+        <v>1116</v>
       </c>
       <c r="N479" t="s" s="2">
-        <v>1115</v>
+        <v>1116</v>
       </c>
       <c r="O479" s="2"/>
       <c r="P479" s="2"/>
@@ -59368,7 +59371,7 @@
         <v>74</v>
       </c>
       <c r="AG479" t="s" s="2">
-        <v>1114</v>
+        <v>1115</v>
       </c>
       <c r="AH479" t="s" s="2">
         <v>75</v>
@@ -59385,13 +59388,13 @@
     </row>
     <row r="480">
       <c r="A480" t="s" s="2">
-        <v>1026</v>
+        <v>1027</v>
       </c>
       <c r="B480" t="s" s="2">
-        <v>1116</v>
+        <v>1117</v>
       </c>
       <c r="C480" t="s" s="2">
-        <v>1116</v>
+        <v>1117</v>
       </c>
       <c r="D480" s="2"/>
       <c r="E480" t="s" s="2">
@@ -59417,10 +59420,10 @@
         <v>420</v>
       </c>
       <c r="M480" t="s" s="2">
-        <v>1117</v>
+        <v>1118</v>
       </c>
       <c r="N480" t="s" s="2">
-        <v>1117</v>
+        <v>1118</v>
       </c>
       <c r="O480" s="2"/>
       <c r="P480" s="2"/>
@@ -59471,7 +59474,7 @@
         <v>74</v>
       </c>
       <c r="AG480" t="s" s="2">
-        <v>1116</v>
+        <v>1117</v>
       </c>
       <c r="AH480" t="s" s="2">
         <v>80</v>
@@ -59488,13 +59491,13 @@
     </row>
     <row r="481">
       <c r="A481" t="s" s="2">
-        <v>1026</v>
+        <v>1027</v>
       </c>
       <c r="B481" t="s" s="2">
-        <v>1118</v>
+        <v>1119</v>
       </c>
       <c r="C481" t="s" s="2">
-        <v>1118</v>
+        <v>1119</v>
       </c>
       <c r="D481" s="2"/>
       <c r="E481" t="s" s="2">
@@ -59520,10 +59523,10 @@
         <v>420</v>
       </c>
       <c r="M481" t="s" s="2">
-        <v>1119</v>
+        <v>1120</v>
       </c>
       <c r="N481" t="s" s="2">
-        <v>1119</v>
+        <v>1120</v>
       </c>
       <c r="O481" s="2"/>
       <c r="P481" s="2"/>
@@ -59574,7 +59577,7 @@
         <v>74</v>
       </c>
       <c r="AG481" t="s" s="2">
-        <v>1118</v>
+        <v>1119</v>
       </c>
       <c r="AH481" t="s" s="2">
         <v>80</v>
@@ -59591,13 +59594,13 @@
     </row>
     <row r="482">
       <c r="A482" t="s" s="2">
-        <v>1026</v>
+        <v>1027</v>
       </c>
       <c r="B482" t="s" s="2">
-        <v>1120</v>
+        <v>1121</v>
       </c>
       <c r="C482" t="s" s="2">
-        <v>1120</v>
+        <v>1121</v>
       </c>
       <c r="D482" s="2"/>
       <c r="E482" t="s" s="2">
@@ -59620,13 +59623,13 @@
         <v>74</v>
       </c>
       <c r="L482" t="s" s="2">
-        <v>975</v>
+        <v>976</v>
       </c>
       <c r="M482" t="s" s="2">
-        <v>873</v>
+        <v>875</v>
       </c>
       <c r="N482" t="s" s="2">
-        <v>873</v>
+        <v>875</v>
       </c>
       <c r="O482" s="2"/>
       <c r="P482" s="2"/>
@@ -59657,25 +59660,25 @@
       </c>
       <c r="Z482" s="2"/>
       <c r="AA482" t="s" s="2">
+        <v>1122</v>
+      </c>
+      <c r="AB482" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AC482" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AD482" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AE482" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AF482" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AG482" t="s" s="2">
         <v>1121</v>
-      </c>
-      <c r="AB482" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AC482" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AD482" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AE482" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AF482" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AG482" t="s" s="2">
-        <v>1120</v>
       </c>
       <c r="AH482" t="s" s="2">
         <v>80</v>
@@ -59692,13 +59695,13 @@
     </row>
     <row r="483">
       <c r="A483" t="s" s="2">
-        <v>1122</v>
+        <v>1123</v>
       </c>
       <c r="B483" t="s" s="2">
-        <v>1122</v>
+        <v>1123</v>
       </c>
       <c r="C483" t="s" s="2">
-        <v>1122</v>
+        <v>1123</v>
       </c>
       <c r="D483" s="2"/>
       <c r="E483" t="s" s="2">
@@ -59724,10 +59727,10 @@
         <v>77</v>
       </c>
       <c r="M483" t="s" s="2">
-        <v>1125</v>
+        <v>1126</v>
       </c>
       <c r="N483" t="s" s="2">
-        <v>1126</v>
+        <v>1127</v>
       </c>
       <c r="O483" s="2"/>
       <c r="P483" s="2"/>
@@ -59795,13 +59798,13 @@
     </row>
     <row r="484">
       <c r="A484" t="s" s="2">
-        <v>1122</v>
+        <v>1123</v>
       </c>
       <c r="B484" t="s" s="2">
-        <v>1127</v>
+        <v>1128</v>
       </c>
       <c r="C484" t="s" s="2">
-        <v>1127</v>
+        <v>1128</v>
       </c>
       <c r="D484" s="2"/>
       <c r="E484" t="s" s="2">
@@ -59824,13 +59827,13 @@
         <v>74</v>
       </c>
       <c r="L484" t="s" s="2">
-        <v>975</v>
+        <v>976</v>
       </c>
       <c r="M484" t="s" s="2">
-        <v>1128</v>
+        <v>1129</v>
       </c>
       <c r="N484" t="s" s="2">
-        <v>1128</v>
+        <v>1129</v>
       </c>
       <c r="O484" s="2"/>
       <c r="P484" s="2"/>
@@ -59881,7 +59884,7 @@
         <v>74</v>
       </c>
       <c r="AG484" t="s" s="2">
-        <v>1127</v>
+        <v>1128</v>
       </c>
       <c r="AH484" t="s" s="2">
         <v>80</v>
@@ -59898,13 +59901,13 @@
     </row>
     <row r="485">
       <c r="A485" t="s" s="2">
-        <v>1129</v>
+        <v>1130</v>
       </c>
       <c r="B485" t="s" s="2">
-        <v>1129</v>
+        <v>1130</v>
       </c>
       <c r="C485" t="s" s="2">
-        <v>1129</v>
+        <v>1130</v>
       </c>
       <c r="D485" s="2"/>
       <c r="E485" t="s" s="2">
@@ -59930,10 +59933,10 @@
         <v>77</v>
       </c>
       <c r="M485" t="s" s="2">
-        <v>1132</v>
+        <v>1133</v>
       </c>
       <c r="N485" t="s" s="2">
-        <v>1133</v>
+        <v>1134</v>
       </c>
       <c r="O485" s="2"/>
       <c r="P485" s="2"/>
@@ -60001,13 +60004,13 @@
     </row>
     <row r="486">
       <c r="A486" t="s" s="2">
-        <v>1129</v>
+        <v>1130</v>
       </c>
       <c r="B486" t="s" s="2">
-        <v>845</v>
+        <v>847</v>
       </c>
       <c r="C486" t="s" s="2">
-        <v>845</v>
+        <v>847</v>
       </c>
       <c r="D486" s="2"/>
       <c r="E486" t="s" s="2">
@@ -60030,13 +60033,13 @@
         <v>74</v>
       </c>
       <c r="L486" t="s" s="2">
-        <v>1134</v>
+        <v>1135</v>
       </c>
       <c r="M486" t="s" s="2">
-        <v>844</v>
+        <v>846</v>
       </c>
       <c r="N486" t="s" s="2">
-        <v>844</v>
+        <v>846</v>
       </c>
       <c r="O486" s="2"/>
       <c r="P486" s="2"/>
@@ -60087,7 +60090,7 @@
         <v>74</v>
       </c>
       <c r="AG486" t="s" s="2">
-        <v>845</v>
+        <v>847</v>
       </c>
       <c r="AH486" t="s" s="2">
         <v>80</v>
@@ -60104,13 +60107,13 @@
     </row>
     <row r="487">
       <c r="A487" t="s" s="2">
-        <v>1135</v>
+        <v>1136</v>
       </c>
       <c r="B487" t="s" s="2">
-        <v>1135</v>
+        <v>1136</v>
       </c>
       <c r="C487" t="s" s="2">
-        <v>1135</v>
+        <v>1136</v>
       </c>
       <c r="D487" s="2"/>
       <c r="E487" t="s" s="2">
@@ -60136,10 +60139,10 @@
         <v>77</v>
       </c>
       <c r="M487" t="s" s="2">
-        <v>1138</v>
+        <v>1139</v>
       </c>
       <c r="N487" t="s" s="2">
-        <v>1139</v>
+        <v>1140</v>
       </c>
       <c r="O487" s="2"/>
       <c r="P487" s="2"/>
@@ -60207,13 +60210,13 @@
     </row>
     <row r="488">
       <c r="A488" t="s" s="2">
-        <v>1135</v>
+        <v>1136</v>
       </c>
       <c r="B488" t="s" s="2">
-        <v>1140</v>
+        <v>1141</v>
       </c>
       <c r="C488" t="s" s="2">
-        <v>1140</v>
+        <v>1141</v>
       </c>
       <c r="D488" s="2"/>
       <c r="E488" t="s" s="2">
@@ -60293,7 +60296,7 @@
         <v>74</v>
       </c>
       <c r="AG488" t="s" s="2">
-        <v>1140</v>
+        <v>1141</v>
       </c>
       <c r="AH488" t="s" s="2">
         <v>80</v>
@@ -60310,13 +60313,13 @@
     </row>
     <row r="489">
       <c r="A489" t="s" s="2">
-        <v>1135</v>
+        <v>1136</v>
       </c>
       <c r="B489" t="s" s="2">
-        <v>1141</v>
+        <v>1142</v>
       </c>
       <c r="C489" t="s" s="2">
-        <v>1141</v>
+        <v>1142</v>
       </c>
       <c r="D489" s="2"/>
       <c r="E489" t="s" s="2">
@@ -60342,10 +60345,10 @@
         <v>81</v>
       </c>
       <c r="M489" t="s" s="2">
-        <v>1142</v>
+        <v>1143</v>
       </c>
       <c r="N489" t="s" s="2">
-        <v>1143</v>
+        <v>1144</v>
       </c>
       <c r="O489" s="2"/>
       <c r="P489" s="2"/>
@@ -60396,7 +60399,7 @@
         <v>74</v>
       </c>
       <c r="AG489" t="s" s="2">
-        <v>1141</v>
+        <v>1142</v>
       </c>
       <c r="AH489" t="s" s="2">
         <v>80</v>
@@ -60413,13 +60416,13 @@
     </row>
     <row r="490">
       <c r="A490" t="s" s="2">
-        <v>1135</v>
+        <v>1136</v>
       </c>
       <c r="B490" t="s" s="2">
-        <v>1144</v>
+        <v>1145</v>
       </c>
       <c r="C490" t="s" s="2">
-        <v>1144</v>
+        <v>1145</v>
       </c>
       <c r="D490" s="2"/>
       <c r="E490" t="s" s="2">
@@ -60445,10 +60448,10 @@
         <v>81</v>
       </c>
       <c r="M490" t="s" s="2">
-        <v>1145</v>
+        <v>1146</v>
       </c>
       <c r="N490" t="s" s="2">
-        <v>1145</v>
+        <v>1146</v>
       </c>
       <c r="O490" s="2"/>
       <c r="P490" s="2"/>
@@ -60499,7 +60502,7 @@
         <v>74</v>
       </c>
       <c r="AG490" t="s" s="2">
-        <v>1144</v>
+        <v>1145</v>
       </c>
       <c r="AH490" t="s" s="2">
         <v>80</v>
@@ -60516,13 +60519,13 @@
     </row>
     <row r="491">
       <c r="A491" t="s" s="2">
-        <v>1146</v>
+        <v>1147</v>
       </c>
       <c r="B491" t="s" s="2">
-        <v>1146</v>
+        <v>1147</v>
       </c>
       <c r="C491" t="s" s="2">
-        <v>1146</v>
+        <v>1147</v>
       </c>
       <c r="D491" s="2"/>
       <c r="E491" t="s" s="2">
@@ -60548,10 +60551,10 @@
         <v>77</v>
       </c>
       <c r="M491" t="s" s="2">
-        <v>1149</v>
+        <v>1150</v>
       </c>
       <c r="N491" t="s" s="2">
-        <v>1150</v>
+        <v>1151</v>
       </c>
       <c r="O491" s="2"/>
       <c r="P491" s="2"/>
@@ -60619,13 +60622,13 @@
     </row>
     <row r="492">
       <c r="A492" t="s" s="2">
-        <v>1146</v>
+        <v>1147</v>
       </c>
       <c r="B492" t="s" s="2">
-        <v>1151</v>
+        <v>1152</v>
       </c>
       <c r="C492" t="s" s="2">
-        <v>1151</v>
+        <v>1152</v>
       </c>
       <c r="D492" s="2"/>
       <c r="E492" t="s" s="2">
@@ -60651,10 +60654,10 @@
         <v>81</v>
       </c>
       <c r="M492" t="s" s="2">
-        <v>1152</v>
+        <v>1153</v>
       </c>
       <c r="N492" t="s" s="2">
-        <v>1152</v>
+        <v>1153</v>
       </c>
       <c r="O492" s="2"/>
       <c r="P492" s="2"/>
@@ -60705,7 +60708,7 @@
         <v>74</v>
       </c>
       <c r="AG492" t="s" s="2">
-        <v>1151</v>
+        <v>1152</v>
       </c>
       <c r="AH492" t="s" s="2">
         <v>80</v>
@@ -60722,13 +60725,13 @@
     </row>
     <row r="493">
       <c r="A493" t="s" s="2">
-        <v>1146</v>
+        <v>1147</v>
       </c>
       <c r="B493" t="s" s="2">
-        <v>1153</v>
+        <v>1154</v>
       </c>
       <c r="C493" t="s" s="2">
-        <v>1153</v>
+        <v>1154</v>
       </c>
       <c r="D493" s="2"/>
       <c r="E493" t="s" s="2">
@@ -60754,10 +60757,10 @@
         <v>81</v>
       </c>
       <c r="M493" t="s" s="2">
-        <v>1142</v>
+        <v>1143</v>
       </c>
       <c r="N493" t="s" s="2">
-        <v>1143</v>
+        <v>1144</v>
       </c>
       <c r="O493" s="2"/>
       <c r="P493" s="2"/>
@@ -60808,7 +60811,7 @@
         <v>74</v>
       </c>
       <c r="AG493" t="s" s="2">
-        <v>1153</v>
+        <v>1154</v>
       </c>
       <c r="AH493" t="s" s="2">
         <v>80</v>
@@ -60825,13 +60828,13 @@
     </row>
     <row r="494">
       <c r="A494" t="s" s="2">
-        <v>1146</v>
+        <v>1147</v>
       </c>
       <c r="B494" t="s" s="2">
-        <v>1154</v>
+        <v>1155</v>
       </c>
       <c r="C494" t="s" s="2">
-        <v>1154</v>
+        <v>1155</v>
       </c>
       <c r="D494" s="2"/>
       <c r="E494" t="s" s="2">
@@ -60857,10 +60860,10 @@
         <v>81</v>
       </c>
       <c r="M494" t="s" s="2">
-        <v>1155</v>
+        <v>1156</v>
       </c>
       <c r="N494" t="s" s="2">
-        <v>1155</v>
+        <v>1156</v>
       </c>
       <c r="O494" s="2"/>
       <c r="P494" s="2"/>
@@ -60911,7 +60914,7 @@
         <v>74</v>
       </c>
       <c r="AG494" t="s" s="2">
-        <v>1154</v>
+        <v>1155</v>
       </c>
       <c r="AH494" t="s" s="2">
         <v>80</v>
@@ -60928,13 +60931,13 @@
     </row>
     <row r="495">
       <c r="A495" t="s" s="2">
-        <v>1156</v>
+        <v>1157</v>
       </c>
       <c r="B495" t="s" s="2">
-        <v>1156</v>
+        <v>1157</v>
       </c>
       <c r="C495" t="s" s="2">
-        <v>1156</v>
+        <v>1157</v>
       </c>
       <c r="D495" s="2"/>
       <c r="E495" t="s" s="2">
@@ -60960,10 +60963,10 @@
         <v>77</v>
       </c>
       <c r="M495" t="s" s="2">
-        <v>1159</v>
+        <v>1160</v>
       </c>
       <c r="N495" t="s" s="2">
-        <v>1160</v>
+        <v>1161</v>
       </c>
       <c r="O495" s="2"/>
       <c r="P495" s="2"/>
@@ -61031,13 +61034,13 @@
     </row>
     <row r="496">
       <c r="A496" t="s" s="2">
-        <v>1156</v>
+        <v>1157</v>
       </c>
       <c r="B496" t="s" s="2">
-        <v>1161</v>
+        <v>1162</v>
       </c>
       <c r="C496" t="s" s="2">
-        <v>1161</v>
+        <v>1162</v>
       </c>
       <c r="D496" s="2"/>
       <c r="E496" t="s" s="2">
@@ -61063,10 +61066,10 @@
         <v>187</v>
       </c>
       <c r="M496" t="s" s="2">
-        <v>1162</v>
+        <v>1163</v>
       </c>
       <c r="N496" t="s" s="2">
-        <v>1162</v>
+        <v>1163</v>
       </c>
       <c r="O496" s="2"/>
       <c r="P496" s="2"/>
@@ -61117,7 +61120,7 @@
         <v>74</v>
       </c>
       <c r="AG496" t="s" s="2">
-        <v>1161</v>
+        <v>1162</v>
       </c>
       <c r="AH496" t="s" s="2">
         <v>75</v>
@@ -61134,13 +61137,13 @@
     </row>
     <row r="497">
       <c r="A497" t="s" s="2">
-        <v>1156</v>
+        <v>1157</v>
       </c>
       <c r="B497" t="s" s="2">
-        <v>1163</v>
+        <v>1164</v>
       </c>
       <c r="C497" t="s" s="2">
-        <v>1163</v>
+        <v>1164</v>
       </c>
       <c r="D497" s="2"/>
       <c r="E497" t="s" s="2">
@@ -61166,10 +61169,10 @@
         <v>81</v>
       </c>
       <c r="M497" t="s" s="2">
-        <v>1164</v>
+        <v>1165</v>
       </c>
       <c r="N497" t="s" s="2">
-        <v>1164</v>
+        <v>1165</v>
       </c>
       <c r="O497" s="2"/>
       <c r="P497" s="2"/>
@@ -61220,7 +61223,7 @@
         <v>74</v>
       </c>
       <c r="AG497" t="s" s="2">
-        <v>1163</v>
+        <v>1164</v>
       </c>
       <c r="AH497" t="s" s="2">
         <v>80</v>
@@ -61237,13 +61240,13 @@
     </row>
     <row r="498">
       <c r="A498" t="s" s="2">
-        <v>1156</v>
+        <v>1157</v>
       </c>
       <c r="B498" t="s" s="2">
-        <v>1165</v>
+        <v>1166</v>
       </c>
       <c r="C498" t="s" s="2">
-        <v>1165</v>
+        <v>1166</v>
       </c>
       <c r="D498" s="2"/>
       <c r="E498" t="s" s="2">
@@ -61269,10 +61272,10 @@
         <v>81</v>
       </c>
       <c r="M498" t="s" s="2">
-        <v>1166</v>
+        <v>1167</v>
       </c>
       <c r="N498" t="s" s="2">
-        <v>1166</v>
+        <v>1167</v>
       </c>
       <c r="O498" s="2"/>
       <c r="P498" s="2"/>
@@ -61323,7 +61326,7 @@
         <v>74</v>
       </c>
       <c r="AG498" t="s" s="2">
-        <v>1165</v>
+        <v>1166</v>
       </c>
       <c r="AH498" t="s" s="2">
         <v>75</v>
@@ -61340,13 +61343,13 @@
     </row>
     <row r="499">
       <c r="A499" t="s" s="2">
-        <v>1156</v>
+        <v>1157</v>
       </c>
       <c r="B499" t="s" s="2">
-        <v>1167</v>
+        <v>1168</v>
       </c>
       <c r="C499" t="s" s="2">
-        <v>1167</v>
+        <v>1168</v>
       </c>
       <c r="D499" s="2"/>
       <c r="E499" t="s" s="2">
@@ -61372,10 +61375,10 @@
         <v>81</v>
       </c>
       <c r="M499" t="s" s="2">
-        <v>1168</v>
+        <v>1169</v>
       </c>
       <c r="N499" t="s" s="2">
-        <v>1168</v>
+        <v>1169</v>
       </c>
       <c r="O499" s="2"/>
       <c r="P499" s="2"/>
@@ -61426,7 +61429,7 @@
         <v>74</v>
       </c>
       <c r="AG499" t="s" s="2">
-        <v>1167</v>
+        <v>1168</v>
       </c>
       <c r="AH499" t="s" s="2">
         <v>75</v>
@@ -61443,13 +61446,13 @@
     </row>
     <row r="500">
       <c r="A500" t="s" s="2">
-        <v>1156</v>
+        <v>1157</v>
       </c>
       <c r="B500" t="s" s="2">
-        <v>1169</v>
+        <v>1170</v>
       </c>
       <c r="C500" t="s" s="2">
-        <v>1169</v>
+        <v>1170</v>
       </c>
       <c r="D500" s="2"/>
       <c r="E500" t="s" s="2">
@@ -61475,10 +61478,10 @@
         <v>81</v>
       </c>
       <c r="M500" t="s" s="2">
-        <v>1170</v>
+        <v>1171</v>
       </c>
       <c r="N500" t="s" s="2">
-        <v>1170</v>
+        <v>1171</v>
       </c>
       <c r="O500" s="2"/>
       <c r="P500" s="2"/>
@@ -61529,7 +61532,7 @@
         <v>74</v>
       </c>
       <c r="AG500" t="s" s="2">
-        <v>1169</v>
+        <v>1170</v>
       </c>
       <c r="AH500" t="s" s="2">
         <v>75</v>
@@ -61546,13 +61549,13 @@
     </row>
     <row r="501">
       <c r="A501" t="s" s="2">
-        <v>1156</v>
+        <v>1157</v>
       </c>
       <c r="B501" t="s" s="2">
-        <v>1171</v>
+        <v>1172</v>
       </c>
       <c r="C501" t="s" s="2">
-        <v>1171</v>
+        <v>1172</v>
       </c>
       <c r="D501" s="2"/>
       <c r="E501" t="s" s="2">
@@ -61578,10 +61581,10 @@
         <v>81</v>
       </c>
       <c r="M501" t="s" s="2">
-        <v>1172</v>
+        <v>1173</v>
       </c>
       <c r="N501" t="s" s="2">
-        <v>1172</v>
+        <v>1173</v>
       </c>
       <c r="O501" s="2"/>
       <c r="P501" s="2"/>
@@ -61632,7 +61635,7 @@
         <v>74</v>
       </c>
       <c r="AG501" t="s" s="2">
-        <v>1171</v>
+        <v>1172</v>
       </c>
       <c r="AH501" t="s" s="2">
         <v>75</v>
@@ -61649,13 +61652,13 @@
     </row>
     <row r="502">
       <c r="A502" t="s" s="2">
-        <v>1156</v>
+        <v>1157</v>
       </c>
       <c r="B502" t="s" s="2">
-        <v>1173</v>
+        <v>1174</v>
       </c>
       <c r="C502" t="s" s="2">
-        <v>1173</v>
+        <v>1174</v>
       </c>
       <c r="D502" s="2"/>
       <c r="E502" t="s" s="2">
@@ -61681,10 +61684,10 @@
         <v>81</v>
       </c>
       <c r="M502" t="s" s="2">
-        <v>1174</v>
+        <v>1175</v>
       </c>
       <c r="N502" t="s" s="2">
-        <v>1174</v>
+        <v>1175</v>
       </c>
       <c r="O502" s="2"/>
       <c r="P502" s="2"/>
@@ -61735,7 +61738,7 @@
         <v>74</v>
       </c>
       <c r="AG502" t="s" s="2">
-        <v>1173</v>
+        <v>1174</v>
       </c>
       <c r="AH502" t="s" s="2">
         <v>75</v>
@@ -61752,13 +61755,13 @@
     </row>
     <row r="503">
       <c r="A503" t="s" s="2">
-        <v>1156</v>
+        <v>1157</v>
       </c>
       <c r="B503" t="s" s="2">
-        <v>1175</v>
+        <v>1176</v>
       </c>
       <c r="C503" t="s" s="2">
-        <v>1175</v>
+        <v>1176</v>
       </c>
       <c r="D503" s="2"/>
       <c r="E503" t="s" s="2">
@@ -61784,10 +61787,10 @@
         <v>81</v>
       </c>
       <c r="M503" t="s" s="2">
-        <v>1176</v>
+        <v>1177</v>
       </c>
       <c r="N503" t="s" s="2">
-        <v>1176</v>
+        <v>1177</v>
       </c>
       <c r="O503" s="2"/>
       <c r="P503" s="2"/>
@@ -61838,7 +61841,7 @@
         <v>74</v>
       </c>
       <c r="AG503" t="s" s="2">
-        <v>1175</v>
+        <v>1176</v>
       </c>
       <c r="AH503" t="s" s="2">
         <v>75</v>
@@ -61855,13 +61858,13 @@
     </row>
     <row r="504">
       <c r="A504" t="s" s="2">
-        <v>1156</v>
+        <v>1157</v>
       </c>
       <c r="B504" t="s" s="2">
-        <v>1177</v>
+        <v>1178</v>
       </c>
       <c r="C504" t="s" s="2">
-        <v>1177</v>
+        <v>1178</v>
       </c>
       <c r="D504" s="2"/>
       <c r="E504" t="s" s="2">
@@ -61887,10 +61890,10 @@
         <v>81</v>
       </c>
       <c r="M504" t="s" s="2">
-        <v>1178</v>
+        <v>1179</v>
       </c>
       <c r="N504" t="s" s="2">
-        <v>1178</v>
+        <v>1179</v>
       </c>
       <c r="O504" s="2"/>
       <c r="P504" s="2"/>
@@ -61941,7 +61944,7 @@
         <v>74</v>
       </c>
       <c r="AG504" t="s" s="2">
-        <v>1177</v>
+        <v>1178</v>
       </c>
       <c r="AH504" t="s" s="2">
         <v>75</v>
@@ -61958,13 +61961,13 @@
     </row>
     <row r="505">
       <c r="A505" t="s" s="2">
-        <v>1156</v>
+        <v>1157</v>
       </c>
       <c r="B505" t="s" s="2">
-        <v>1179</v>
+        <v>1180</v>
       </c>
       <c r="C505" t="s" s="2">
-        <v>1179</v>
+        <v>1180</v>
       </c>
       <c r="D505" s="2"/>
       <c r="E505" t="s" s="2">
@@ -61990,10 +61993,10 @@
         <v>81</v>
       </c>
       <c r="M505" t="s" s="2">
-        <v>1180</v>
+        <v>1181</v>
       </c>
       <c r="N505" t="s" s="2">
-        <v>1180</v>
+        <v>1181</v>
       </c>
       <c r="O505" s="2"/>
       <c r="P505" s="2"/>
@@ -62044,7 +62047,7 @@
         <v>74</v>
       </c>
       <c r="AG505" t="s" s="2">
-        <v>1179</v>
+        <v>1180</v>
       </c>
       <c r="AH505" t="s" s="2">
         <v>75</v>
@@ -62061,13 +62064,13 @@
     </row>
     <row r="506">
       <c r="A506" t="s" s="2">
-        <v>1156</v>
+        <v>1157</v>
       </c>
       <c r="B506" t="s" s="2">
-        <v>1181</v>
+        <v>1182</v>
       </c>
       <c r="C506" t="s" s="2">
-        <v>1181</v>
+        <v>1182</v>
       </c>
       <c r="D506" s="2"/>
       <c r="E506" t="s" s="2">
@@ -62093,10 +62096,10 @@
         <v>81</v>
       </c>
       <c r="M506" t="s" s="2">
-        <v>1182</v>
+        <v>1183</v>
       </c>
       <c r="N506" t="s" s="2">
-        <v>1182</v>
+        <v>1183</v>
       </c>
       <c r="O506" s="2"/>
       <c r="P506" s="2"/>
@@ -62147,7 +62150,7 @@
         <v>74</v>
       </c>
       <c r="AG506" t="s" s="2">
-        <v>1181</v>
+        <v>1182</v>
       </c>
       <c r="AH506" t="s" s="2">
         <v>75</v>
@@ -62164,13 +62167,13 @@
     </row>
     <row r="507">
       <c r="A507" t="s" s="2">
-        <v>1183</v>
+        <v>1184</v>
       </c>
       <c r="B507" t="s" s="2">
-        <v>1183</v>
+        <v>1184</v>
       </c>
       <c r="C507" t="s" s="2">
-        <v>1183</v>
+        <v>1184</v>
       </c>
       <c r="D507" s="2"/>
       <c r="E507" t="s" s="2">
@@ -62196,10 +62199,10 @@
         <v>77</v>
       </c>
       <c r="M507" t="s" s="2">
-        <v>1186</v>
+        <v>1187</v>
       </c>
       <c r="N507" t="s" s="2">
-        <v>1187</v>
+        <v>1188</v>
       </c>
       <c r="O507" s="2"/>
       <c r="P507" s="2"/>
@@ -62267,13 +62270,13 @@
     </row>
     <row r="508">
       <c r="A508" t="s" s="2">
-        <v>1183</v>
+        <v>1184</v>
       </c>
       <c r="B508" t="s" s="2">
-        <v>1188</v>
+        <v>1189</v>
       </c>
       <c r="C508" t="s" s="2">
-        <v>1188</v>
+        <v>1189</v>
       </c>
       <c r="D508" s="2"/>
       <c r="E508" t="s" s="2">
@@ -62296,13 +62299,13 @@
         <v>74</v>
       </c>
       <c r="L508" t="s" s="2">
-        <v>959</v>
+        <v>960</v>
       </c>
       <c r="M508" t="s" s="2">
-        <v>1189</v>
+        <v>1190</v>
       </c>
       <c r="N508" t="s" s="2">
-        <v>1189</v>
+        <v>1190</v>
       </c>
       <c r="O508" s="2"/>
       <c r="P508" s="2"/>
@@ -62353,7 +62356,7 @@
         <v>74</v>
       </c>
       <c r="AG508" t="s" s="2">
-        <v>1188</v>
+        <v>1189</v>
       </c>
       <c r="AH508" t="s" s="2">
         <v>80</v>
@@ -62370,13 +62373,13 @@
     </row>
     <row r="509">
       <c r="A509" t="s" s="2">
-        <v>1183</v>
+        <v>1184</v>
       </c>
       <c r="B509" t="s" s="2">
-        <v>1190</v>
+        <v>1191</v>
       </c>
       <c r="C509" t="s" s="2">
-        <v>1190</v>
+        <v>1191</v>
       </c>
       <c r="D509" s="2"/>
       <c r="E509" t="s" s="2">
@@ -62402,10 +62405,10 @@
         <v>393</v>
       </c>
       <c r="M509" t="s" s="2">
-        <v>1191</v>
+        <v>1192</v>
       </c>
       <c r="N509" t="s" s="2">
-        <v>1191</v>
+        <v>1192</v>
       </c>
       <c r="O509" s="2"/>
       <c r="P509" s="2"/>
@@ -62420,7 +62423,7 @@
         <v>74</v>
       </c>
       <c r="U509" t="s" s="2">
-        <v>1192</v>
+        <v>1193</v>
       </c>
       <c r="V509" t="s" s="2">
         <v>74</v>
@@ -62436,7 +62439,7 @@
       </c>
       <c r="Z509" s="2"/>
       <c r="AA509" t="s" s="2">
-        <v>1041</v>
+        <v>1042</v>
       </c>
       <c r="AB509" t="s" s="2">
         <v>74</v>
@@ -62454,7 +62457,7 @@
         <v>74</v>
       </c>
       <c r="AG509" t="s" s="2">
-        <v>1190</v>
+        <v>1191</v>
       </c>
       <c r="AH509" t="s" s="2">
         <v>80</v>
@@ -62471,13 +62474,13 @@
     </row>
     <row r="510">
       <c r="A510" t="s" s="2">
-        <v>1183</v>
+        <v>1184</v>
       </c>
       <c r="B510" t="s" s="2">
-        <v>1193</v>
+        <v>1194</v>
       </c>
       <c r="C510" t="s" s="2">
-        <v>1193</v>
+        <v>1194</v>
       </c>
       <c r="D510" s="2"/>
       <c r="E510" t="s" s="2">
@@ -62503,10 +62506,10 @@
         <v>226</v>
       </c>
       <c r="M510" t="s" s="2">
-        <v>1194</v>
+        <v>1195</v>
       </c>
       <c r="N510" t="s" s="2">
-        <v>1194</v>
+        <v>1195</v>
       </c>
       <c r="O510" s="2"/>
       <c r="P510" s="2"/>
@@ -62557,7 +62560,7 @@
         <v>74</v>
       </c>
       <c r="AG510" t="s" s="2">
-        <v>1193</v>
+        <v>1194</v>
       </c>
       <c r="AH510" t="s" s="2">
         <v>80</v>
@@ -62574,13 +62577,13 @@
     </row>
     <row r="511">
       <c r="A511" t="s" s="2">
-        <v>1183</v>
+        <v>1184</v>
       </c>
       <c r="B511" t="s" s="2">
-        <v>1195</v>
+        <v>1196</v>
       </c>
       <c r="C511" t="s" s="2">
-        <v>1195</v>
+        <v>1196</v>
       </c>
       <c r="D511" s="2"/>
       <c r="E511" t="s" s="2">
@@ -62606,10 +62609,10 @@
         <v>81</v>
       </c>
       <c r="M511" t="s" s="2">
-        <v>1196</v>
+        <v>1197</v>
       </c>
       <c r="N511" t="s" s="2">
-        <v>1196</v>
+        <v>1197</v>
       </c>
       <c r="O511" s="2"/>
       <c r="P511" s="2"/>
@@ -62660,7 +62663,7 @@
         <v>74</v>
       </c>
       <c r="AG511" t="s" s="2">
-        <v>1195</v>
+        <v>1196</v>
       </c>
       <c r="AH511" t="s" s="2">
         <v>75</v>
@@ -62677,13 +62680,13 @@
     </row>
     <row r="512">
       <c r="A512" t="s" s="2">
-        <v>1183</v>
+        <v>1184</v>
       </c>
       <c r="B512" t="s" s="2">
-        <v>1197</v>
+        <v>1198</v>
       </c>
       <c r="C512" t="s" s="2">
-        <v>1197</v>
+        <v>1198</v>
       </c>
       <c r="D512" s="2"/>
       <c r="E512" t="s" s="2">
@@ -62709,10 +62712,10 @@
         <v>81</v>
       </c>
       <c r="M512" t="s" s="2">
-        <v>1198</v>
+        <v>1199</v>
       </c>
       <c r="N512" t="s" s="2">
-        <v>1198</v>
+        <v>1199</v>
       </c>
       <c r="O512" s="2"/>
       <c r="P512" s="2"/>
@@ -62763,7 +62766,7 @@
         <v>74</v>
       </c>
       <c r="AG512" t="s" s="2">
-        <v>1197</v>
+        <v>1198</v>
       </c>
       <c r="AH512" t="s" s="2">
         <v>75</v>
@@ -62780,13 +62783,13 @@
     </row>
     <row r="513">
       <c r="A513" t="s" s="2">
-        <v>1183</v>
+        <v>1184</v>
       </c>
       <c r="B513" t="s" s="2">
-        <v>1199</v>
+        <v>1200</v>
       </c>
       <c r="C513" t="s" s="2">
-        <v>1199</v>
+        <v>1200</v>
       </c>
       <c r="D513" s="2"/>
       <c r="E513" t="s" s="2">
@@ -62809,13 +62812,13 @@
         <v>74</v>
       </c>
       <c r="L513" t="s" s="2">
-        <v>1076</v>
+        <v>1077</v>
       </c>
       <c r="M513" t="s" s="2">
-        <v>1077</v>
+        <v>1078</v>
       </c>
       <c r="N513" t="s" s="2">
-        <v>1077</v>
+        <v>1078</v>
       </c>
       <c r="O513" s="2"/>
       <c r="P513" s="2"/>
@@ -62866,7 +62869,7 @@
         <v>74</v>
       </c>
       <c r="AG513" t="s" s="2">
-        <v>1199</v>
+        <v>1200</v>
       </c>
       <c r="AH513" t="s" s="2">
         <v>80</v>
@@ -62883,13 +62886,13 @@
     </row>
     <row r="514">
       <c r="A514" t="s" s="2">
-        <v>1183</v>
+        <v>1184</v>
       </c>
       <c r="B514" t="s" s="2">
-        <v>1200</v>
+        <v>1201</v>
       </c>
       <c r="C514" t="s" s="2">
-        <v>1200</v>
+        <v>1201</v>
       </c>
       <c r="D514" s="2"/>
       <c r="E514" t="s" s="2">
@@ -62912,13 +62915,13 @@
         <v>74</v>
       </c>
       <c r="L514" t="s" s="2">
-        <v>1057</v>
+        <v>1058</v>
       </c>
       <c r="M514" t="s" s="2">
-        <v>1201</v>
+        <v>1202</v>
       </c>
       <c r="N514" t="s" s="2">
-        <v>1201</v>
+        <v>1202</v>
       </c>
       <c r="O514" s="2"/>
       <c r="P514" s="2"/>
@@ -62969,7 +62972,7 @@
         <v>74</v>
       </c>
       <c r="AG514" t="s" s="2">
-        <v>1200</v>
+        <v>1201</v>
       </c>
       <c r="AH514" t="s" s="2">
         <v>80</v>
@@ -62986,13 +62989,13 @@
     </row>
     <row r="515">
       <c r="A515" t="s" s="2">
-        <v>1183</v>
+        <v>1184</v>
       </c>
       <c r="B515" t="s" s="2">
-        <v>1202</v>
+        <v>1203</v>
       </c>
       <c r="C515" t="s" s="2">
-        <v>1202</v>
+        <v>1203</v>
       </c>
       <c r="D515" s="2"/>
       <c r="E515" t="s" s="2">
@@ -63015,13 +63018,13 @@
         <v>74</v>
       </c>
       <c r="L515" t="s" s="2">
-        <v>1057</v>
+        <v>1058</v>
       </c>
       <c r="M515" t="s" s="2">
-        <v>1203</v>
+        <v>1204</v>
       </c>
       <c r="N515" t="s" s="2">
-        <v>1203</v>
+        <v>1204</v>
       </c>
       <c r="O515" s="2"/>
       <c r="P515" s="2"/>
@@ -63072,7 +63075,7 @@
         <v>74</v>
       </c>
       <c r="AG515" t="s" s="2">
-        <v>1202</v>
+        <v>1203</v>
       </c>
       <c r="AH515" t="s" s="2">
         <v>80</v>
@@ -63089,13 +63092,13 @@
     </row>
     <row r="516">
       <c r="A516" t="s" s="2">
-        <v>1183</v>
+        <v>1184</v>
       </c>
       <c r="B516" t="s" s="2">
-        <v>1204</v>
+        <v>1205</v>
       </c>
       <c r="C516" t="s" s="2">
-        <v>1204</v>
+        <v>1205</v>
       </c>
       <c r="D516" s="2"/>
       <c r="E516" t="s" s="2">
@@ -63118,13 +63121,13 @@
         <v>74</v>
       </c>
       <c r="L516" t="s" s="2">
-        <v>975</v>
+        <v>976</v>
       </c>
       <c r="M516" t="s" s="2">
-        <v>1205</v>
+        <v>1206</v>
       </c>
       <c r="N516" t="s" s="2">
-        <v>1206</v>
+        <v>1207</v>
       </c>
       <c r="O516" s="2"/>
       <c r="P516" s="2"/>
@@ -63155,7 +63158,7 @@
       </c>
       <c r="Z516" s="2"/>
       <c r="AA516" t="s" s="2">
-        <v>1207</v>
+        <v>1208</v>
       </c>
       <c r="AB516" t="s" s="2">
         <v>74</v>
@@ -63173,7 +63176,7 @@
         <v>74</v>
       </c>
       <c r="AG516" t="s" s="2">
-        <v>1204</v>
+        <v>1205</v>
       </c>
       <c r="AH516" t="s" s="2">
         <v>80</v>
@@ -63190,13 +63193,13 @@
     </row>
     <row r="517">
       <c r="A517" t="s" s="2">
-        <v>1183</v>
+        <v>1184</v>
       </c>
       <c r="B517" t="s" s="2">
-        <v>1208</v>
+        <v>1209</v>
       </c>
       <c r="C517" t="s" s="2">
-        <v>1208</v>
+        <v>1209</v>
       </c>
       <c r="D517" s="2"/>
       <c r="E517" t="s" s="2">
@@ -63219,13 +63222,13 @@
         <v>74</v>
       </c>
       <c r="L517" t="s" s="2">
-        <v>1209</v>
+        <v>1210</v>
       </c>
       <c r="M517" t="s" s="2">
-        <v>1210</v>
+        <v>1211</v>
       </c>
       <c r="N517" t="s" s="2">
-        <v>1210</v>
+        <v>1211</v>
       </c>
       <c r="O517" s="2"/>
       <c r="P517" s="2"/>
@@ -63276,7 +63279,7 @@
         <v>74</v>
       </c>
       <c r="AG517" t="s" s="2">
-        <v>1208</v>
+        <v>1209</v>
       </c>
       <c r="AH517" t="s" s="2">
         <v>80</v>
@@ -63293,13 +63296,13 @@
     </row>
     <row r="518">
       <c r="A518" t="s" s="2">
-        <v>1183</v>
+        <v>1184</v>
       </c>
       <c r="B518" t="s" s="2">
-        <v>1211</v>
+        <v>1212</v>
       </c>
       <c r="C518" t="s" s="2">
-        <v>1211</v>
+        <v>1212</v>
       </c>
       <c r="D518" s="2"/>
       <c r="E518" t="s" s="2">
@@ -63322,13 +63325,13 @@
         <v>74</v>
       </c>
       <c r="L518" t="s" s="2">
-        <v>1057</v>
+        <v>1058</v>
       </c>
       <c r="M518" t="s" s="2">
-        <v>1212</v>
+        <v>1213</v>
       </c>
       <c r="N518" t="s" s="2">
-        <v>1212</v>
+        <v>1213</v>
       </c>
       <c r="O518" s="2"/>
       <c r="P518" s="2"/>
@@ -63379,7 +63382,7 @@
         <v>74</v>
       </c>
       <c r="AG518" t="s" s="2">
-        <v>1211</v>
+        <v>1212</v>
       </c>
       <c r="AH518" t="s" s="2">
         <v>75</v>
@@ -63396,13 +63399,13 @@
     </row>
     <row r="519">
       <c r="A519" t="s" s="2">
-        <v>1183</v>
+        <v>1184</v>
       </c>
       <c r="B519" t="s" s="2">
-        <v>1213</v>
+        <v>1214</v>
       </c>
       <c r="C519" t="s" s="2">
-        <v>1213</v>
+        <v>1214</v>
       </c>
       <c r="D519" s="2"/>
       <c r="E519" t="s" s="2">
@@ -63428,10 +63431,10 @@
         <v>81</v>
       </c>
       <c r="M519" t="s" s="2">
-        <v>1214</v>
+        <v>1215</v>
       </c>
       <c r="N519" t="s" s="2">
-        <v>1214</v>
+        <v>1215</v>
       </c>
       <c r="O519" s="2"/>
       <c r="P519" s="2"/>
@@ -63482,7 +63485,7 @@
         <v>74</v>
       </c>
       <c r="AG519" t="s" s="2">
-        <v>1213</v>
+        <v>1214</v>
       </c>
       <c r="AH519" t="s" s="2">
         <v>75</v>
